--- a/argus/kship/models/136150_model.xlsx
+++ b/argus/kship/models/136150_model.xlsx
@@ -3774,7 +3774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-09-30</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 44.7, "op_wape_pct": 116.1, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 68.89, "rev_act": 42.66, "op_pred": -13.78, "op_act": -10.14}, {"q": "2025Q4", "rev_pred": 68.89, "rev_act": 116.45, "op_pred": -13.78, "op_act": 9.48}, {"q": "2026Q1", "rev_pred": 68.89, "rev_act": 39.88, "op_pred": -13.78, "op_act": -20.14}, {"q": "2026Q2", "rev_pred": 68.89, "rev_act": 99.52, "op_pred": -13.78, "op_act": 5.43}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 44.7, "op_wape_pct": 116.1, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "selection_oos_at_freeze": null, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 68.89, "rev_act": 42.66, "op_pred": -13.78, "op_act": -10.14}, {"q": "2025Q4", "rev_pred": 68.89, "rev_act": 116.45, "op_pred": -13.78, "op_act": 9.48}, {"q": "2026Q1", "rev_pred": 68.89, "rev_act": 39.88, "op_pred": -13.78, "op_act": -20.14}, {"q": "2026Q2", "rev_pred": 68.89, "rev_act": 99.52, "op_pred": -13.78, "op_act": 5.43}]}</t>
         </is>
       </c>
     </row>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -7435,7 +7435,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/136150_model.xlsx
+++ b/argus/kship/models/136150_model.xlsx
@@ -25,7 +25,7 @@
     <definedName name="BS별도H">BS별도!$C$1:$W$1</definedName>
     <definedName name="BS별도">BS별도!$C$5:$W$76</definedName>
     <definedName name="SUBQH">subQ!$A$1:$W$1</definedName>
-    <definedName name="subQ">subQ!$A$5:$W$39</definedName>
+    <definedName name="subQ">subQ!$A$5:$W$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -888,838 +888,898 @@
     <comment ref="K25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 121억 × 1.35% − 총차입금 80억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 121억 × 1.35%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 80억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도</t>
       </text>
     </comment>
     <comment ref="L25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 113억 × 1.35% − 총차입금 80억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 113억 × 1.35%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 80억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도</t>
       </text>
     </comment>
     <comment ref="N25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 90억 × 1.35% − 총차입금 80억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 90억 × 1.35%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 80억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도</t>
       </text>
     </comment>
     <comment ref="O25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 82억 × 1.35% − 총차입금 80억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 82억 × 1.35%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 80억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도</t>
       </text>
     </comment>
     <comment ref="P25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 62억 × 1.35% − 총차입금 80억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 62억 × 1.35%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 80억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도</t>
       </text>
     </comment>
     <comment ref="Q25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 54억 × 1.35% − 총차입금 80억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 54억 × 1.35%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 80억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도</t>
       </text>
     </comment>
     <comment ref="S25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 31억 × 1.35% − 총차입금 80억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 31억 × 1.35%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 80억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도</t>
       </text>
     </comment>
     <comment ref="T25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 23억 × 1.35% − 총차입금 80억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 23억 × 1.35%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 80억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도</t>
       </text>
     </comment>
     <comment ref="U25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 3억 × 1.35% − 총차입금 80억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 3억 × 1.35%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 80억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도</t>
       </text>
     </comment>
     <comment ref="V25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 -5억 × 1.35% − 총차입금 80억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 -5억 × 1.35%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 80억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도</t>
       </text>
     </comment>
     <comment ref="K26" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): 모델 v 그대로
+이자발생자산 121억 × 1.35%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 80억 × 0.00%(없음) (연율) ÷ 4</t>
+      </text>
+    </comment>
+    <comment ref="L26" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): 모델 v 그대로
+이자발생자산 113억 × 1.35%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 80억 × 0.00%(없음) (연율) ÷ 4</t>
+      </text>
+    </comment>
+    <comment ref="N26" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): 모델 v 그대로
+이자발생자산 90억 × 1.35%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 80억 × 0.00%(없음) (연율) ÷ 4</t>
+      </text>
+    </comment>
+    <comment ref="O26" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): 모델 v 그대로
+이자발생자산 82억 × 1.35%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 80억 × 0.00%(없음) (연율) ÷ 4</t>
+      </text>
+    </comment>
+    <comment ref="P26" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): 모델 v 그대로
+이자발생자산 62억 × 1.35%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 80억 × 0.00%(없음) (연율) ÷ 4</t>
+      </text>
+    </comment>
+    <comment ref="Q26" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): 모델 v 그대로
+이자발생자산 54억 × 1.35%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 80억 × 0.00%(없음) (연율) ÷ 4</t>
+      </text>
+    </comment>
+    <comment ref="S26" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): 모델 v 그대로
+이자발생자산 31억 × 1.35%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 80억 × 0.00%(없음) (연율) ÷ 4</t>
+      </text>
+    </comment>
+    <comment ref="T26" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): 모델 v 그대로
+이자발생자산 23억 × 1.35%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 80억 × 0.00%(없음) (연율) ÷ 4</t>
+      </text>
+    </comment>
+    <comment ref="U26" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): 모델 v 그대로
+이자발생자산 3억 × 1.35%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 80억 × 0.00%(없음) (연율) ÷ 4</t>
+      </text>
+    </comment>
+    <comment ref="V26" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): 모델 v 그대로
+이자발생자산 -5억 × 1.35%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 80억 × 0.00%(없음) (연율) ÷ 4</t>
+      </text>
+    </comment>
+    <comment ref="K27" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 일회성 미가정 → 0</t>
       </text>
     </comment>
-    <comment ref="L26" authorId="0" shapeId="0">
+    <comment ref="L27" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 일회성 미가정 → 0</t>
       </text>
     </comment>
-    <comment ref="N26" authorId="0" shapeId="0">
+    <comment ref="N27" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 일회성 미가정 → 0</t>
       </text>
     </comment>
-    <comment ref="O26" authorId="0" shapeId="0">
+    <comment ref="O27" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 일회성 미가정 → 0</t>
       </text>
     </comment>
-    <comment ref="P26" authorId="0" shapeId="0">
+    <comment ref="P27" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 일회성 미가정 → 0</t>
       </text>
     </comment>
-    <comment ref="Q26" authorId="0" shapeId="0">
+    <comment ref="Q27" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 일회성 미가정 → 0</t>
       </text>
     </comment>
-    <comment ref="S26" authorId="0" shapeId="0">
+    <comment ref="S27" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 일회성 미가정 → 0</t>
       </text>
     </comment>
-    <comment ref="T26" authorId="0" shapeId="0">
+    <comment ref="T27" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 일회성 미가정 → 0</t>
       </text>
     </comment>
-    <comment ref="U26" authorId="0" shapeId="0">
+    <comment ref="U27" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 일회성 미가정 → 0</t>
       </text>
     </comment>
-    <comment ref="V26" authorId="0" shapeId="0">
+    <comment ref="V27" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 일회성 미가정 → 0</t>
       </text>
     </comment>
-    <comment ref="K27" authorId="0" shapeId="0">
+    <comment ref="K28" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 세전이익
-max(세전, 0) × 세율 22.0%(세전 합 ≤ 0 → 법정세율 근사 22% 가정)</t>
-      </text>
-    </comment>
-    <comment ref="L27" authorId="0" shapeId="0">
+max(세전, 0) × 세율 22.0%(최근 5분기 세전 합 ≤ 0; 세전 &gt; 0 분기 중위 -37.0% 도 5~27% 밖 → 법정세율 근사 22% 가정)</t>
+      </text>
+    </comment>
+    <comment ref="L28" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 세전이익
-max(세전, 0) × 세율 22.0%(세전 합 ≤ 0 → 법정세율 근사 22% 가정)</t>
-      </text>
-    </comment>
-    <comment ref="N27" authorId="0" shapeId="0">
+max(세전, 0) × 세율 22.0%(최근 5분기 세전 합 ≤ 0; 세전 &gt; 0 분기 중위 -37.0% 도 5~27% 밖 → 법정세율 근사 22% 가정)</t>
+      </text>
+    </comment>
+    <comment ref="N28" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 세전이익
-max(세전, 0) × 세율 22.0%(세전 합 ≤ 0 → 법정세율 근사 22% 가정)</t>
-      </text>
-    </comment>
-    <comment ref="O27" authorId="0" shapeId="0">
+max(세전, 0) × 세율 22.0%(최근 5분기 세전 합 ≤ 0; 세전 &gt; 0 분기 중위 -37.0% 도 5~27% 밖 → 법정세율 근사 22% 가정)</t>
+      </text>
+    </comment>
+    <comment ref="O28" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 세전이익
-max(세전, 0) × 세율 22.0%(세전 합 ≤ 0 → 법정세율 근사 22% 가정)</t>
-      </text>
-    </comment>
-    <comment ref="P27" authorId="0" shapeId="0">
+max(세전, 0) × 세율 22.0%(최근 5분기 세전 합 ≤ 0; 세전 &gt; 0 분기 중위 -37.0% 도 5~27% 밖 → 법정세율 근사 22% 가정)</t>
+      </text>
+    </comment>
+    <comment ref="P28" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 세전이익
-max(세전, 0) × 세율 22.0%(세전 합 ≤ 0 → 법정세율 근사 22% 가정)</t>
-      </text>
-    </comment>
-    <comment ref="Q27" authorId="0" shapeId="0">
+max(세전, 0) × 세율 22.0%(최근 5분기 세전 합 ≤ 0; 세전 &gt; 0 분기 중위 -37.0% 도 5~27% 밖 → 법정세율 근사 22% 가정)</t>
+      </text>
+    </comment>
+    <comment ref="Q28" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 세전이익
-max(세전, 0) × 세율 22.0%(세전 합 ≤ 0 → 법정세율 근사 22% 가정)</t>
-      </text>
-    </comment>
-    <comment ref="S27" authorId="0" shapeId="0">
+max(세전, 0) × 세율 22.0%(최근 5분기 세전 합 ≤ 0; 세전 &gt; 0 분기 중위 -37.0% 도 5~27% 밖 → 법정세율 근사 22% 가정)</t>
+      </text>
+    </comment>
+    <comment ref="S28" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 세전이익
-max(세전, 0) × 세율 22.0%(세전 합 ≤ 0 → 법정세율 근사 22% 가정)</t>
-      </text>
-    </comment>
-    <comment ref="T27" authorId="0" shapeId="0">
+max(세전, 0) × 세율 22.0%(최근 5분기 세전 합 ≤ 0; 세전 &gt; 0 분기 중위 -37.0% 도 5~27% 밖 → 법정세율 근사 22% 가정)</t>
+      </text>
+    </comment>
+    <comment ref="T28" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 세전이익
-max(세전, 0) × 세율 22.0%(세전 합 ≤ 0 → 법정세율 근사 22% 가정)</t>
-      </text>
-    </comment>
-    <comment ref="U27" authorId="0" shapeId="0">
+max(세전, 0) × 세율 22.0%(최근 5분기 세전 합 ≤ 0; 세전 &gt; 0 분기 중위 -37.0% 도 5~27% 밖 → 법정세율 근사 22% 가정)</t>
+      </text>
+    </comment>
+    <comment ref="U28" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 세전이익
-max(세전, 0) × 세율 22.0%(세전 합 ≤ 0 → 법정세율 근사 22% 가정)</t>
-      </text>
-    </comment>
-    <comment ref="V27" authorId="0" shapeId="0">
+max(세전, 0) × 세율 22.0%(최근 5분기 세전 합 ≤ 0; 세전 &gt; 0 분기 중위 -37.0% 도 5~27% 밖 → 법정세율 근사 22% 가정)</t>
+      </text>
+    </comment>
+    <comment ref="V28" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 세전이익
-max(세전, 0) × 세율 22.0%(세전 합 ≤ 0 → 법정세율 근사 22% 가정)</t>
-      </text>
-    </comment>
-    <comment ref="K28" authorId="0" shapeId="0">
+max(세전, 0) × 세율 22.0%(최근 5분기 세전 합 ≤ 0; 세전 &gt; 0 분기 중위 -37.0% 도 5~27% 밖 → 법정세율 근사 22% 가정)</t>
+      </text>
+    </comment>
+    <comment ref="K29" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 당기순이익
 당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)</t>
       </text>
     </comment>
-    <comment ref="L28" authorId="0" shapeId="0">
+    <comment ref="L29" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 당기순이익
 당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)</t>
       </text>
     </comment>
-    <comment ref="N28" authorId="0" shapeId="0">
+    <comment ref="N29" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 당기순이익
 당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)</t>
       </text>
     </comment>
-    <comment ref="O28" authorId="0" shapeId="0">
+    <comment ref="O29" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 당기순이익
 당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)</t>
       </text>
     </comment>
-    <comment ref="P28" authorId="0" shapeId="0">
+    <comment ref="P29" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 당기순이익
 당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)</t>
       </text>
     </comment>
-    <comment ref="Q28" authorId="0" shapeId="0">
+    <comment ref="Q29" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 당기순이익
 당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)</t>
       </text>
     </comment>
-    <comment ref="S28" authorId="0" shapeId="0">
+    <comment ref="S29" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 당기순이익
 당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)</t>
       </text>
     </comment>
-    <comment ref="T28" authorId="0" shapeId="0">
+    <comment ref="T29" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 당기순이익
 당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)</t>
       </text>
     </comment>
-    <comment ref="U28" authorId="0" shapeId="0">
+    <comment ref="U29" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 당기순이익
 당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)</t>
       </text>
     </comment>
-    <comment ref="V28" authorId="0" shapeId="0">
+    <comment ref="V29" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 당기순이익
 당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)</t>
       </text>
     </comment>
-    <comment ref="K29" authorId="0" shapeId="0">
+    <comment ref="K30" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 마지막 실적 유지(가정)</t>
       </text>
     </comment>
-    <comment ref="L29" authorId="0" shapeId="0">
+    <comment ref="L30" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 마지막 실적 유지(가정)</t>
       </text>
     </comment>
-    <comment ref="N29" authorId="0" shapeId="0">
+    <comment ref="N30" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 마지막 실적 유지(가정)</t>
       </text>
     </comment>
-    <comment ref="O29" authorId="0" shapeId="0">
+    <comment ref="O30" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 마지막 실적 유지(가정)</t>
       </text>
     </comment>
-    <comment ref="P29" authorId="0" shapeId="0">
+    <comment ref="P30" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 마지막 실적 유지(가정)</t>
       </text>
     </comment>
-    <comment ref="Q29" authorId="0" shapeId="0">
+    <comment ref="Q30" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 마지막 실적 유지(가정)</t>
       </text>
     </comment>
-    <comment ref="S29" authorId="0" shapeId="0">
+    <comment ref="S30" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 마지막 실적 유지(가정)</t>
       </text>
     </comment>
-    <comment ref="T29" authorId="0" shapeId="0">
+    <comment ref="T30" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 마지막 실적 유지(가정)</t>
       </text>
     </comment>
-    <comment ref="U29" authorId="0" shapeId="0">
+    <comment ref="U30" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 마지막 실적 유지(가정)</t>
       </text>
     </comment>
-    <comment ref="V29" authorId="0" shapeId="0">
+    <comment ref="V30" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 마지막 실적 유지(가정)</t>
       </text>
     </comment>
-    <comment ref="K30" authorId="0" shapeId="0">
+    <comment ref="K31" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 전분기 + 당기순이익 − v
 전분기 + 당기순이익 − 배당(Q2 지급 가정)</t>
       </text>
     </comment>
-    <comment ref="L30" authorId="0" shapeId="0">
+    <comment ref="L31" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 전분기 + 당기순이익 − v
 전분기 + 당기순이익 − 배당(Q2 지급 가정)</t>
       </text>
     </comment>
-    <comment ref="N30" authorId="0" shapeId="0">
+    <comment ref="N31" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 전분기 + 당기순이익 − v
 전분기 + 당기순이익 − 배당(Q2 지급 가정)</t>
       </text>
     </comment>
-    <comment ref="O30" authorId="0" shapeId="0">
+    <comment ref="O31" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 전분기 + 당기순이익 − v
 전분기 + 당기순이익 − 배당(Q2 지급 가정)</t>
       </text>
     </comment>
-    <comment ref="P30" authorId="0" shapeId="0">
+    <comment ref="P31" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 전분기 + 당기순이익 − v
 전분기 + 당기순이익 − 배당(Q2 지급 가정)</t>
       </text>
     </comment>
-    <comment ref="Q30" authorId="0" shapeId="0">
+    <comment ref="Q31" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 전분기 + 당기순이익 − v
 전분기 + 당기순이익 − 배당(Q2 지급 가정)</t>
       </text>
     </comment>
-    <comment ref="S30" authorId="0" shapeId="0">
+    <comment ref="S31" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 전분기 + 당기순이익 − v
 전분기 + 당기순이익 − 배당(Q2 지급 가정)</t>
       </text>
     </comment>
-    <comment ref="T30" authorId="0" shapeId="0">
+    <comment ref="T31" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 전분기 + 당기순이익 − v
 전분기 + 당기순이익 − 배당(Q2 지급 가정)</t>
       </text>
     </comment>
-    <comment ref="U30" authorId="0" shapeId="0">
+    <comment ref="U31" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 전분기 + 당기순이익 − v
 전분기 + 당기순이익 − 배당(Q2 지급 가정)</t>
       </text>
     </comment>
-    <comment ref="V30" authorId="0" shapeId="0">
+    <comment ref="V31" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 전분기 + 당기순이익 − v
 전분기 + 당기순이익 − 배당(Q2 지급 가정)</t>
       </text>
     </comment>
-    <comment ref="K31" authorId="0" shapeId="0">
+    <comment ref="K32" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 전분기 + 지배주주순이익 − v
 전분기 + 지배주주순이익 − 배당</t>
       </text>
     </comment>
-    <comment ref="L31" authorId="0" shapeId="0">
+    <comment ref="L32" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 전분기 + 지배주주순이익 − v
 전분기 + 지배주주순이익 − 배당</t>
       </text>
     </comment>
-    <comment ref="N31" authorId="0" shapeId="0">
+    <comment ref="N32" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 전분기 + 지배주주순이익 − v
 전분기 + 지배주주순이익 − 배당</t>
       </text>
     </comment>
-    <comment ref="O31" authorId="0" shapeId="0">
+    <comment ref="O32" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 전분기 + 지배주주순이익 − v
 전분기 + 지배주주순이익 − 배당</t>
       </text>
     </comment>
-    <comment ref="P31" authorId="0" shapeId="0">
+    <comment ref="P32" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 전분기 + 지배주주순이익 − v
 전분기 + 지배주주순이익 − 배당</t>
       </text>
     </comment>
-    <comment ref="Q31" authorId="0" shapeId="0">
+    <comment ref="Q32" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 전분기 + 지배주주순이익 − v
 전분기 + 지배주주순이익 − 배당</t>
       </text>
     </comment>
-    <comment ref="S31" authorId="0" shapeId="0">
+    <comment ref="S32" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 전분기 + 지배주주순이익 − v
 전분기 + 지배주주순이익 − 배당</t>
       </text>
     </comment>
-    <comment ref="T31" authorId="0" shapeId="0">
+    <comment ref="T32" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 전분기 + 지배주주순이익 − v
 전분기 + 지배주주순이익 − 배당</t>
       </text>
     </comment>
-    <comment ref="U31" authorId="0" shapeId="0">
+    <comment ref="U32" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 전분기 + 지배주주순이익 − v
 전분기 + 지배주주순이익 − 배당</t>
       </text>
     </comment>
-    <comment ref="V31" authorId="0" shapeId="0">
+    <comment ref="V32" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 전분기 + 지배주주순이익 − v
 전분기 + 지배주주순이익 − 배당</t>
       </text>
     </comment>
-    <comment ref="K32" authorId="0" shapeId="0">
+    <comment ref="K33" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 마지막 실적 유지(가정)</t>
       </text>
     </comment>
-    <comment ref="L32" authorId="0" shapeId="0">
+    <comment ref="L33" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 마지막 실적 유지(가정)</t>
       </text>
     </comment>
-    <comment ref="N32" authorId="0" shapeId="0">
+    <comment ref="N33" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 마지막 실적 유지(가정)</t>
       </text>
     </comment>
-    <comment ref="O32" authorId="0" shapeId="0">
+    <comment ref="O33" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 마지막 실적 유지(가정)</t>
       </text>
     </comment>
-    <comment ref="P32" authorId="0" shapeId="0">
+    <comment ref="P33" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 마지막 실적 유지(가정)</t>
       </text>
     </comment>
-    <comment ref="Q32" authorId="0" shapeId="0">
+    <comment ref="Q33" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 마지막 실적 유지(가정)</t>
       </text>
     </comment>
-    <comment ref="S32" authorId="0" shapeId="0">
+    <comment ref="S33" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 마지막 실적 유지(가정)</t>
       </text>
     </comment>
-    <comment ref="T32" authorId="0" shapeId="0">
+    <comment ref="T33" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 마지막 실적 유지(가정)</t>
       </text>
     </comment>
-    <comment ref="U32" authorId="0" shapeId="0">
+    <comment ref="U33" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 마지막 실적 유지(가정)</t>
       </text>
     </comment>
-    <comment ref="V32" authorId="0" shapeId="0">
+    <comment ref="V33" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 마지막 실적 유지(가정)</t>
       </text>
     </comment>
-    <comment ref="K33" authorId="0" shapeId="0">
+    <comment ref="K34" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
       </text>
     </comment>
-    <comment ref="L33" authorId="0" shapeId="0">
+    <comment ref="L34" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
       </text>
     </comment>
-    <comment ref="N33" authorId="0" shapeId="0">
+    <comment ref="N34" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
       </text>
     </comment>
-    <comment ref="O33" authorId="0" shapeId="0">
+    <comment ref="O34" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
       </text>
     </comment>
-    <comment ref="P33" authorId="0" shapeId="0">
+    <comment ref="P34" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
       </text>
     </comment>
-    <comment ref="Q33" authorId="0" shapeId="0">
+    <comment ref="Q34" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
       </text>
     </comment>
-    <comment ref="S33" authorId="0" shapeId="0">
+    <comment ref="S34" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
       </text>
     </comment>
-    <comment ref="T33" authorId="0" shapeId="0">
+    <comment ref="T34" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
       </text>
     </comment>
-    <comment ref="U33" authorId="0" shapeId="0">
+    <comment ref="U34" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
       </text>
     </comment>
-    <comment ref="V33" authorId="0" shapeId="0">
+    <comment ref="V34" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
       </text>
     </comment>
-    <comment ref="K34" authorId="0" shapeId="0">
+    <comment ref="K35" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정</t>
       </text>
     </comment>
-    <comment ref="L34" authorId="0" shapeId="0">
+    <comment ref="L35" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정</t>
       </text>
     </comment>
-    <comment ref="N34" authorId="0" shapeId="0">
+    <comment ref="N35" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정</t>
       </text>
     </comment>
-    <comment ref="O34" authorId="0" shapeId="0">
+    <comment ref="O35" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정</t>
       </text>
     </comment>
-    <comment ref="P34" authorId="0" shapeId="0">
+    <comment ref="P35" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정</t>
       </text>
     </comment>
-    <comment ref="Q34" authorId="0" shapeId="0">
+    <comment ref="Q35" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정</t>
       </text>
     </comment>
-    <comment ref="S34" authorId="0" shapeId="0">
+    <comment ref="S35" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정</t>
       </text>
     </comment>
-    <comment ref="T34" authorId="0" shapeId="0">
+    <comment ref="T35" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정</t>
       </text>
     </comment>
-    <comment ref="U34" authorId="0" shapeId="0">
+    <comment ref="U35" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정</t>
       </text>
     </comment>
-    <comment ref="V34" authorId="0" shapeId="0">
+    <comment ref="V35" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정</t>
       </text>
     </comment>
-    <comment ref="K38" authorId="0" shapeId="0">
+    <comment ref="K39" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
       </text>
     </comment>
-    <comment ref="L38" authorId="0" shapeId="0">
+    <comment ref="L39" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
       </text>
     </comment>
-    <comment ref="N38" authorId="0" shapeId="0">
+    <comment ref="N39" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
       </text>
     </comment>
-    <comment ref="O38" authorId="0" shapeId="0">
+    <comment ref="O39" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
       </text>
     </comment>
-    <comment ref="P38" authorId="0" shapeId="0">
+    <comment ref="P39" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
       </text>
     </comment>
-    <comment ref="Q38" authorId="0" shapeId="0">
+    <comment ref="Q39" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
       </text>
     </comment>
-    <comment ref="S38" authorId="0" shapeId="0">
+    <comment ref="S39" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
       </text>
     </comment>
-    <comment ref="T38" authorId="0" shapeId="0">
+    <comment ref="T39" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
       </text>
     </comment>
-    <comment ref="U38" authorId="0" shapeId="0">
+    <comment ref="U39" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
       </text>
     </comment>
-    <comment ref="V38" authorId="0" shapeId="0">
+    <comment ref="V39" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
       </text>
     </comment>
-    <comment ref="K41" authorId="0" shapeId="0">
+    <comment ref="K42" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
 현재 종가 ÷ BPS(추정 포함)</t>
       </text>
     </comment>
-    <comment ref="L41" authorId="0" shapeId="0">
+    <comment ref="L42" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
 현재 종가 ÷ BPS(추정 포함)</t>
       </text>
     </comment>
-    <comment ref="N41" authorId="0" shapeId="0">
+    <comment ref="N42" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
 현재 종가 ÷ BPS(추정 포함)</t>
       </text>
     </comment>
-    <comment ref="O41" authorId="0" shapeId="0">
+    <comment ref="O42" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
 현재 종가 ÷ BPS(추정 포함)</t>
       </text>
     </comment>
-    <comment ref="P41" authorId="0" shapeId="0">
+    <comment ref="P42" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
 현재 종가 ÷ BPS(추정 포함)</t>
       </text>
     </comment>
-    <comment ref="Q41" authorId="0" shapeId="0">
+    <comment ref="Q42" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
 현재 종가 ÷ BPS(추정 포함)</t>
       </text>
     </comment>
-    <comment ref="S41" authorId="0" shapeId="0">
+    <comment ref="S42" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
 현재 종가 ÷ BPS(추정 포함)</t>
       </text>
     </comment>
-    <comment ref="T41" authorId="0" shapeId="0">
+    <comment ref="T42" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
 현재 종가 ÷ BPS(추정 포함)</t>
       </text>
     </comment>
-    <comment ref="U41" authorId="0" shapeId="0">
+    <comment ref="U42" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
 현재 종가 ÷ BPS(추정 포함)</t>
       </text>
     </comment>
-    <comment ref="V41" authorId="0" shapeId="0">
+    <comment ref="V42" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
 현재 종가 ÷ BPS(추정 포함)</t>
       </text>
     </comment>
-    <comment ref="K42" authorId="0" shapeId="0">
+    <comment ref="K43" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
 = 매출액 추정(부문 미분리)</t>
       </text>
     </comment>
-    <comment ref="L42" authorId="0" shapeId="0">
+    <comment ref="L43" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
 = 매출액 추정(부문 미분리)</t>
       </text>
     </comment>
-    <comment ref="N42" authorId="0" shapeId="0">
+    <comment ref="N43" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
 = 매출액 추정(부문 미분리)</t>
       </text>
     </comment>
-    <comment ref="O42" authorId="0" shapeId="0">
+    <comment ref="O43" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
 = 매출액 추정(부문 미분리)</t>
       </text>
     </comment>
-    <comment ref="P42" authorId="0" shapeId="0">
+    <comment ref="P43" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
 = 매출액 추정(부문 미분리)</t>
       </text>
     </comment>
-    <comment ref="Q42" authorId="0" shapeId="0">
+    <comment ref="Q43" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
 = 매출액 추정(부문 미분리)</t>
       </text>
     </comment>
-    <comment ref="S42" authorId="0" shapeId="0">
+    <comment ref="S43" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
 = 매출액 추정(부문 미분리)</t>
       </text>
     </comment>
-    <comment ref="T42" authorId="0" shapeId="0">
+    <comment ref="T43" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
 = 매출액 추정(부문 미분리)</t>
       </text>
     </comment>
-    <comment ref="U42" authorId="0" shapeId="0">
+    <comment ref="U43" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
 = 매출액 추정(부문 미분리)</t>
       </text>
     </comment>
-    <comment ref="V42" authorId="0" shapeId="0">
+    <comment ref="V43" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
 = 매출액 추정(부문 미분리)</t>
       </text>
     </comment>
-    <comment ref="K43" authorId="0" shapeId="0">
+    <comment ref="K44" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출전사
 = 매출액 × OPM(부문 미분리)</t>
       </text>
     </comment>
-    <comment ref="L43" authorId="0" shapeId="0">
+    <comment ref="L44" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출전사
 = 매출액 × OPM(부문 미분리)</t>
       </text>
     </comment>
-    <comment ref="N43" authorId="0" shapeId="0">
+    <comment ref="N44" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출전사
 = 매출액 × OPM(부문 미분리)</t>
       </text>
     </comment>
-    <comment ref="O43" authorId="0" shapeId="0">
+    <comment ref="O44" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출전사
 = 매출액 × OPM(부문 미분리)</t>
       </text>
     </comment>
-    <comment ref="P43" authorId="0" shapeId="0">
+    <comment ref="P44" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출전사
 = 매출액 × OPM(부문 미분리)</t>
       </text>
     </comment>
-    <comment ref="Q43" authorId="0" shapeId="0">
+    <comment ref="Q44" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출전사
 = 매출액 × OPM(부문 미분리)</t>
       </text>
     </comment>
-    <comment ref="S43" authorId="0" shapeId="0">
+    <comment ref="S44" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출전사
 = 매출액 × OPM(부문 미분리)</t>
       </text>
     </comment>
-    <comment ref="T43" authorId="0" shapeId="0">
+    <comment ref="T44" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출전사
 = 매출액 × OPM(부문 미분리)</t>
       </text>
     </comment>
-    <comment ref="U43" authorId="0" shapeId="0">
+    <comment ref="U44" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출전사
 = 매출액 × OPM(부문 미분리)</t>
       </text>
     </comment>
-    <comment ref="V43" authorId="0" shapeId="0">
+    <comment ref="V44" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출전사
 = 매출액 × OPM(부문 미분리)</t>
@@ -2122,1344 +2182,1404 @@
     </comment>
     <comment ref="K11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 121억 × 1.35% − 총차입금 80억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 121억 × 1.35%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 80억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [abs]</t>
       </text>
     </comment>
     <comment ref="L11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 113억 × 1.35% − 총차입금 80억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 113억 × 1.35%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 80억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [abs]</t>
       </text>
     </comment>
     <comment ref="N11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 90억 × 1.35% − 총차입금 80억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 90억 × 1.35%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 80억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [abs]</t>
       </text>
     </comment>
     <comment ref="O11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 82억 × 1.35% − 총차입금 80억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 82억 × 1.35%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 80억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [abs]</t>
       </text>
     </comment>
     <comment ref="P11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 62억 × 1.35% − 총차입금 80억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 62억 × 1.35%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 80억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [abs]</t>
       </text>
     </comment>
     <comment ref="Q11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 54억 × 1.35% − 총차입금 80억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 54억 × 1.35%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 80억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [abs]</t>
       </text>
     </comment>
     <comment ref="S11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 31억 × 1.35% − 총차입금 80억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 31억 × 1.35%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 80억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [abs]</t>
       </text>
     </comment>
     <comment ref="T11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 23억 × 1.35% − 총차입금 80억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 23억 × 1.35%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 80억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [abs]</t>
       </text>
     </comment>
     <comment ref="U11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 3억 × 1.35% − 총차입금 80억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 3억 × 1.35%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 80억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [abs]</t>
       </text>
     </comment>
     <comment ref="V11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 -5억 × 1.35% − 총차입금 80억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 -5억 × 1.35%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 80억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [abs]</t>
       </text>
     </comment>
     <comment ref="K12" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 이자발생자산 121억 × 1.35%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 80억 × 0.00%(없음) (연율) ÷ 4
+[abs]</t>
+      </text>
+    </comment>
+    <comment ref="L12" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 이자발생자산 113억 × 1.35%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 80억 × 0.00%(없음) (연율) ÷ 4
+[abs]</t>
+      </text>
+    </comment>
+    <comment ref="N12" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 이자발생자산 90억 × 1.35%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 80억 × 0.00%(없음) (연율) ÷ 4
+[abs]</t>
+      </text>
+    </comment>
+    <comment ref="O12" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 이자발생자산 82억 × 1.35%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 80억 × 0.00%(없음) (연율) ÷ 4
+[abs]</t>
+      </text>
+    </comment>
+    <comment ref="P12" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 이자발생자산 62억 × 1.35%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 80억 × 0.00%(없음) (연율) ÷ 4
+[abs]</t>
+      </text>
+    </comment>
+    <comment ref="Q12" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 이자발생자산 54억 × 1.35%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 80억 × 0.00%(없음) (연율) ÷ 4
+[abs]</t>
+      </text>
+    </comment>
+    <comment ref="S12" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 이자발생자산 31억 × 1.35%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 80억 × 0.00%(없음) (연율) ÷ 4
+[abs]</t>
+      </text>
+    </comment>
+    <comment ref="T12" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 이자발생자산 23억 × 1.35%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 80억 × 0.00%(없음) (연율) ÷ 4
+[abs]</t>
+      </text>
+    </comment>
+    <comment ref="U12" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 이자발생자산 3억 × 1.35%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 80억 × 0.00%(없음) (연율) ÷ 4
+[abs]</t>
+      </text>
+    </comment>
+    <comment ref="V12" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 이자발생자산 -5억 × 1.35%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 80억 × 0.00%(없음) (연율) ÷ 4
+[abs]</t>
+      </text>
+    </comment>
+    <comment ref="K13" authorId="0" shapeId="0">
       <text>
         <t>추정: 일회성 미가정 → 0
 [abs]</t>
       </text>
     </comment>
-    <comment ref="L12" authorId="0" shapeId="0">
+    <comment ref="L13" authorId="0" shapeId="0">
       <text>
         <t>추정: 일회성 미가정 → 0
 [abs]</t>
       </text>
     </comment>
-    <comment ref="N12" authorId="0" shapeId="0">
+    <comment ref="N13" authorId="0" shapeId="0">
       <text>
         <t>추정: 일회성 미가정 → 0
 [abs]</t>
       </text>
     </comment>
-    <comment ref="O12" authorId="0" shapeId="0">
+    <comment ref="O13" authorId="0" shapeId="0">
       <text>
         <t>추정: 일회성 미가정 → 0
 [abs]</t>
       </text>
     </comment>
-    <comment ref="P12" authorId="0" shapeId="0">
+    <comment ref="P13" authorId="0" shapeId="0">
       <text>
         <t>추정: 일회성 미가정 → 0
 [abs]</t>
       </text>
     </comment>
-    <comment ref="Q12" authorId="0" shapeId="0">
+    <comment ref="Q13" authorId="0" shapeId="0">
       <text>
         <t>추정: 일회성 미가정 → 0
 [abs]</t>
       </text>
     </comment>
-    <comment ref="S12" authorId="0" shapeId="0">
+    <comment ref="S13" authorId="0" shapeId="0">
       <text>
         <t>추정: 일회성 미가정 → 0
 [abs]</t>
       </text>
     </comment>
-    <comment ref="T12" authorId="0" shapeId="0">
+    <comment ref="T13" authorId="0" shapeId="0">
       <text>
         <t>추정: 일회성 미가정 → 0
 [abs]</t>
       </text>
     </comment>
-    <comment ref="U12" authorId="0" shapeId="0">
+    <comment ref="U13" authorId="0" shapeId="0">
       <text>
         <t>추정: 일회성 미가정 → 0
 [abs]</t>
       </text>
     </comment>
-    <comment ref="V12" authorId="0" shapeId="0">
+    <comment ref="V13" authorId="0" shapeId="0">
       <text>
         <t>추정: 일회성 미가정 → 0
 [abs]</t>
       </text>
     </comment>
-    <comment ref="K13" authorId="0" shapeId="0">
+    <comment ref="K14" authorId="0" shapeId="0">
       <text>
         <t>추정: 영업이익 + 금융손익 + 기타영업외 + 지분법 + 환관련(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="L13" authorId="0" shapeId="0">
+    <comment ref="L14" authorId="0" shapeId="0">
       <text>
         <t>추정: 영업이익 + 금융손익 + 기타영업외 + 지분법 + 환관련(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="N13" authorId="0" shapeId="0">
+    <comment ref="N14" authorId="0" shapeId="0">
       <text>
         <t>추정: 영업이익 + 금융손익 + 기타영업외 + 지분법 + 환관련(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="O13" authorId="0" shapeId="0">
+    <comment ref="O14" authorId="0" shapeId="0">
       <text>
         <t>추정: 영업이익 + 금융손익 + 기타영업외 + 지분법 + 환관련(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="P13" authorId="0" shapeId="0">
+    <comment ref="P14" authorId="0" shapeId="0">
       <text>
         <t>추정: 영업이익 + 금융손익 + 기타영업외 + 지분법 + 환관련(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="Q13" authorId="0" shapeId="0">
+    <comment ref="Q14" authorId="0" shapeId="0">
       <text>
         <t>추정: 영업이익 + 금융손익 + 기타영업외 + 지분법 + 환관련(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="S13" authorId="0" shapeId="0">
+    <comment ref="S14" authorId="0" shapeId="0">
       <text>
         <t>추정: 영업이익 + 금융손익 + 기타영업외 + 지분법 + 환관련(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="T13" authorId="0" shapeId="0">
+    <comment ref="T14" authorId="0" shapeId="0">
       <text>
         <t>추정: 영업이익 + 금융손익 + 기타영업외 + 지분법 + 환관련(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="U13" authorId="0" shapeId="0">
+    <comment ref="U14" authorId="0" shapeId="0">
       <text>
         <t>추정: 영업이익 + 금융손익 + 기타영업외 + 지분법 + 환관련(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="V13" authorId="0" shapeId="0">
+    <comment ref="V14" authorId="0" shapeId="0">
       <text>
         <t>추정: 영업이익 + 금융손익 + 기타영업외 + 지분법 + 환관련(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="K14" authorId="0" shapeId="0">
-      <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(세전 합 ≤ 0 → 법정세율 근사 22% 가정)
+    <comment ref="K15" authorId="0" shapeId="0">
+      <text>
+        <t>추정: max(세전, 0) × 세율 22.0%(최근 5분기 세전 합 ≤ 0; 세전 &gt; 0 분기 중위 -37.0% 도 5~27% 밖 → 법정세율 근사 22% 가정)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="L14" authorId="0" shapeId="0">
-      <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(세전 합 ≤ 0 → 법정세율 근사 22% 가정)
+    <comment ref="L15" authorId="0" shapeId="0">
+      <text>
+        <t>추정: max(세전, 0) × 세율 22.0%(최근 5분기 세전 합 ≤ 0; 세전 &gt; 0 분기 중위 -37.0% 도 5~27% 밖 → 법정세율 근사 22% 가정)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="N14" authorId="0" shapeId="0">
-      <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(세전 합 ≤ 0 → 법정세율 근사 22% 가정)
+    <comment ref="N15" authorId="0" shapeId="0">
+      <text>
+        <t>추정: max(세전, 0) × 세율 22.0%(최근 5분기 세전 합 ≤ 0; 세전 &gt; 0 분기 중위 -37.0% 도 5~27% 밖 → 법정세율 근사 22% 가정)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="O14" authorId="0" shapeId="0">
-      <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(세전 합 ≤ 0 → 법정세율 근사 22% 가정)
+    <comment ref="O15" authorId="0" shapeId="0">
+      <text>
+        <t>추정: max(세전, 0) × 세율 22.0%(최근 5분기 세전 합 ≤ 0; 세전 &gt; 0 분기 중위 -37.0% 도 5~27% 밖 → 법정세율 근사 22% 가정)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="P14" authorId="0" shapeId="0">
-      <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(세전 합 ≤ 0 → 법정세율 근사 22% 가정)
+    <comment ref="P15" authorId="0" shapeId="0">
+      <text>
+        <t>추정: max(세전, 0) × 세율 22.0%(최근 5분기 세전 합 ≤ 0; 세전 &gt; 0 분기 중위 -37.0% 도 5~27% 밖 → 법정세율 근사 22% 가정)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="Q14" authorId="0" shapeId="0">
-      <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(세전 합 ≤ 0 → 법정세율 근사 22% 가정)
+    <comment ref="Q15" authorId="0" shapeId="0">
+      <text>
+        <t>추정: max(세전, 0) × 세율 22.0%(최근 5분기 세전 합 ≤ 0; 세전 &gt; 0 분기 중위 -37.0% 도 5~27% 밖 → 법정세율 근사 22% 가정)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="S14" authorId="0" shapeId="0">
-      <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(세전 합 ≤ 0 → 법정세율 근사 22% 가정)
+    <comment ref="S15" authorId="0" shapeId="0">
+      <text>
+        <t>추정: max(세전, 0) × 세율 22.0%(최근 5분기 세전 합 ≤ 0; 세전 &gt; 0 분기 중위 -37.0% 도 5~27% 밖 → 법정세율 근사 22% 가정)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="T14" authorId="0" shapeId="0">
-      <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(세전 합 ≤ 0 → 법정세율 근사 22% 가정)
+    <comment ref="T15" authorId="0" shapeId="0">
+      <text>
+        <t>추정: max(세전, 0) × 세율 22.0%(최근 5분기 세전 합 ≤ 0; 세전 &gt; 0 분기 중위 -37.0% 도 5~27% 밖 → 법정세율 근사 22% 가정)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="U14" authorId="0" shapeId="0">
-      <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(세전 합 ≤ 0 → 법정세율 근사 22% 가정)
+    <comment ref="U15" authorId="0" shapeId="0">
+      <text>
+        <t>추정: max(세전, 0) × 세율 22.0%(최근 5분기 세전 합 ≤ 0; 세전 &gt; 0 분기 중위 -37.0% 도 5~27% 밖 → 법정세율 근사 22% 가정)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="V14" authorId="0" shapeId="0">
-      <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(세전 합 ≤ 0 → 법정세율 근사 22% 가정)
+    <comment ref="V15" authorId="0" shapeId="0">
+      <text>
+        <t>추정: max(세전, 0) × 세율 22.0%(최근 5분기 세전 합 ≤ 0; 세전 &gt; 0 분기 중위 -37.0% 도 5~27% 밖 → 법정세율 근사 22% 가정)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="K15" authorId="0" shapeId="0">
+    <comment ref="K16" authorId="0" shapeId="0">
       <text>
         <t>추정: 세전이익 − 법인세비용(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="L15" authorId="0" shapeId="0">
+    <comment ref="L16" authorId="0" shapeId="0">
       <text>
         <t>추정: 세전이익 − 법인세비용(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="N15" authorId="0" shapeId="0">
+    <comment ref="N16" authorId="0" shapeId="0">
       <text>
         <t>추정: 세전이익 − 법인세비용(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="O15" authorId="0" shapeId="0">
+    <comment ref="O16" authorId="0" shapeId="0">
       <text>
         <t>추정: 세전이익 − 법인세비용(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="P15" authorId="0" shapeId="0">
+    <comment ref="P16" authorId="0" shapeId="0">
       <text>
         <t>추정: 세전이익 − 법인세비용(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="Q15" authorId="0" shapeId="0">
+    <comment ref="Q16" authorId="0" shapeId="0">
       <text>
         <t>추정: 세전이익 − 법인세비용(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="S15" authorId="0" shapeId="0">
+    <comment ref="S16" authorId="0" shapeId="0">
       <text>
         <t>추정: 세전이익 − 법인세비용(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="T15" authorId="0" shapeId="0">
+    <comment ref="T16" authorId="0" shapeId="0">
       <text>
         <t>추정: 세전이익 − 법인세비용(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="U15" authorId="0" shapeId="0">
+    <comment ref="U16" authorId="0" shapeId="0">
       <text>
         <t>추정: 세전이익 − 법인세비용(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="V15" authorId="0" shapeId="0">
+    <comment ref="V16" authorId="0" shapeId="0">
       <text>
         <t>추정: 세전이익 − 법인세비용(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="K16" authorId="0" shapeId="0">
+    <comment ref="K17" authorId="0" shapeId="0">
       <text>
         <t>추정: 당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="L16" authorId="0" shapeId="0">
+    <comment ref="L17" authorId="0" shapeId="0">
       <text>
         <t>추정: 당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="N16" authorId="0" shapeId="0">
+    <comment ref="N17" authorId="0" shapeId="0">
       <text>
         <t>추정: 당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="O16" authorId="0" shapeId="0">
+    <comment ref="O17" authorId="0" shapeId="0">
       <text>
         <t>추정: 당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="P16" authorId="0" shapeId="0">
+    <comment ref="P17" authorId="0" shapeId="0">
       <text>
         <t>추정: 당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="Q16" authorId="0" shapeId="0">
+    <comment ref="Q17" authorId="0" shapeId="0">
       <text>
         <t>추정: 당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="S16" authorId="0" shapeId="0">
+    <comment ref="S17" authorId="0" shapeId="0">
       <text>
         <t>추정: 당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="T16" authorId="0" shapeId="0">
+    <comment ref="T17" authorId="0" shapeId="0">
       <text>
         <t>추정: 당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="U16" authorId="0" shapeId="0">
+    <comment ref="U17" authorId="0" shapeId="0">
       <text>
         <t>추정: 당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="V16" authorId="0" shapeId="0">
+    <comment ref="V17" authorId="0" shapeId="0">
       <text>
         <t>추정: 당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="H17" authorId="0" shapeId="0">
+    <comment ref="H18" authorId="0" shapeId="0">
       <text>
         <t>연간 실측(BS 시트에 2025.12A 없음 — 모델 a 값 직접)</t>
       </text>
     </comment>
-    <comment ref="K17" authorId="0" shapeId="0">
+    <comment ref="K18" authorId="0" shapeId="0">
       <text>
         <t>추정: 부채총계 + 자본총계(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="L17" authorId="0" shapeId="0">
+    <comment ref="L18" authorId="0" shapeId="0">
       <text>
         <t>추정: 부채총계 + 자본총계(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="N17" authorId="0" shapeId="0">
+    <comment ref="N18" authorId="0" shapeId="0">
       <text>
         <t>추정: 부채총계 + 자본총계(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="O17" authorId="0" shapeId="0">
+    <comment ref="O18" authorId="0" shapeId="0">
       <text>
         <t>추정: 부채총계 + 자본총계(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="P17" authorId="0" shapeId="0">
+    <comment ref="P18" authorId="0" shapeId="0">
       <text>
         <t>추정: 부채총계 + 자본총계(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="Q17" authorId="0" shapeId="0">
+    <comment ref="Q18" authorId="0" shapeId="0">
       <text>
         <t>추정: 부채총계 + 자본총계(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="S17" authorId="0" shapeId="0">
+    <comment ref="S18" authorId="0" shapeId="0">
       <text>
         <t>추정: 부채총계 + 자본총계(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="T17" authorId="0" shapeId="0">
+    <comment ref="T18" authorId="0" shapeId="0">
       <text>
         <t>추정: 부채총계 + 자본총계(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="U17" authorId="0" shapeId="0">
+    <comment ref="U18" authorId="0" shapeId="0">
       <text>
         <t>추정: 부채총계 + 자본총계(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="V17" authorId="0" shapeId="0">
+    <comment ref="V18" authorId="0" shapeId="0">
       <text>
         <t>추정: 부채총계 + 자본총계(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="H18" authorId="0" shapeId="0">
+    <comment ref="H19" authorId="0" shapeId="0">
       <text>
         <t>연간 실측(BS 시트에 2025.12A 없음 — 모델 a 값 직접)</t>
       </text>
     </comment>
-    <comment ref="K18" authorId="0" shapeId="0">
+    <comment ref="K19" authorId="0" shapeId="0">
       <text>
         <t>추정: 마지막 실적 유지(가정)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="L18" authorId="0" shapeId="0">
+    <comment ref="L19" authorId="0" shapeId="0">
       <text>
         <t>추정: 마지막 실적 유지(가정)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="N18" authorId="0" shapeId="0">
+    <comment ref="N19" authorId="0" shapeId="0">
       <text>
         <t>추정: 마지막 실적 유지(가정)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="O18" authorId="0" shapeId="0">
+    <comment ref="O19" authorId="0" shapeId="0">
       <text>
         <t>추정: 마지막 실적 유지(가정)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="P18" authorId="0" shapeId="0">
+    <comment ref="P19" authorId="0" shapeId="0">
       <text>
         <t>추정: 마지막 실적 유지(가정)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="Q18" authorId="0" shapeId="0">
+    <comment ref="Q19" authorId="0" shapeId="0">
       <text>
         <t>추정: 마지막 실적 유지(가정)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="S18" authorId="0" shapeId="0">
+    <comment ref="S19" authorId="0" shapeId="0">
       <text>
         <t>추정: 마지막 실적 유지(가정)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="T18" authorId="0" shapeId="0">
+    <comment ref="T19" authorId="0" shapeId="0">
       <text>
         <t>추정: 마지막 실적 유지(가정)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="U18" authorId="0" shapeId="0">
+    <comment ref="U19" authorId="0" shapeId="0">
       <text>
         <t>추정: 마지막 실적 유지(가정)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="V18" authorId="0" shapeId="0">
+    <comment ref="V19" authorId="0" shapeId="0">
       <text>
         <t>추정: 마지막 실적 유지(가정)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="H19" authorId="0" shapeId="0">
+    <comment ref="H20" authorId="0" shapeId="0">
       <text>
         <t>연간 실측(BS 시트에 2025.12A 없음 — 모델 a 값 직접)</t>
       </text>
     </comment>
-    <comment ref="K19" authorId="0" shapeId="0">
+    <comment ref="K20" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + 당기순이익 − 배당(Q2 지급 가정)
 [roll]</t>
       </text>
     </comment>
-    <comment ref="L19" authorId="0" shapeId="0">
+    <comment ref="L20" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + 당기순이익 − 배당(Q2 지급 가정)
 [roll]</t>
       </text>
     </comment>
-    <comment ref="N19" authorId="0" shapeId="0">
+    <comment ref="N20" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + 당기순이익 − 배당(Q2 지급 가정)
 [roll]</t>
       </text>
     </comment>
-    <comment ref="O19" authorId="0" shapeId="0">
+    <comment ref="O20" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + 당기순이익 − 배당(Q2 지급 가정)
 [roll]</t>
       </text>
     </comment>
-    <comment ref="P19" authorId="0" shapeId="0">
+    <comment ref="P20" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + 당기순이익 − 배당(Q2 지급 가정)
 [roll]</t>
       </text>
     </comment>
-    <comment ref="Q19" authorId="0" shapeId="0">
+    <comment ref="Q20" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + 당기순이익 − 배당(Q2 지급 가정)
 [roll]</t>
       </text>
     </comment>
-    <comment ref="S19" authorId="0" shapeId="0">
+    <comment ref="S20" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + 당기순이익 − 배당(Q2 지급 가정)
 [roll]</t>
       </text>
     </comment>
-    <comment ref="T19" authorId="0" shapeId="0">
+    <comment ref="T20" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + 당기순이익 − 배당(Q2 지급 가정)
 [roll]</t>
       </text>
     </comment>
-    <comment ref="U19" authorId="0" shapeId="0">
+    <comment ref="U20" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + 당기순이익 − 배당(Q2 지급 가정)
 [roll]</t>
       </text>
     </comment>
-    <comment ref="V19" authorId="0" shapeId="0">
+    <comment ref="V20" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + 당기순이익 − 배당(Q2 지급 가정)
 [roll]</t>
       </text>
     </comment>
-    <comment ref="H20" authorId="0" shapeId="0">
+    <comment ref="H21" authorId="0" shapeId="0">
       <text>
         <t>연간 실측(BS 시트에 2025.12A 없음 — 모델 a 값 직접)</t>
       </text>
     </comment>
-    <comment ref="K20" authorId="0" shapeId="0">
+    <comment ref="K21" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + 지배주주순이익 − 배당
 [roll]</t>
       </text>
     </comment>
-    <comment ref="L20" authorId="0" shapeId="0">
+    <comment ref="L21" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + 지배주주순이익 − 배당
 [roll]</t>
       </text>
     </comment>
-    <comment ref="N20" authorId="0" shapeId="0">
+    <comment ref="N21" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + 지배주주순이익 − 배당
 [roll]</t>
       </text>
     </comment>
-    <comment ref="O20" authorId="0" shapeId="0">
+    <comment ref="O21" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + 지배주주순이익 − 배당
 [roll]</t>
       </text>
     </comment>
-    <comment ref="P20" authorId="0" shapeId="0">
+    <comment ref="P21" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + 지배주주순이익 − 배당
 [roll]</t>
       </text>
     </comment>
-    <comment ref="Q20" authorId="0" shapeId="0">
+    <comment ref="Q21" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + 지배주주순이익 − 배당
 [roll]</t>
       </text>
     </comment>
-    <comment ref="S20" authorId="0" shapeId="0">
+    <comment ref="S21" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + 지배주주순이익 − 배당
 [roll]</t>
       </text>
     </comment>
-    <comment ref="T20" authorId="0" shapeId="0">
+    <comment ref="T21" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + 지배주주순이익 − 배당
 [roll]</t>
       </text>
     </comment>
-    <comment ref="U20" authorId="0" shapeId="0">
+    <comment ref="U21" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + 지배주주순이익 − 배당
 [roll]</t>
       </text>
     </comment>
-    <comment ref="V20" authorId="0" shapeId="0">
+    <comment ref="V21" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + 지배주주순이익 − 배당
 [roll]</t>
       </text>
     </comment>
-    <comment ref="H21" authorId="0" shapeId="0">
+    <comment ref="H22" authorId="0" shapeId="0">
       <text>
         <t>연간 실측(BS 시트에 2025.12A 없음 — 모델 a 값 직접)</t>
       </text>
     </comment>
-    <comment ref="K21" authorId="0" shapeId="0">
+    <comment ref="K22" authorId="0" shapeId="0">
       <text>
         <t>추정: 마지막 실적 유지(가정)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="L21" authorId="0" shapeId="0">
+    <comment ref="L22" authorId="0" shapeId="0">
       <text>
         <t>추정: 마지막 실적 유지(가정)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="N21" authorId="0" shapeId="0">
+    <comment ref="N22" authorId="0" shapeId="0">
       <text>
         <t>추정: 마지막 실적 유지(가정)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="O21" authorId="0" shapeId="0">
+    <comment ref="O22" authorId="0" shapeId="0">
       <text>
         <t>추정: 마지막 실적 유지(가정)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="P21" authorId="0" shapeId="0">
+    <comment ref="P22" authorId="0" shapeId="0">
       <text>
         <t>추정: 마지막 실적 유지(가정)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="Q21" authorId="0" shapeId="0">
+    <comment ref="Q22" authorId="0" shapeId="0">
       <text>
         <t>추정: 마지막 실적 유지(가정)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="S21" authorId="0" shapeId="0">
+    <comment ref="S22" authorId="0" shapeId="0">
       <text>
         <t>추정: 마지막 실적 유지(가정)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="T21" authorId="0" shapeId="0">
+    <comment ref="T22" authorId="0" shapeId="0">
       <text>
         <t>추정: 마지막 실적 유지(가정)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="U21" authorId="0" shapeId="0">
+    <comment ref="U22" authorId="0" shapeId="0">
       <text>
         <t>추정: 마지막 실적 유지(가정)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="V21" authorId="0" shapeId="0">
+    <comment ref="V22" authorId="0" shapeId="0">
       <text>
         <t>추정: 마지막 실적 유지(가정)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="H22" authorId="0" shapeId="0">
+    <comment ref="H23" authorId="0" shapeId="0">
       <text>
         <t>연간 실측(BS 시트에 2025.12A 없음 — 모델 a 값 직접)</t>
       </text>
     </comment>
-    <comment ref="K22" authorId="0" shapeId="0">
+    <comment ref="K23" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="L22" authorId="0" shapeId="0">
+    <comment ref="L23" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="N22" authorId="0" shapeId="0">
+    <comment ref="N23" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="O22" authorId="0" shapeId="0">
+    <comment ref="O23" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="P22" authorId="0" shapeId="0">
+    <comment ref="P23" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="Q22" authorId="0" shapeId="0">
+    <comment ref="Q23" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="S22" authorId="0" shapeId="0">
+    <comment ref="S23" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="T22" authorId="0" shapeId="0">
+    <comment ref="T23" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="U22" authorId="0" shapeId="0">
+    <comment ref="U23" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="V22" authorId="0" shapeId="0">
+    <comment ref="V23" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="H23" authorId="0" shapeId="0">
+    <comment ref="H24" authorId="0" shapeId="0">
       <text>
         <t>연간 실측(BS 시트에 2025.12A 없음 — 모델 a 값 직접)</t>
       </text>
     </comment>
-    <comment ref="K23" authorId="0" shapeId="0">
+    <comment ref="K24" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="L23" authorId="0" shapeId="0">
+    <comment ref="L24" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="N23" authorId="0" shapeId="0">
+    <comment ref="N24" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="O23" authorId="0" shapeId="0">
+    <comment ref="O24" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="P23" authorId="0" shapeId="0">
+    <comment ref="P24" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="Q23" authorId="0" shapeId="0">
+    <comment ref="Q24" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="S23" authorId="0" shapeId="0">
+    <comment ref="S24" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="T23" authorId="0" shapeId="0">
+    <comment ref="T24" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="U23" authorId="0" shapeId="0">
+    <comment ref="U24" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="V23" authorId="0" shapeId="0">
+    <comment ref="V24" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="H24" authorId="0" shapeId="0">
+    <comment ref="H25" authorId="0" shapeId="0">
       <text>
         <t>연간 실측(BS 시트에 2025.12A 없음 — 모델 a 값 직접)</t>
       </text>
     </comment>
-    <comment ref="E26" authorId="0" shapeId="0">
+    <comment ref="E27" authorId="0" shapeId="0">
       <text>
         <t>실측(계정 매핑 없음 — 모델값 직접) — fin.sep.cf.영업활동으로인한현금흐름</t>
       </text>
     </comment>
-    <comment ref="F26" authorId="0" shapeId="0">
+    <comment ref="F27" authorId="0" shapeId="0">
       <text>
         <t>실측(계정 매핑 없음 — 모델값 직접) — fin.sep.cf.영업활동으로인한현금흐름</t>
       </text>
     </comment>
-    <comment ref="G26" authorId="0" shapeId="0">
+    <comment ref="G27" authorId="0" shapeId="0">
       <text>
         <t>실측(계정 매핑 없음 — 모델값 직접) — fin.sep.cf.영업활동으로인한현금흐름</t>
       </text>
     </comment>
-    <comment ref="I26" authorId="0" shapeId="0">
+    <comment ref="I27" authorId="0" shapeId="0">
       <text>
         <t>실측(계정 매핑 없음 — 모델값 직접) — fin.sep.cf.영업활동으로인한현금흐름</t>
       </text>
     </comment>
-    <comment ref="J26" authorId="0" shapeId="0">
+    <comment ref="J27" authorId="0" shapeId="0">
       <text>
         <t>실측(계정 매핑 없음 — 모델값 직접) — fin.sep.cf.영업활동으로인한현금흐름</t>
       </text>
     </comment>
-    <comment ref="E27" authorId="0" shapeId="0">
+    <comment ref="E28" authorId="0" shapeId="0">
       <text>
         <t>실측(계정 매핑 없음 — 모델값 직접) — fin.shares.common_outstanding</t>
       </text>
     </comment>
-    <comment ref="F27" authorId="0" shapeId="0">
+    <comment ref="F28" authorId="0" shapeId="0">
       <text>
         <t>실측(계정 매핑 없음 — 모델값 직접) — fin.shares.common_outstanding</t>
       </text>
     </comment>
-    <comment ref="G27" authorId="0" shapeId="0">
+    <comment ref="G28" authorId="0" shapeId="0">
       <text>
         <t>실측(계정 매핑 없음 — 모델값 직접) — fin.shares.common_outstanding</t>
       </text>
     </comment>
-    <comment ref="I27" authorId="0" shapeId="0">
+    <comment ref="I28" authorId="0" shapeId="0">
       <text>
         <t>실측(계정 매핑 없음 — 모델값 직접) — fin.shares.common_outstanding</t>
       </text>
     </comment>
-    <comment ref="J27" authorId="0" shapeId="0">
+    <comment ref="J28" authorId="0" shapeId="0">
       <text>
         <t>실측(계정 매핑 없음 — 모델값 직접) — fin.shares.common_outstanding</t>
       </text>
     </comment>
-    <comment ref="K27" authorId="0" shapeId="0">
+    <comment ref="K28" authorId="0" shapeId="0">
       <text>
         <t>추정: 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="L27" authorId="0" shapeId="0">
+    <comment ref="L28" authorId="0" shapeId="0">
       <text>
         <t>추정: 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="N27" authorId="0" shapeId="0">
+    <comment ref="N28" authorId="0" shapeId="0">
       <text>
         <t>추정: 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="O27" authorId="0" shapeId="0">
+    <comment ref="O28" authorId="0" shapeId="0">
       <text>
         <t>추정: 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="P27" authorId="0" shapeId="0">
+    <comment ref="P28" authorId="0" shapeId="0">
       <text>
         <t>추정: 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="Q27" authorId="0" shapeId="0">
+    <comment ref="Q28" authorId="0" shapeId="0">
       <text>
         <t>추정: 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="S27" authorId="0" shapeId="0">
+    <comment ref="S28" authorId="0" shapeId="0">
       <text>
         <t>추정: 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="T27" authorId="0" shapeId="0">
+    <comment ref="T28" authorId="0" shapeId="0">
       <text>
         <t>추정: 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="U27" authorId="0" shapeId="0">
+    <comment ref="U28" authorId="0" shapeId="0">
       <text>
         <t>추정: 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="V27" authorId="0" shapeId="0">
+    <comment ref="V28" authorId="0" shapeId="0">
       <text>
         <t>추정: 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="K28" authorId="0" shapeId="0">
+    <comment ref="K29" authorId="0" shapeId="0">
       <text>
         <t>추정: 지배주주순이익 ÷ 유통주식수
 [per_share]</t>
       </text>
     </comment>
-    <comment ref="L28" authorId="0" shapeId="0">
+    <comment ref="L29" authorId="0" shapeId="0">
       <text>
         <t>추정: 지배주주순이익 ÷ 유통주식수
 [per_share]</t>
       </text>
     </comment>
-    <comment ref="N28" authorId="0" shapeId="0">
+    <comment ref="N29" authorId="0" shapeId="0">
       <text>
         <t>추정: 지배주주순이익 ÷ 유통주식수
 [per_share]</t>
       </text>
     </comment>
-    <comment ref="O28" authorId="0" shapeId="0">
+    <comment ref="O29" authorId="0" shapeId="0">
       <text>
         <t>추정: 지배주주순이익 ÷ 유통주식수
 [per_share]</t>
       </text>
     </comment>
-    <comment ref="P28" authorId="0" shapeId="0">
+    <comment ref="P29" authorId="0" shapeId="0">
       <text>
         <t>추정: 지배주주순이익 ÷ 유통주식수
 [per_share]</t>
       </text>
     </comment>
-    <comment ref="Q28" authorId="0" shapeId="0">
+    <comment ref="Q29" authorId="0" shapeId="0">
       <text>
         <t>추정: 지배주주순이익 ÷ 유통주식수
 [per_share]</t>
       </text>
     </comment>
-    <comment ref="S28" authorId="0" shapeId="0">
+    <comment ref="S29" authorId="0" shapeId="0">
       <text>
         <t>추정: 지배주주순이익 ÷ 유통주식수
 [per_share]</t>
       </text>
     </comment>
-    <comment ref="T28" authorId="0" shapeId="0">
+    <comment ref="T29" authorId="0" shapeId="0">
       <text>
         <t>추정: 지배주주순이익 ÷ 유통주식수
 [per_share]</t>
       </text>
     </comment>
-    <comment ref="U28" authorId="0" shapeId="0">
+    <comment ref="U29" authorId="0" shapeId="0">
       <text>
         <t>추정: 지배주주순이익 ÷ 유통주식수
 [per_share]</t>
       </text>
     </comment>
-    <comment ref="V28" authorId="0" shapeId="0">
+    <comment ref="V29" authorId="0" shapeId="0">
       <text>
         <t>추정: 지배주주순이익 ÷ 유통주식수
 [per_share]</t>
       </text>
     </comment>
-    <comment ref="K29" authorId="0" shapeId="0">
+    <comment ref="K30" authorId="0" shapeId="0">
       <text>
         <t>추정: 지배주주지분 ÷ 유통주식수
 [per_share]</t>
       </text>
     </comment>
-    <comment ref="L29" authorId="0" shapeId="0">
+    <comment ref="L30" authorId="0" shapeId="0">
       <text>
         <t>추정: 지배주주지분 ÷ 유통주식수
 [per_share]</t>
       </text>
     </comment>
-    <comment ref="N29" authorId="0" shapeId="0">
+    <comment ref="N30" authorId="0" shapeId="0">
       <text>
         <t>추정: 지배주주지분 ÷ 유통주식수
 [per_share]</t>
       </text>
     </comment>
-    <comment ref="O29" authorId="0" shapeId="0">
+    <comment ref="O30" authorId="0" shapeId="0">
       <text>
         <t>추정: 지배주주지분 ÷ 유통주식수
 [per_share]</t>
       </text>
     </comment>
-    <comment ref="P29" authorId="0" shapeId="0">
+    <comment ref="P30" authorId="0" shapeId="0">
       <text>
         <t>추정: 지배주주지분 ÷ 유통주식수
 [per_share]</t>
       </text>
     </comment>
-    <comment ref="Q29" authorId="0" shapeId="0">
+    <comment ref="Q30" authorId="0" shapeId="0">
       <text>
         <t>추정: 지배주주지분 ÷ 유통주식수
 [per_share]</t>
       </text>
     </comment>
-    <comment ref="S29" authorId="0" shapeId="0">
+    <comment ref="S30" authorId="0" shapeId="0">
       <text>
         <t>추정: 지배주주지분 ÷ 유통주식수
 [per_share]</t>
       </text>
     </comment>
-    <comment ref="T29" authorId="0" shapeId="0">
+    <comment ref="T30" authorId="0" shapeId="0">
       <text>
         <t>추정: 지배주주지분 ÷ 유통주식수
 [per_share]</t>
       </text>
     </comment>
-    <comment ref="U29" authorId="0" shapeId="0">
+    <comment ref="U30" authorId="0" shapeId="0">
       <text>
         <t>추정: 지배주주지분 ÷ 유통주식수
 [per_share]</t>
       </text>
     </comment>
-    <comment ref="V29" authorId="0" shapeId="0">
+    <comment ref="V30" authorId="0" shapeId="0">
       <text>
         <t>추정: 지배주주지분 ÷ 유통주식수
 [per_share]</t>
       </text>
     </comment>
-    <comment ref="G30" authorId="0" shapeId="0">
+    <comment ref="G31" authorId="0" shapeId="0">
       <text>
         <t>실측(계정 매핑 없음 — 모델값 직접) — fin.dividend.dps_common(연간, Q4 에 표기)</t>
       </text>
     </comment>
-    <comment ref="H30" authorId="0" shapeId="0">
+    <comment ref="H31" authorId="0" shapeId="0">
       <text>
         <t>연간(actual) — 분기 미완 연도, 모델 a 값 직접</t>
       </text>
     </comment>
-    <comment ref="L30" authorId="0" shapeId="0">
+    <comment ref="L31" authorId="0" shapeId="0">
       <text>
         <t>추정(가정 셀 참조 불가 — 기준값 없음, 모델값 직접): 직전 결산 DPS 0원 유지</t>
       </text>
     </comment>
-    <comment ref="Q30" authorId="0" shapeId="0">
+    <comment ref="Q31" authorId="0" shapeId="0">
       <text>
         <t>추정(가정 셀 참조 불가 — 기준값 없음, 모델값 직접): 직전 결산 DPS 0원 유지</t>
       </text>
     </comment>
-    <comment ref="V30" authorId="0" shapeId="0">
+    <comment ref="V31" authorId="0" shapeId="0">
       <text>
         <t>추정(가정 셀 참조 불가 — 기준값 없음, 모델값 직접): 직전 결산 DPS 0원 유지</t>
       </text>
     </comment>
-    <comment ref="J31" authorId="0" shapeId="0">
+    <comment ref="J32" authorId="0" shapeId="0">
       <text>
         <t>실측(계정 매핑 없음 — 모델값 직접) — 토스 일봉 분기 평균 ÷ TTM EPS</t>
       </text>
     </comment>
-    <comment ref="K31" authorId="0" shapeId="0">
+    <comment ref="K32" authorId="0" shapeId="0">
       <text>
         <t>추정(가정 셀 참조 불가 — 기준값 없음, 모델값 직접): 현재 종가 ÷ TTM EPS(추정 포함)</t>
       </text>
     </comment>
-    <comment ref="E32" authorId="0" shapeId="0">
+    <comment ref="E33" authorId="0" shapeId="0">
       <text>
         <t>실측(계정 매핑 없음 — 모델값 직접) — 토스 일봉 분기 평균 ÷ BPS</t>
       </text>
     </comment>
-    <comment ref="F32" authorId="0" shapeId="0">
+    <comment ref="F33" authorId="0" shapeId="0">
       <text>
         <t>실측(계정 매핑 없음 — 모델값 직접) — 토스 일봉 분기 평균 ÷ BPS</t>
       </text>
     </comment>
-    <comment ref="G32" authorId="0" shapeId="0">
+    <comment ref="G33" authorId="0" shapeId="0">
       <text>
         <t>실측(계정 매핑 없음 — 모델값 직접) — 토스 일봉 분기 평균 ÷ BPS</t>
       </text>
     </comment>
-    <comment ref="H32" authorId="0" shapeId="0">
+    <comment ref="H33" authorId="0" shapeId="0">
       <text>
         <t>연간(actual) — 분기 미완 연도, 모델 a 값 직접</t>
       </text>
     </comment>
-    <comment ref="I32" authorId="0" shapeId="0">
+    <comment ref="I33" authorId="0" shapeId="0">
       <text>
         <t>실측(계정 매핑 없음 — 모델값 직접) — 토스 일봉 분기 평균 ÷ BPS</t>
       </text>
     </comment>
-    <comment ref="J32" authorId="0" shapeId="0">
+    <comment ref="J33" authorId="0" shapeId="0">
       <text>
         <t>실측(계정 매핑 없음 — 모델값 직접) — 토스 일봉 분기 평균 ÷ BPS</t>
       </text>
     </comment>
-    <comment ref="K32" authorId="0" shapeId="0">
+    <comment ref="K33" authorId="0" shapeId="0">
       <text>
         <t>추정: 현재 종가 ÷ BPS(추정 포함)
 [yoy]</t>
       </text>
     </comment>
-    <comment ref="L32" authorId="0" shapeId="0">
+    <comment ref="L33" authorId="0" shapeId="0">
       <text>
         <t>추정: 현재 종가 ÷ BPS(추정 포함)
 [yoy]</t>
       </text>
     </comment>
-    <comment ref="N32" authorId="0" shapeId="0">
+    <comment ref="N33" authorId="0" shapeId="0">
       <text>
         <t>추정: 현재 종가 ÷ BPS(추정 포함)
 [yoy]</t>
       </text>
     </comment>
-    <comment ref="O32" authorId="0" shapeId="0">
+    <comment ref="O33" authorId="0" shapeId="0">
       <text>
         <t>추정: 현재 종가 ÷ BPS(추정 포함)
 [yoy]</t>
       </text>
     </comment>
-    <comment ref="P32" authorId="0" shapeId="0">
+    <comment ref="P33" authorId="0" shapeId="0">
       <text>
         <t>추정: 현재 종가 ÷ BPS(추정 포함)
 [yoy]</t>
       </text>
     </comment>
-    <comment ref="Q32" authorId="0" shapeId="0">
+    <comment ref="Q33" authorId="0" shapeId="0">
       <text>
         <t>추정: 현재 종가 ÷ BPS(추정 포함)
 [yoy]</t>
       </text>
     </comment>
-    <comment ref="S32" authorId="0" shapeId="0">
+    <comment ref="S33" authorId="0" shapeId="0">
       <text>
         <t>추정: 현재 종가 ÷ BPS(추정 포함)
 [yoy]</t>
       </text>
     </comment>
-    <comment ref="T32" authorId="0" shapeId="0">
+    <comment ref="T33" authorId="0" shapeId="0">
       <text>
         <t>추정: 현재 종가 ÷ BPS(추정 포함)
 [yoy]</t>
       </text>
     </comment>
-    <comment ref="U32" authorId="0" shapeId="0">
+    <comment ref="U33" authorId="0" shapeId="0">
       <text>
         <t>추정: 현재 종가 ÷ BPS(추정 포함)
 [yoy]</t>
       </text>
     </comment>
-    <comment ref="V32" authorId="0" shapeId="0">
+    <comment ref="V33" authorId="0" shapeId="0">
       <text>
         <t>추정: 현재 종가 ÷ BPS(추정 포함)
 [yoy]</t>
       </text>
     </comment>
-    <comment ref="E33" authorId="0" shapeId="0">
+    <comment ref="E34" authorId="0" shapeId="0">
       <text>
         <t>실측(계정 매핑 없음 — 모델값 직접) — = 매출액(부문 미분리)</t>
       </text>
     </comment>
-    <comment ref="F33" authorId="0" shapeId="0">
+    <comment ref="F34" authorId="0" shapeId="0">
       <text>
         <t>실측(계정 매핑 없음 — 모델값 직접) — = 매출액(부문 미분리)</t>
       </text>
     </comment>
-    <comment ref="G33" authorId="0" shapeId="0">
+    <comment ref="G34" authorId="0" shapeId="0">
       <text>
         <t>실측(계정 매핑 없음 — 모델값 직접) — = 매출액(부문 미분리)</t>
       </text>
     </comment>
-    <comment ref="I33" authorId="0" shapeId="0">
+    <comment ref="I34" authorId="0" shapeId="0">
       <text>
         <t>실측(계정 매핑 없음 — 모델값 직접) — = 매출액(부문 미분리)</t>
       </text>
     </comment>
-    <comment ref="J33" authorId="0" shapeId="0">
+    <comment ref="J34" authorId="0" shapeId="0">
       <text>
         <t>실측(계정 매핑 없음 — 모델값 직접) — = 매출액(부문 미분리)</t>
       </text>
     </comment>
-    <comment ref="K33" authorId="0" shapeId="0">
+    <comment ref="K34" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 추정(부문 미분리)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="L33" authorId="0" shapeId="0">
+    <comment ref="L34" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 추정(부문 미분리)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="N33" authorId="0" shapeId="0">
+    <comment ref="N34" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 추정(부문 미분리)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="O33" authorId="0" shapeId="0">
+    <comment ref="O34" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 추정(부문 미분리)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="P33" authorId="0" shapeId="0">
+    <comment ref="P34" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 추정(부문 미분리)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="Q33" authorId="0" shapeId="0">
+    <comment ref="Q34" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 추정(부문 미분리)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="S33" authorId="0" shapeId="0">
+    <comment ref="S34" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 추정(부문 미분리)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="T33" authorId="0" shapeId="0">
+    <comment ref="T34" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 추정(부문 미분리)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="U33" authorId="0" shapeId="0">
+    <comment ref="U34" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 추정(부문 미분리)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="V33" authorId="0" shapeId="0">
+    <comment ref="V34" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 추정(부문 미분리)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="E34" authorId="0" shapeId="0">
+    <comment ref="E35" authorId="0" shapeId="0">
       <text>
         <t>실측(계정 매핑 없음 — 모델값 직접) — = 영업이익(부문 미분리)</t>
       </text>
     </comment>
-    <comment ref="F34" authorId="0" shapeId="0">
+    <comment ref="F35" authorId="0" shapeId="0">
       <text>
         <t>실측(계정 매핑 없음 — 모델값 직접) — = 영업이익(부문 미분리)</t>
       </text>
     </comment>
-    <comment ref="G34" authorId="0" shapeId="0">
+    <comment ref="G35" authorId="0" shapeId="0">
       <text>
         <t>실측(계정 매핑 없음 — 모델값 직접) — = 영업이익(부문 미분리)</t>
       </text>
     </comment>
-    <comment ref="I34" authorId="0" shapeId="0">
+    <comment ref="I35" authorId="0" shapeId="0">
       <text>
         <t>실측(계정 매핑 없음 — 모델값 직접) — = 영업이익(부문 미분리)</t>
       </text>
     </comment>
-    <comment ref="J34" authorId="0" shapeId="0">
+    <comment ref="J35" authorId="0" shapeId="0">
       <text>
         <t>실측(계정 매핑 없음 — 모델값 직접) — = 영업이익(부문 미분리)</t>
       </text>
     </comment>
-    <comment ref="K34" authorId="0" shapeId="0">
+    <comment ref="K35" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 × OPM(부문 미분리)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="L34" authorId="0" shapeId="0">
+    <comment ref="L35" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 × OPM(부문 미분리)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="N34" authorId="0" shapeId="0">
+    <comment ref="N35" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 × OPM(부문 미분리)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="O34" authorId="0" shapeId="0">
+    <comment ref="O35" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 × OPM(부문 미분리)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="P34" authorId="0" shapeId="0">
+    <comment ref="P35" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 × OPM(부문 미분리)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="Q34" authorId="0" shapeId="0">
+    <comment ref="Q35" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 × OPM(부문 미분리)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="S34" authorId="0" shapeId="0">
+    <comment ref="S35" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 × OPM(부문 미분리)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="T34" authorId="0" shapeId="0">
+    <comment ref="T35" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 × OPM(부문 미분리)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="U34" authorId="0" shapeId="0">
+    <comment ref="U35" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 × OPM(부문 미분리)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="V34" authorId="0" shapeId="0">
+    <comment ref="V35" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 × OPM(부문 미분리)
 [ratio]</t>
@@ -3895,7 +4015,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 매출 드라이버 폴백(고객 연동 격자 상관 0.87 가 단일 검정 5% 임계 r 0.88 미달(n=5) (suppliers_mentions·시차 2·수준·창 8)): 전년동기 × (1+g) 추세 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출</t>
+          <t>한계: 모델 quality.warnings — 매출 드라이버 폴백(고객 연동 격자 상관 0.87 가 단일 검정 5% 임계 r 0.88 미달(n=5) (suppliers_mentions·시차 2·수준·창 8)): 전년동기 × (1+g) 추세 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 +3/+1/+6/+4(중위 +3억) → 추정 2026Q3 +0억(차 -3억, -88%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
@@ -3917,7 +4037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W56"/>
+  <dimension ref="A1:W57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4260,38 +4380,38 @@
         <v>1501.75</v>
       </c>
       <c r="K6" s="16" t="n">
-        <v>1419.72</v>
+        <v>1418.75</v>
       </c>
       <c r="L6" s="16" t="n">
-        <v>1353.36</v>
+        <v>1355.4</v>
       </c>
       <c r="M6" s="17" t="n">
-        <v>1461.87</v>
+        <v>1461.31</v>
       </c>
       <c r="N6" s="16" t="n">
-        <v>1353.36</v>
+        <v>1355.4</v>
       </c>
       <c r="O6" s="16" t="n">
-        <v>1353.36</v>
+        <v>1355.4</v>
       </c>
       <c r="P6" s="16" t="n">
-        <v>1353.36</v>
+        <v>1355.4</v>
       </c>
       <c r="Q6" s="16" t="n">
-        <v>1353.36</v>
+        <v>1355.4</v>
       </c>
       <c r="R6" s="11" t="n"/>
       <c r="S6" s="16" t="n">
-        <v>1353.36</v>
+        <v>1355.4</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1353.36</v>
+        <v>1355.4</v>
       </c>
       <c r="U6" s="16" t="n">
-        <v>1353.36</v>
+        <v>1355.4</v>
       </c>
       <c r="V6" s="16" t="n">
-        <v>1353.36</v>
+        <v>1355.4</v>
       </c>
       <c r="W6" s="11" t="n"/>
     </row>
@@ -4325,38 +4445,38 @@
         <v>1550.89</v>
       </c>
       <c r="K7" s="16" t="n">
-        <v>1353.36</v>
+        <v>1355.4</v>
       </c>
       <c r="L7" s="16" t="n">
-        <v>1353.36</v>
+        <v>1355.4</v>
       </c>
       <c r="M7" s="17" t="n">
-        <v>1353.36</v>
+        <v>1355.4</v>
       </c>
       <c r="N7" s="16" t="n">
-        <v>1353.36</v>
+        <v>1355.4</v>
       </c>
       <c r="O7" s="16" t="n">
-        <v>1353.36</v>
+        <v>1355.4</v>
       </c>
       <c r="P7" s="16" t="n">
-        <v>1353.36</v>
+        <v>1355.4</v>
       </c>
       <c r="Q7" s="16" t="n">
-        <v>1353.36</v>
+        <v>1355.4</v>
       </c>
       <c r="R7" s="11" t="n"/>
       <c r="S7" s="16" t="n">
-        <v>1353.36</v>
+        <v>1355.4</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1353.36</v>
+        <v>1355.4</v>
       </c>
       <c r="U7" s="16" t="n">
-        <v>1353.36</v>
+        <v>1355.4</v>
       </c>
       <c r="V7" s="16" t="n">
-        <v>1353.36</v>
+        <v>1355.4</v>
       </c>
       <c r="W7" s="11" t="n"/>
     </row>
@@ -4390,38 +4510,38 @@
         <v>942.16</v>
       </c>
       <c r="K8" s="16" t="n">
-        <v>890.83</v>
+        <v>890.41</v>
       </c>
       <c r="L8" s="16" t="n">
-        <v>861.35</v>
+        <v>863.3099999999999</v>
       </c>
       <c r="M8" s="17" t="n">
-        <v>922.02</v>
+        <v>921.71</v>
       </c>
       <c r="N8" s="16" t="n">
-        <v>861.35</v>
+        <v>863.3099999999999</v>
       </c>
       <c r="O8" s="16" t="n">
-        <v>861.35</v>
+        <v>863.3099999999999</v>
       </c>
       <c r="P8" s="16" t="n">
-        <v>861.35</v>
+        <v>863.3099999999999</v>
       </c>
       <c r="Q8" s="16" t="n">
-        <v>861.35</v>
+        <v>863.3099999999999</v>
       </c>
       <c r="R8" s="11" t="n"/>
       <c r="S8" s="16" t="n">
-        <v>861.35</v>
+        <v>863.3099999999999</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>861.35</v>
+        <v>863.3099999999999</v>
       </c>
       <c r="U8" s="16" t="n">
-        <v>861.35</v>
+        <v>863.3099999999999</v>
       </c>
       <c r="V8" s="16" t="n">
-        <v>861.35</v>
+        <v>863.3099999999999</v>
       </c>
       <c r="W8" s="11" t="n"/>
     </row>
@@ -4455,38 +4575,38 @@
         <v>954.75</v>
       </c>
       <c r="K9" s="16" t="n">
-        <v>861.35</v>
+        <v>863.3099999999999</v>
       </c>
       <c r="L9" s="16" t="n">
-        <v>861.35</v>
+        <v>863.3099999999999</v>
       </c>
       <c r="M9" s="17" t="n">
-        <v>861.35</v>
+        <v>863.3099999999999</v>
       </c>
       <c r="N9" s="16" t="n">
-        <v>861.35</v>
+        <v>863.3099999999999</v>
       </c>
       <c r="O9" s="16" t="n">
-        <v>861.35</v>
+        <v>863.3099999999999</v>
       </c>
       <c r="P9" s="16" t="n">
-        <v>861.35</v>
+        <v>863.3099999999999</v>
       </c>
       <c r="Q9" s="16" t="n">
-        <v>861.35</v>
+        <v>863.3099999999999</v>
       </c>
       <c r="R9" s="11" t="n"/>
       <c r="S9" s="16" t="n">
-        <v>861.35</v>
+        <v>863.3099999999999</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>861.35</v>
+        <v>863.3099999999999</v>
       </c>
       <c r="U9" s="16" t="n">
-        <v>861.35</v>
+        <v>863.3099999999999</v>
       </c>
       <c r="V9" s="16" t="n">
-        <v>861.35</v>
+        <v>863.3099999999999</v>
       </c>
       <c r="W9" s="11" t="n"/>
     </row>
@@ -4520,38 +4640,38 @@
         <v>1746.09</v>
       </c>
       <c r="K10" s="16" t="n">
-        <v>1633.4</v>
+        <v>1631.97</v>
       </c>
       <c r="L10" s="16" t="n">
-        <v>1536.74</v>
+        <v>1539.06</v>
       </c>
       <c r="M10" s="17" t="n">
-        <v>1697.39</v>
+        <v>1696.56</v>
       </c>
       <c r="N10" s="16" t="n">
-        <v>1536.74</v>
+        <v>1539.06</v>
       </c>
       <c r="O10" s="16" t="n">
-        <v>1536.74</v>
+        <v>1539.06</v>
       </c>
       <c r="P10" s="16" t="n">
-        <v>1536.74</v>
+        <v>1539.06</v>
       </c>
       <c r="Q10" s="16" t="n">
-        <v>1536.74</v>
+        <v>1539.06</v>
       </c>
       <c r="R10" s="11" t="n"/>
       <c r="S10" s="16" t="n">
-        <v>1536.74</v>
+        <v>1539.06</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1536.74</v>
+        <v>1539.06</v>
       </c>
       <c r="U10" s="16" t="n">
-        <v>1536.74</v>
+        <v>1539.06</v>
       </c>
       <c r="V10" s="16" t="n">
-        <v>1536.74</v>
+        <v>1539.06</v>
       </c>
       <c r="W10" s="11" t="n"/>
     </row>
@@ -4585,38 +4705,38 @@
         <v>1767.09</v>
       </c>
       <c r="K11" s="16" t="n">
-        <v>1536.74</v>
+        <v>1539.06</v>
       </c>
       <c r="L11" s="16" t="n">
-        <v>1536.74</v>
+        <v>1539.06</v>
       </c>
       <c r="M11" s="17" t="n">
-        <v>1536.74</v>
+        <v>1539.06</v>
       </c>
       <c r="N11" s="16" t="n">
-        <v>1536.74</v>
+        <v>1539.06</v>
       </c>
       <c r="O11" s="16" t="n">
-        <v>1536.74</v>
+        <v>1539.06</v>
       </c>
       <c r="P11" s="16" t="n">
-        <v>1536.74</v>
+        <v>1539.06</v>
       </c>
       <c r="Q11" s="16" t="n">
-        <v>1536.74</v>
+        <v>1539.06</v>
       </c>
       <c r="R11" s="11" t="n"/>
       <c r="S11" s="16" t="n">
-        <v>1536.74</v>
+        <v>1539.06</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1536.74</v>
+        <v>1539.06</v>
       </c>
       <c r="U11" s="16" t="n">
-        <v>1536.74</v>
+        <v>1539.06</v>
       </c>
       <c r="V11" s="16" t="n">
-        <v>1536.74</v>
+        <v>1539.06</v>
       </c>
       <c r="W11" s="11" t="n"/>
     </row>
@@ -4650,38 +4770,38 @@
         <v>220.8</v>
       </c>
       <c r="K12" s="16" t="n">
-        <v>210.55</v>
+        <v>210.43</v>
       </c>
       <c r="L12" s="16" t="n">
-        <v>201.89</v>
+        <v>202.16</v>
       </c>
       <c r="M12" s="17" t="n">
-        <v>214.29</v>
+        <v>214.23</v>
       </c>
       <c r="N12" s="16" t="n">
-        <v>201.89</v>
+        <v>202.16</v>
       </c>
       <c r="O12" s="16" t="n">
-        <v>201.89</v>
+        <v>202.16</v>
       </c>
       <c r="P12" s="16" t="n">
-        <v>201.89</v>
+        <v>202.16</v>
       </c>
       <c r="Q12" s="16" t="n">
-        <v>201.89</v>
+        <v>202.16</v>
       </c>
       <c r="R12" s="11" t="n"/>
       <c r="S12" s="16" t="n">
-        <v>201.89</v>
+        <v>202.16</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>201.89</v>
+        <v>202.16</v>
       </c>
       <c r="U12" s="16" t="n">
-        <v>201.89</v>
+        <v>202.16</v>
       </c>
       <c r="V12" s="16" t="n">
-        <v>201.89</v>
+        <v>202.16</v>
       </c>
       <c r="W12" s="11" t="n"/>
     </row>
@@ -4715,38 +4835,38 @@
         <v>228.56</v>
       </c>
       <c r="K13" s="16" t="n">
-        <v>201.89</v>
+        <v>202.16</v>
       </c>
       <c r="L13" s="16" t="n">
-        <v>201.89</v>
+        <v>202.16</v>
       </c>
       <c r="M13" s="17" t="n">
-        <v>201.89</v>
+        <v>202.16</v>
       </c>
       <c r="N13" s="16" t="n">
-        <v>201.89</v>
+        <v>202.16</v>
       </c>
       <c r="O13" s="16" t="n">
-        <v>201.89</v>
+        <v>202.16</v>
       </c>
       <c r="P13" s="16" t="n">
-        <v>201.89</v>
+        <v>202.16</v>
       </c>
       <c r="Q13" s="16" t="n">
-        <v>201.89</v>
+        <v>202.16</v>
       </c>
       <c r="R13" s="11" t="n"/>
       <c r="S13" s="16" t="n">
-        <v>201.89</v>
+        <v>202.16</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>201.89</v>
+        <v>202.16</v>
       </c>
       <c r="U13" s="16" t="n">
-        <v>201.89</v>
+        <v>202.16</v>
       </c>
       <c r="V13" s="16" t="n">
-        <v>201.89</v>
+        <v>202.16</v>
       </c>
       <c r="W13" s="11" t="n"/>
     </row>
@@ -5235,7 +5355,7 @@
       <c r="H24" s="22" t="n"/>
       <c r="I24" s="21" t="n"/>
       <c r="J24" s="23">
-        <f>IFERROR(subQ!J36/subQ!E36-1,"")</f>
+        <f>IFERROR(subQ!J37/subQ!E37-1,"")</f>
         <v/>
       </c>
       <c r="K24" s="24" t="n">
@@ -5358,7 +5478,7 @@
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>drv:기타영업외손익</t>
+          <t>drv:이자손익</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -5368,7 +5488,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>기타영업외손익 (가정, 억원)</t>
+          <t>이자손익 (가정, 억원)</t>
         </is>
       </c>
       <c r="E26" s="26">
@@ -5396,42 +5516,42 @@
         <v/>
       </c>
       <c r="K26" s="29" t="n">
-        <v>0</v>
+        <v>0.41</v>
       </c>
       <c r="L26" s="29" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="M26" s="30">
         <f>subQ!M12</f>
         <v/>
       </c>
       <c r="N26" s="29" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="O26" s="29" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="P26" s="29" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="Q26" s="29" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="R26" s="30">
         <f>subQ!R12</f>
         <v/>
       </c>
       <c r="S26" s="29" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="T26" s="29" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="U26" s="29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="V26" s="29" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="W26" s="30">
         <f>subQ!W12</f>
@@ -5441,90 +5561,90 @@
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>drv:법인세비용</t>
+          <t>drv:기타영업외손익</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>ratio</t>
+          <t>abs</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>법인세율(/세전)</t>
-        </is>
-      </c>
-      <c r="E27" s="21">
-        <f>IFERROR(subQ!E14/subQ!E13,"")</f>
-        <v/>
-      </c>
-      <c r="F27" s="21">
-        <f>IFERROR(subQ!F14/subQ!F13,"")</f>
-        <v/>
-      </c>
-      <c r="G27" s="21">
-        <f>IFERROR(subQ!G14/subQ!G13,"")</f>
-        <v/>
-      </c>
-      <c r="H27" s="22">
-        <f>IFERROR(subQ!H14/subQ!H13,"")</f>
-        <v/>
-      </c>
-      <c r="I27" s="21">
-        <f>IFERROR(subQ!I14/subQ!I13,"")</f>
-        <v/>
-      </c>
-      <c r="J27" s="23">
-        <f>IFERROR(subQ!J14/subQ!J13,"")</f>
-        <v/>
-      </c>
-      <c r="K27" s="24" t="n">
-        <v>-0</v>
-      </c>
-      <c r="L27" s="24" t="n">
-        <v>-0</v>
-      </c>
-      <c r="M27" s="25">
-        <f>IFERROR(subQ!M14/subQ!M13,"")</f>
-        <v/>
-      </c>
-      <c r="N27" s="24" t="n">
-        <v>-0</v>
-      </c>
-      <c r="O27" s="24" t="n">
-        <v>-0</v>
-      </c>
-      <c r="P27" s="24" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Q27" s="24" t="n">
-        <v>-0</v>
-      </c>
-      <c r="R27" s="25">
-        <f>IFERROR(subQ!R14/subQ!R13,"")</f>
-        <v/>
-      </c>
-      <c r="S27" s="24" t="n">
-        <v>-0</v>
-      </c>
-      <c r="T27" s="24" t="n">
-        <v>-0</v>
-      </c>
-      <c r="U27" s="24" t="n">
-        <v>-0</v>
-      </c>
-      <c r="V27" s="24" t="n">
-        <v>-0</v>
-      </c>
-      <c r="W27" s="25">
-        <f>IFERROR(subQ!W14/subQ!W13,"")</f>
+          <t>기타영업외손익 (가정, 억원)</t>
+        </is>
+      </c>
+      <c r="E27" s="26">
+        <f>subQ!E13</f>
+        <v/>
+      </c>
+      <c r="F27" s="26">
+        <f>subQ!F13</f>
+        <v/>
+      </c>
+      <c r="G27" s="26">
+        <f>subQ!G13</f>
+        <v/>
+      </c>
+      <c r="H27" s="27">
+        <f>subQ!H13</f>
+        <v/>
+      </c>
+      <c r="I27" s="26">
+        <f>subQ!I13</f>
+        <v/>
+      </c>
+      <c r="J27" s="28">
+        <f>subQ!J13</f>
+        <v/>
+      </c>
+      <c r="K27" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="30">
+        <f>subQ!M13</f>
+        <v/>
+      </c>
+      <c r="N27" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" s="30">
+        <f>subQ!R13</f>
+        <v/>
+      </c>
+      <c r="S27" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" s="30">
+        <f>subQ!W13</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>drv:지배주주순이익</t>
+          <t>drv:법인세비용</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -5534,216 +5654,231 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>지배주주 비중(/당기순이익)</t>
+          <t>법인세율(/세전)</t>
         </is>
       </c>
       <c r="E28" s="21">
-        <f>IFERROR(subQ!E16/subQ!E15,"")</f>
+        <f>IFERROR(subQ!E15/subQ!E14,"")</f>
         <v/>
       </c>
       <c r="F28" s="21">
-        <f>IFERROR(subQ!F16/subQ!F15,"")</f>
+        <f>IFERROR(subQ!F15/subQ!F14,"")</f>
         <v/>
       </c>
       <c r="G28" s="21">
-        <f>IFERROR(subQ!G16/subQ!G15,"")</f>
+        <f>IFERROR(subQ!G15/subQ!G14,"")</f>
         <v/>
       </c>
       <c r="H28" s="22">
-        <f>IFERROR(subQ!H16/subQ!H15,"")</f>
+        <f>IFERROR(subQ!H15/subQ!H14,"")</f>
         <v/>
       </c>
       <c r="I28" s="21">
-        <f>IFERROR(subQ!I16/subQ!I15,"")</f>
+        <f>IFERROR(subQ!I15/subQ!I14,"")</f>
         <v/>
       </c>
       <c r="J28" s="23">
-        <f>IFERROR(subQ!J16/subQ!J15,"")</f>
+        <f>IFERROR(subQ!J15/subQ!J14,"")</f>
         <v/>
       </c>
       <c r="K28" s="24" t="n">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="L28" s="24" t="n">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="M28" s="25">
-        <f>IFERROR(subQ!M16/subQ!M15,"")</f>
+        <f>IFERROR(subQ!M15/subQ!M14,"")</f>
         <v/>
       </c>
       <c r="N28" s="24" t="n">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="O28" s="24" t="n">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="P28" s="24" t="n">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="Q28" s="24" t="n">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="R28" s="25">
-        <f>IFERROR(subQ!R16/subQ!R15,"")</f>
+        <f>IFERROR(subQ!R15/subQ!R14,"")</f>
         <v/>
       </c>
       <c r="S28" s="24" t="n">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="T28" s="24" t="n">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="U28" s="24" t="n">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="V28" s="24" t="n">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="W28" s="25">
-        <f>IFERROR(subQ!W16/subQ!W15,"")</f>
+        <f>IFERROR(subQ!W15/subQ!W14,"")</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>drv:부채총계</t>
+          <t>drv:지배주주순이익</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>qoq</t>
+          <t>ratio</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>부채총계 QoQ</t>
-        </is>
-      </c>
-      <c r="E29" s="21" t="n"/>
+          <t>지배주주 비중(/당기순이익)</t>
+        </is>
+      </c>
+      <c r="E29" s="21">
+        <f>IFERROR(subQ!E17/subQ!E16,"")</f>
+        <v/>
+      </c>
       <c r="F29" s="21">
-        <f>IFERROR(subQ!F18/subQ!E18-1,"")</f>
+        <f>IFERROR(subQ!F17/subQ!F16,"")</f>
         <v/>
       </c>
       <c r="G29" s="21">
-        <f>IFERROR(subQ!G18/subQ!F18-1,"")</f>
-        <v/>
-      </c>
-      <c r="H29" s="22" t="n"/>
+        <f>IFERROR(subQ!G17/subQ!G16,"")</f>
+        <v/>
+      </c>
+      <c r="H29" s="22">
+        <f>IFERROR(subQ!H17/subQ!H16,"")</f>
+        <v/>
+      </c>
       <c r="I29" s="21">
-        <f>IFERROR(subQ!I18/subQ!G18-1,"")</f>
+        <f>IFERROR(subQ!I17/subQ!I16,"")</f>
         <v/>
       </c>
       <c r="J29" s="23">
-        <f>IFERROR(subQ!J18/subQ!I18-1,"")</f>
+        <f>IFERROR(subQ!J17/subQ!J16,"")</f>
         <v/>
       </c>
       <c r="K29" s="24" t="n">
-        <v>-1e-05</v>
+        <v>1</v>
       </c>
       <c r="L29" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" s="25" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="M29" s="25">
+        <f>IFERROR(subQ!M17/subQ!M16,"")</f>
+        <v/>
+      </c>
       <c r="N29" s="24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O29" s="24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P29" s="24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q29" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" s="25" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="R29" s="25">
+        <f>IFERROR(subQ!R17/subQ!R16,"")</f>
+        <v/>
+      </c>
       <c r="S29" s="24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T29" s="24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U29" s="24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V29" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" s="25" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="W29" s="25">
+        <f>IFERROR(subQ!W17/subQ!W16,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>drv:자본총계</t>
+          <t>drv:부채총계</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>roll</t>
+          <t>qoq</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>자본총계 기타변동(배당 등, 억원)</t>
-        </is>
-      </c>
-      <c r="E30" s="26" t="n"/>
-      <c r="F30" s="26">
-        <f>IFERROR(subQ!E19+subQ!F15-subQ!F19,"")</f>
-        <v/>
-      </c>
-      <c r="G30" s="26">
-        <f>IFERROR(subQ!F19+subQ!G15-subQ!G19,"")</f>
-        <v/>
-      </c>
-      <c r="H30" s="27" t="n"/>
-      <c r="I30" s="26">
-        <f>IFERROR(subQ!G19+subQ!I15-subQ!I19,"")</f>
-        <v/>
-      </c>
-      <c r="J30" s="28">
-        <f>IFERROR(subQ!I19+subQ!J15-subQ!J19,"")</f>
-        <v/>
-      </c>
-      <c r="K30" s="29" t="n">
-        <v>0.0046</v>
-      </c>
-      <c r="L30" s="29" t="n">
-        <v>-0</v>
-      </c>
-      <c r="M30" s="30" t="n"/>
-      <c r="N30" s="29" t="n">
+          <t>부채총계 QoQ</t>
+        </is>
+      </c>
+      <c r="E30" s="21" t="n"/>
+      <c r="F30" s="21">
+        <f>IFERROR(subQ!F19/subQ!E19-1,"")</f>
+        <v/>
+      </c>
+      <c r="G30" s="21">
+        <f>IFERROR(subQ!G19/subQ!F19-1,"")</f>
+        <v/>
+      </c>
+      <c r="H30" s="22" t="n"/>
+      <c r="I30" s="21">
+        <f>IFERROR(subQ!I19/subQ!G19-1,"")</f>
+        <v/>
+      </c>
+      <c r="J30" s="23">
+        <f>IFERROR(subQ!J19/subQ!I19-1,"")</f>
+        <v/>
+      </c>
+      <c r="K30" s="24" t="n">
+        <v>-1e-05</v>
+      </c>
+      <c r="L30" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="O30" s="29" t="n">
+      <c r="M30" s="25" t="n"/>
+      <c r="N30" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="P30" s="29" t="n">
+      <c r="O30" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" s="29" t="n">
+      <c r="P30" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="R30" s="30" t="n"/>
-      <c r="S30" s="29" t="n">
+      <c r="Q30" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="T30" s="29" t="n">
+      <c r="R30" s="25" t="n"/>
+      <c r="S30" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="U30" s="29" t="n">
+      <c r="T30" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="V30" s="29" t="n">
+      <c r="U30" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="W30" s="30" t="n"/>
+      <c r="V30" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" s="25" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>drv:지배주주지분</t>
+          <t>drv:자본총계</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -5753,7 +5888,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>지배주주지분 기타변동(배당 등, 억원)</t>
+          <t>자본총계 기타변동(배당 등, 억원)</t>
         </is>
       </c>
       <c r="E31" s="26" t="n"/>
@@ -5811,75 +5946,75 @@
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>drv:총차입금</t>
+          <t>drv:지배주주지분</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>qoq</t>
+          <t>roll</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>총차입금 QoQ</t>
-        </is>
-      </c>
-      <c r="E32" s="21" t="n"/>
-      <c r="F32" s="21">
-        <f>IFERROR(subQ!F21/subQ!E21-1,"")</f>
-        <v/>
-      </c>
-      <c r="G32" s="21">
-        <f>IFERROR(subQ!G21/subQ!F21-1,"")</f>
-        <v/>
-      </c>
-      <c r="H32" s="22" t="n"/>
-      <c r="I32" s="21">
-        <f>IFERROR(subQ!I21/subQ!G21-1,"")</f>
-        <v/>
-      </c>
-      <c r="J32" s="23">
-        <f>IFERROR(subQ!J21/subQ!I21-1,"")</f>
-        <v/>
-      </c>
-      <c r="K32" s="24" t="n">
+          <t>지배주주지분 기타변동(배당 등, 억원)</t>
+        </is>
+      </c>
+      <c r="E32" s="26" t="n"/>
+      <c r="F32" s="26">
+        <f>IFERROR(subQ!E21+subQ!F17-subQ!F21,"")</f>
+        <v/>
+      </c>
+      <c r="G32" s="26">
+        <f>IFERROR(subQ!F21+subQ!G17-subQ!G21,"")</f>
+        <v/>
+      </c>
+      <c r="H32" s="27" t="n"/>
+      <c r="I32" s="26">
+        <f>IFERROR(subQ!G21+subQ!I17-subQ!I21,"")</f>
+        <v/>
+      </c>
+      <c r="J32" s="28">
+        <f>IFERROR(subQ!I21+subQ!J17-subQ!J21,"")</f>
+        <v/>
+      </c>
+      <c r="K32" s="29" t="n">
+        <v>0.0046</v>
+      </c>
+      <c r="L32" s="29" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M32" s="30" t="n"/>
+      <c r="N32" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="L32" s="24" t="n">
+      <c r="O32" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="M32" s="25" t="n"/>
-      <c r="N32" s="24" t="n">
+      <c r="P32" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="O32" s="24" t="n">
+      <c r="Q32" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="P32" s="24" t="n">
+      <c r="R32" s="30" t="n"/>
+      <c r="S32" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" s="24" t="n">
+      <c r="T32" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="R32" s="25" t="n"/>
-      <c r="S32" s="24" t="n">
+      <c r="U32" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="T32" s="24" t="n">
+      <c r="V32" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="U32" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" s="25" t="n"/>
+      <c r="W32" s="30" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>drv:순차입금</t>
+          <t>drv:총차입금</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -5889,7 +6024,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>순차입금 QoQ</t>
+          <t>총차입금 QoQ</t>
         </is>
       </c>
       <c r="E33" s="21" t="n"/>
@@ -5911,43 +6046,43 @@
         <v/>
       </c>
       <c r="K33" s="24" t="n">
-        <v>-0.858468</v>
+        <v>0</v>
       </c>
       <c r="L33" s="24" t="n">
-        <v>-17.097015</v>
+        <v>0</v>
       </c>
       <c r="M33" s="25" t="n"/>
       <c r="N33" s="24" t="n">
-        <v>0.355586</v>
+        <v>0</v>
       </c>
       <c r="O33" s="24" t="n">
-        <v>0.670999</v>
+        <v>0</v>
       </c>
       <c r="P33" s="24" t="n">
-        <v>0.170282</v>
+        <v>0</v>
       </c>
       <c r="Q33" s="24" t="n">
-        <v>0.404162</v>
+        <v>0</v>
       </c>
       <c r="R33" s="25" t="n"/>
       <c r="S33" s="24" t="n">
-        <v>0.09802</v>
+        <v>0</v>
       </c>
       <c r="T33" s="24" t="n">
-        <v>0.224932</v>
+        <v>0</v>
       </c>
       <c r="U33" s="24" t="n">
-        <v>0.07889599999999999</v>
+        <v>0</v>
       </c>
       <c r="V33" s="24" t="n">
-        <v>0.200069</v>
+        <v>0</v>
       </c>
       <c r="W33" s="25" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>drv:이자발생자산</t>
+          <t>drv:순차입금</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -5957,7 +6092,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>이자발생자산 QoQ</t>
+          <t>순차입금 QoQ</t>
         </is>
       </c>
       <c r="E34" s="21" t="n"/>
@@ -5979,43 +6114,43 @@
         <v/>
       </c>
       <c r="K34" s="24" t="n">
-        <v>-0.06721199999999999</v>
+        <v>-0.858468</v>
       </c>
       <c r="L34" s="24" t="n">
-        <v>-0.203265</v>
+        <v>-17.097015</v>
       </c>
       <c r="M34" s="25" t="n"/>
       <c r="N34" s="24" t="n">
-        <v>-0.085412</v>
+        <v>0.355586</v>
       </c>
       <c r="O34" s="24" t="n">
-        <v>-0.239011</v>
+        <v>0.670999</v>
       </c>
       <c r="P34" s="24" t="n">
-        <v>-0.13312</v>
+        <v>0.170282</v>
       </c>
       <c r="Q34" s="24" t="n">
-        <v>-0.426541</v>
+        <v>0.404162</v>
       </c>
       <c r="R34" s="25" t="n"/>
       <c r="S34" s="24" t="n">
-        <v>-0.253299</v>
+        <v>0.09802</v>
       </c>
       <c r="T34" s="24" t="n">
-        <v>-0.854741</v>
+        <v>0.224932</v>
       </c>
       <c r="U34" s="24" t="n">
-        <v>-2.52819</v>
+        <v>0.07889599999999999</v>
       </c>
       <c r="V34" s="24" t="n">
-        <v>4.524272</v>
+        <v>0.200069</v>
       </c>
       <c r="W34" s="25" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>drv:현금및현금성자산</t>
+          <t>drv:이자발생자산</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -6025,7 +6160,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>현금및현금성자산 QoQ</t>
+          <t>이자발생자산 QoQ</t>
         </is>
       </c>
       <c r="E35" s="21" t="n"/>
@@ -6046,43 +6181,72 @@
         <f>IFERROR(subQ!J24/subQ!I24-1,"")</f>
         <v/>
       </c>
-      <c r="K35" s="31" t="n"/>
-      <c r="L35" s="31" t="n"/>
+      <c r="K35" s="24" t="n">
+        <v>-0.06721199999999999</v>
+      </c>
+      <c r="L35" s="24" t="n">
+        <v>-0.203265</v>
+      </c>
       <c r="M35" s="25" t="n"/>
-      <c r="N35" s="31" t="n"/>
-      <c r="O35" s="31" t="n"/>
-      <c r="P35" s="31" t="n"/>
-      <c r="Q35" s="31" t="n"/>
+      <c r="N35" s="24" t="n">
+        <v>-0.085412</v>
+      </c>
+      <c r="O35" s="24" t="n">
+        <v>-0.239011</v>
+      </c>
+      <c r="P35" s="24" t="n">
+        <v>-0.13312</v>
+      </c>
+      <c r="Q35" s="24" t="n">
+        <v>-0.426541</v>
+      </c>
       <c r="R35" s="25" t="n"/>
-      <c r="S35" s="31" t="n"/>
-      <c r="T35" s="31" t="n"/>
-      <c r="U35" s="31" t="n"/>
-      <c r="V35" s="31" t="n"/>
+      <c r="S35" s="24" t="n">
+        <v>-0.253299</v>
+      </c>
+      <c r="T35" s="24" t="n">
+        <v>-0.854741</v>
+      </c>
+      <c r="U35" s="24" t="n">
+        <v>-2.52819</v>
+      </c>
+      <c r="V35" s="24" t="n">
+        <v>4.524272</v>
+      </c>
       <c r="W35" s="25" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>drv:CAPEX</t>
+          <t>drv:현금및현금성자산</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>yoy</t>
+          <t>qoq</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CAPEX YoY</t>
+          <t>현금및현금성자산 QoQ</t>
         </is>
       </c>
       <c r="E36" s="21" t="n"/>
-      <c r="F36" s="21" t="n"/>
-      <c r="G36" s="21" t="n"/>
+      <c r="F36" s="21">
+        <f>IFERROR(subQ!F25/subQ!E25-1,"")</f>
+        <v/>
+      </c>
+      <c r="G36" s="21">
+        <f>IFERROR(subQ!G25/subQ!F25-1,"")</f>
+        <v/>
+      </c>
       <c r="H36" s="22" t="n"/>
-      <c r="I36" s="21" t="n"/>
+      <c r="I36" s="21">
+        <f>IFERROR(subQ!I25/subQ!G25-1,"")</f>
+        <v/>
+      </c>
       <c r="J36" s="23">
-        <f>IFERROR(subQ!J25/subQ!E25-1,"")</f>
+        <f>IFERROR(subQ!J25/subQ!I25-1,"")</f>
         <v/>
       </c>
       <c r="K36" s="31" t="n"/>
@@ -6102,7 +6266,7 @@
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>drv:영업활동현금흐름</t>
+          <t>drv:CAPEX</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -6112,7 +6276,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>영업활동현금흐름 YoY</t>
+          <t>CAPEX YoY</t>
         </is>
       </c>
       <c r="E37" s="21" t="n"/>
@@ -6141,114 +6305,114 @@
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>drv:주식수</t>
+          <t>drv:영업활동현금흐름</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>qoq</t>
+          <t>yoy</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>주식수 QoQ</t>
+          <t>영업활동현금흐름 YoY</t>
         </is>
       </c>
       <c r="E38" s="21" t="n"/>
-      <c r="F38" s="21">
-        <f>IFERROR(subQ!F27/subQ!E27-1,"")</f>
-        <v/>
-      </c>
-      <c r="G38" s="21">
-        <f>IFERROR(subQ!G27/subQ!F27-1,"")</f>
-        <v/>
-      </c>
+      <c r="F38" s="21" t="n"/>
+      <c r="G38" s="21" t="n"/>
       <c r="H38" s="22" t="n"/>
-      <c r="I38" s="21">
-        <f>IFERROR(subQ!I27/subQ!G27-1,"")</f>
-        <v/>
-      </c>
+      <c r="I38" s="21" t="n"/>
       <c r="J38" s="23">
-        <f>IFERROR(subQ!J27/subQ!I27-1,"")</f>
-        <v/>
-      </c>
-      <c r="K38" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" s="24" t="n">
-        <v>0</v>
-      </c>
+        <f>IFERROR(subQ!J27/subQ!E27-1,"")</f>
+        <v/>
+      </c>
+      <c r="K38" s="31" t="n"/>
+      <c r="L38" s="31" t="n"/>
       <c r="M38" s="25" t="n"/>
-      <c r="N38" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" s="24" t="n">
-        <v>0</v>
-      </c>
+      <c r="N38" s="31" t="n"/>
+      <c r="O38" s="31" t="n"/>
+      <c r="P38" s="31" t="n"/>
+      <c r="Q38" s="31" t="n"/>
       <c r="R38" s="25" t="n"/>
-      <c r="S38" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" s="24" t="n">
-        <v>0</v>
-      </c>
+      <c r="S38" s="31" t="n"/>
+      <c r="T38" s="31" t="n"/>
+      <c r="U38" s="31" t="n"/>
+      <c r="V38" s="31" t="n"/>
       <c r="W38" s="25" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>drv:DPS</t>
+          <t>drv:주식수</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>yoy</t>
+          <t>qoq</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>DPS YoY</t>
+          <t>주식수 QoQ</t>
         </is>
       </c>
       <c r="E39" s="21" t="n"/>
-      <c r="F39" s="21" t="n"/>
-      <c r="G39" s="21" t="n"/>
+      <c r="F39" s="21">
+        <f>IFERROR(subQ!F28/subQ!E28-1,"")</f>
+        <v/>
+      </c>
+      <c r="G39" s="21">
+        <f>IFERROR(subQ!G28/subQ!F28-1,"")</f>
+        <v/>
+      </c>
       <c r="H39" s="22" t="n"/>
-      <c r="I39" s="21" t="n"/>
+      <c r="I39" s="21">
+        <f>IFERROR(subQ!I28/subQ!G28-1,"")</f>
+        <v/>
+      </c>
       <c r="J39" s="23">
-        <f>IFERROR(subQ!J30/subQ!E30-1,"")</f>
-        <v/>
-      </c>
-      <c r="K39" s="31" t="n"/>
-      <c r="L39" s="31" t="n"/>
+        <f>IFERROR(subQ!J28/subQ!I28-1,"")</f>
+        <v/>
+      </c>
+      <c r="K39" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="24" t="n">
+        <v>0</v>
+      </c>
       <c r="M39" s="25" t="n"/>
-      <c r="N39" s="31" t="n"/>
-      <c r="O39" s="31" t="n"/>
-      <c r="P39" s="31" t="n"/>
-      <c r="Q39" s="31" t="n"/>
+      <c r="N39" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="24" t="n">
+        <v>0</v>
+      </c>
       <c r="R39" s="25" t="n"/>
-      <c r="S39" s="31" t="n"/>
-      <c r="T39" s="31" t="n"/>
-      <c r="U39" s="31" t="n"/>
-      <c r="V39" s="31" t="n"/>
+      <c r="S39" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" s="24" t="n">
+        <v>0</v>
+      </c>
       <c r="W39" s="25" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>drv:PER</t>
+          <t>drv:DPS</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -6258,7 +6422,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>PER YoY</t>
+          <t>DPS YoY</t>
         </is>
       </c>
       <c r="E40" s="21" t="n"/>
@@ -6287,7 +6451,7 @@
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>drv:PBR</t>
+          <t>drv:PER</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -6297,7 +6461,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>PBR YoY</t>
+          <t>PER YoY</t>
         </is>
       </c>
       <c r="E41" s="21" t="n"/>
@@ -6309,229 +6473,246 @@
         <f>IFERROR(subQ!J32/subQ!E32-1,"")</f>
         <v/>
       </c>
-      <c r="K41" s="24" t="n">
-        <v>-0.672854</v>
-      </c>
-      <c r="L41" s="24" t="n">
-        <v>-0.580282</v>
-      </c>
+      <c r="K41" s="31" t="n"/>
+      <c r="L41" s="31" t="n"/>
       <c r="M41" s="25" t="n"/>
-      <c r="N41" s="24" t="n">
-        <v>-0.520635</v>
-      </c>
-      <c r="O41" s="24" t="n">
-        <v>-0.375494</v>
-      </c>
-      <c r="P41" s="24" t="n">
-        <v>0.141844</v>
-      </c>
-      <c r="Q41" s="24" t="n">
-        <v>0.147651</v>
-      </c>
+      <c r="N41" s="31" t="n"/>
+      <c r="O41" s="31" t="n"/>
+      <c r="P41" s="31" t="n"/>
+      <c r="Q41" s="31" t="n"/>
       <c r="R41" s="25" t="n"/>
-      <c r="S41" s="24" t="n">
-        <v>0.152318</v>
-      </c>
-      <c r="T41" s="24" t="n">
-        <v>0.164557</v>
-      </c>
-      <c r="U41" s="24" t="n">
-        <v>0.167702</v>
-      </c>
-      <c r="V41" s="24" t="n">
-        <v>0.181287</v>
-      </c>
+      <c r="S41" s="31" t="n"/>
+      <c r="T41" s="31" t="n"/>
+      <c r="U41" s="31" t="n"/>
+      <c r="V41" s="31" t="n"/>
       <c r="W41" s="25" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>drv:매출전사</t>
+          <t>drv:PBR</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>ratio</t>
+          <t>yoy</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>매출전사 비중(/매출액)</t>
-        </is>
-      </c>
-      <c r="E42" s="21">
-        <f>IFERROR(subQ!E33/subQ!E5,"")</f>
-        <v/>
-      </c>
-      <c r="F42" s="21">
-        <f>IFERROR(subQ!F33/subQ!F5,"")</f>
-        <v/>
-      </c>
-      <c r="G42" s="21">
-        <f>IFERROR(subQ!G33/subQ!G5,"")</f>
-        <v/>
-      </c>
-      <c r="H42" s="22">
-        <f>IFERROR(subQ!H33/subQ!H5,"")</f>
-        <v/>
-      </c>
-      <c r="I42" s="21">
-        <f>IFERROR(subQ!I33/subQ!I5,"")</f>
-        <v/>
-      </c>
+          <t>PBR YoY</t>
+        </is>
+      </c>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="22" t="n"/>
+      <c r="I42" s="21" t="n"/>
       <c r="J42" s="23">
-        <f>IFERROR(subQ!J33/subQ!J5,"")</f>
+        <f>IFERROR(subQ!J33/subQ!E33-1,"")</f>
         <v/>
       </c>
       <c r="K42" s="24" t="n">
-        <v>1</v>
+        <v>-0.672854</v>
       </c>
       <c r="L42" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="M42" s="25">
-        <f>IFERROR(subQ!M33/subQ!M5,"")</f>
-        <v/>
-      </c>
+        <v>-0.580282</v>
+      </c>
+      <c r="M42" s="25" t="n"/>
       <c r="N42" s="24" t="n">
-        <v>1</v>
+        <v>-0.520635</v>
       </c>
       <c r="O42" s="24" t="n">
-        <v>1</v>
+        <v>-0.375494</v>
       </c>
       <c r="P42" s="24" t="n">
-        <v>1</v>
+        <v>0.141844</v>
       </c>
       <c r="Q42" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="R42" s="25">
-        <f>IFERROR(subQ!R33/subQ!R5,"")</f>
-        <v/>
-      </c>
+        <v>0.147651</v>
+      </c>
+      <c r="R42" s="25" t="n"/>
       <c r="S42" s="24" t="n">
-        <v>1</v>
+        <v>0.152318</v>
       </c>
       <c r="T42" s="24" t="n">
-        <v>1</v>
+        <v>0.164557</v>
       </c>
       <c r="U42" s="24" t="n">
-        <v>1</v>
+        <v>0.167702</v>
       </c>
       <c r="V42" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="W42" s="25">
-        <f>IFERROR(subQ!W33/subQ!W5,"")</f>
-        <v/>
-      </c>
+        <v>0.181287</v>
+      </c>
+      <c r="W42" s="25" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
         <is>
+          <t>drv:매출전사</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>매출전사 비중(/매출액)</t>
+        </is>
+      </c>
+      <c r="E43" s="21">
+        <f>IFERROR(subQ!E34/subQ!E5,"")</f>
+        <v/>
+      </c>
+      <c r="F43" s="21">
+        <f>IFERROR(subQ!F34/subQ!F5,"")</f>
+        <v/>
+      </c>
+      <c r="G43" s="21">
+        <f>IFERROR(subQ!G34/subQ!G5,"")</f>
+        <v/>
+      </c>
+      <c r="H43" s="22">
+        <f>IFERROR(subQ!H34/subQ!H5,"")</f>
+        <v/>
+      </c>
+      <c r="I43" s="21">
+        <f>IFERROR(subQ!I34/subQ!I5,"")</f>
+        <v/>
+      </c>
+      <c r="J43" s="23">
+        <f>IFERROR(subQ!J34/subQ!J5,"")</f>
+        <v/>
+      </c>
+      <c r="K43" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L43" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M43" s="25">
+        <f>IFERROR(subQ!M34/subQ!M5,"")</f>
+        <v/>
+      </c>
+      <c r="N43" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O43" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="P43" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q43" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="R43" s="25">
+        <f>IFERROR(subQ!R34/subQ!R5,"")</f>
+        <v/>
+      </c>
+      <c r="S43" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T43" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="V43" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="W43" s="25">
+        <f>IFERROR(subQ!W34/subQ!W5,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
           <t>drv:OP전사</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>ratio</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>OP전사 마진(/매출전사)</t>
         </is>
       </c>
-      <c r="E43" s="21">
-        <f>IFERROR(subQ!E34/subQ!E33,"")</f>
-        <v/>
-      </c>
-      <c r="F43" s="21">
-        <f>IFERROR(subQ!F34/subQ!F33,"")</f>
-        <v/>
-      </c>
-      <c r="G43" s="21">
-        <f>IFERROR(subQ!G34/subQ!G33,"")</f>
-        <v/>
-      </c>
-      <c r="H43" s="22">
-        <f>IFERROR(subQ!H34/subQ!H33,"")</f>
-        <v/>
-      </c>
-      <c r="I43" s="21">
-        <f>IFERROR(subQ!I34/subQ!I33,"")</f>
-        <v/>
-      </c>
-      <c r="J43" s="23">
-        <f>IFERROR(subQ!J34/subQ!J33,"")</f>
-        <v/>
-      </c>
-      <c r="K43" s="24" t="n">
+      <c r="E44" s="21">
+        <f>IFERROR(subQ!E35/subQ!E34,"")</f>
+        <v/>
+      </c>
+      <c r="F44" s="21">
+        <f>IFERROR(subQ!F35/subQ!F34,"")</f>
+        <v/>
+      </c>
+      <c r="G44" s="21">
+        <f>IFERROR(subQ!G35/subQ!G34,"")</f>
+        <v/>
+      </c>
+      <c r="H44" s="22">
+        <f>IFERROR(subQ!H35/subQ!H34,"")</f>
+        <v/>
+      </c>
+      <c r="I44" s="21">
+        <f>IFERROR(subQ!I35/subQ!I34,"")</f>
+        <v/>
+      </c>
+      <c r="J44" s="23">
+        <f>IFERROR(subQ!J35/subQ!J34,"")</f>
+        <v/>
+      </c>
+      <c r="K44" s="24" t="n">
         <v>-0.199953</v>
       </c>
-      <c r="L43" s="24" t="n">
+      <c r="L44" s="24" t="n">
         <v>-0.2</v>
       </c>
-      <c r="M43" s="25">
-        <f>IFERROR(subQ!M34/subQ!M33,"")</f>
-        <v/>
-      </c>
-      <c r="N43" s="24" t="n">
+      <c r="M44" s="25">
+        <f>IFERROR(subQ!M35/subQ!M34,"")</f>
+        <v/>
+      </c>
+      <c r="N44" s="24" t="n">
         <v>-0.2001</v>
       </c>
-      <c r="O43" s="24" t="n">
+      <c r="O44" s="24" t="n">
         <v>-0.19996</v>
       </c>
-      <c r="P43" s="24" t="n">
+      <c r="P44" s="24" t="n">
         <v>-0.199953</v>
       </c>
-      <c r="Q43" s="24" t="n">
+      <c r="Q44" s="24" t="n">
         <v>-0.2</v>
       </c>
-      <c r="R43" s="25">
-        <f>IFERROR(subQ!R34/subQ!R33,"")</f>
-        <v/>
-      </c>
-      <c r="S43" s="24" t="n">
+      <c r="R44" s="25">
+        <f>IFERROR(subQ!R35/subQ!R34,"")</f>
+        <v/>
+      </c>
+      <c r="S44" s="24" t="n">
         <v>-0.2001</v>
       </c>
-      <c r="T43" s="24" t="n">
+      <c r="T44" s="24" t="n">
         <v>-0.19996</v>
       </c>
-      <c r="U43" s="24" t="n">
+      <c r="U44" s="24" t="n">
         <v>-0.199953</v>
       </c>
-      <c r="V43" s="24" t="n">
+      <c r="V44" s="24" t="n">
         <v>-0.2</v>
       </c>
-      <c r="W43" s="25">
-        <f>IFERROR(subQ!W34/subQ!W33,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="H44" s="9" t="n"/>
-      <c r="J44" s="5" t="n"/>
-      <c r="K44" s="10" t="n"/>
-      <c r="L44" s="10" t="n"/>
-      <c r="M44" s="11" t="n"/>
-      <c r="N44" s="10" t="n"/>
-      <c r="O44" s="10" t="n"/>
-      <c r="P44" s="10" t="n"/>
-      <c r="Q44" s="10" t="n"/>
-      <c r="R44" s="11" t="n"/>
-      <c r="S44" s="10" t="n"/>
-      <c r="T44" s="10" t="n"/>
-      <c r="U44" s="10" t="n"/>
-      <c r="V44" s="10" t="n"/>
-      <c r="W44" s="11" t="n"/>
+      <c r="W44" s="25">
+        <f>IFERROR(subQ!W35/subQ!W34,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>3. 밸류에이션·스칼라</t>
-        </is>
-      </c>
       <c r="H45" s="9" t="n"/>
       <c r="J45" s="5" t="n"/>
       <c r="K45" s="10" t="n"/>
@@ -6549,22 +6730,9 @@
       <c r="W45" s="11" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="12" t="inlineStr">
-        <is>
-          <t>sc:종가</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>종가</t>
-        </is>
-      </c>
-      <c r="D46" s="32" t="n">
-        <v>8080</v>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>원 — aikstockdata(금융위 T+1)</t>
+      <c r="B46" s="1" t="inlineStr">
+        <is>
+          <t>3. 밸류에이션·스칼라</t>
         </is>
       </c>
       <c r="H46" s="9" t="n"/>
@@ -6586,22 +6754,20 @@
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t>sc:기준일</t>
+          <t>sc:종가</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>기준일</t>
-        </is>
-      </c>
-      <c r="D47" s="33" t="inlineStr">
-        <is>
-          <t>20260929</t>
-        </is>
+          <t>종가</t>
+        </is>
+      </c>
+      <c r="D47" s="32" t="n">
+        <v>8080</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>종가 기준일</t>
+          <t>원 — aikstockdata(금융위 T+1)</t>
         </is>
       </c>
       <c r="H47" s="9" t="n"/>
@@ -6623,20 +6789,22 @@
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>sc:COE</t>
+          <t>sc:기준일</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>COE</t>
-        </is>
-      </c>
-      <c r="D48" s="24" t="n">
-        <v>0.09</v>
+          <t>기준일</t>
+        </is>
+      </c>
+      <c r="D48" s="33" t="inlineStr">
+        <is>
+          <t>20260929</t>
+        </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>자기자본비용(가정)</t>
+          <t>종가 기준일</t>
         </is>
       </c>
       <c r="H48" s="9" t="n"/>
@@ -6658,20 +6826,20 @@
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>sc:PER_lo</t>
+          <t>sc:COE</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>PER_lo</t>
-        </is>
-      </c>
-      <c r="D49" s="29" t="n">
-        <v>10</v>
+          <t>COE</t>
+        </is>
+      </c>
+      <c r="D49" s="24" t="n">
+        <v>0.09</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>PER 밴드 하단(배) — sector_default(레퍼런스 TP_PE PB 예시 10/15/20배; 과거 양(+)EPS 분기 1개 &lt; 4)</t>
+          <t>자기자본비용(가정)</t>
         </is>
       </c>
       <c r="H49" s="9" t="n"/>
@@ -6693,20 +6861,20 @@
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t>sc:PER_mid</t>
+          <t>sc:PER_lo</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>PER_mid</t>
+          <t>PER_lo</t>
         </is>
       </c>
       <c r="D50" s="29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>PER 밴드 중단(배)</t>
+          <t>PER 밴드 하단(배) — sector_default(레퍼런스 TP_PE PB 예시 10/15/20배; 과거 양(+)EPS 분기 1개 &lt; 4)</t>
         </is>
       </c>
       <c r="H50" s="9" t="n"/>
@@ -6728,20 +6896,20 @@
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>sc:PER_hi</t>
+          <t>sc:PER_mid</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>PER_hi</t>
+          <t>PER_mid</t>
         </is>
       </c>
       <c r="D51" s="29" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>PER 밴드 상단(배)</t>
+          <t>PER 밴드 중단(배)</t>
         </is>
       </c>
       <c r="H51" s="9" t="n"/>
@@ -6763,20 +6931,20 @@
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t>sc:EPS_Y1가중</t>
+          <t>sc:PER_hi</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>EPS_Y1가중</t>
-        </is>
-      </c>
-      <c r="D52" s="24" t="n">
-        <v>0.5</v>
+          <t>PER_hi</t>
+        </is>
+      </c>
+      <c r="D52" s="29" t="n">
+        <v>20</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>12M fwd EPS = FY(last_actual연도)E × w + FY+1E × (1−w) — 기준 분기 2Q 이면 0.5(가정)</t>
+          <t>PER 밴드 상단(배)</t>
         </is>
       </c>
       <c r="H52" s="9" t="n"/>
@@ -6798,20 +6966,20 @@
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t>sc:세율</t>
+          <t>sc:EPS_Y1가중</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>세율</t>
+          <t>EPS_Y1가중</t>
         </is>
       </c>
       <c r="D53" s="24" t="n">
-        <v>0.22</v>
+        <v>0.5</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>법인세율 가정(참고 — 추정 수식은 드라이버 행 참조)</t>
+          <t>12M fwd EPS = FY(last_actual연도)E × w + FY+1E × (1−w) — 기준 분기 2Q 이면 0.5(가정)</t>
         </is>
       </c>
       <c r="H53" s="9" t="n"/>
@@ -6833,20 +7001,20 @@
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
         <is>
-          <t>sc:판관비율</t>
+          <t>sc:세율</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>판관비율</t>
+          <t>세율</t>
         </is>
       </c>
       <c r="D54" s="24" t="n">
-        <v>0.2281</v>
+        <v>0.22</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>판관비율 가정(참고)</t>
+          <t>법인세율 가정(참고 — 추정 수식은 드라이버 행 참조)</t>
         </is>
       </c>
       <c r="H54" s="9" t="n"/>
@@ -6868,18 +7036,20 @@
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t>sc:배당성향</t>
+          <t>sc:판관비율</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>배당성향</t>
-        </is>
-      </c>
-      <c r="D55" s="24" t="n"/>
+          <t>판관비율</t>
+        </is>
+      </c>
+      <c r="D55" s="24" t="n">
+        <v>0.2281</v>
+      </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>배당성향 가정(참고)</t>
+          <t>판관비율 가정(참고)</t>
         </is>
       </c>
       <c r="H55" s="9" t="n"/>
@@ -6901,18 +7071,18 @@
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
         <is>
-          <t>sc:외화순노출_백만$</t>
+          <t>sc:배당성향</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>외화순노출_백만$</t>
-        </is>
-      </c>
-      <c r="D56" s="29" t="n"/>
+          <t>배당성향</t>
+        </is>
+      </c>
+      <c r="D56" s="24" t="n"/>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>외화 순노출 × Δ기말환율 (외화 시트 방식)</t>
+          <t>배당성향 가정(참고)</t>
         </is>
       </c>
       <c r="H56" s="9" t="n"/>
@@ -6930,6 +7100,39 @@
       <c r="U56" s="10" t="n"/>
       <c r="V56" s="10" t="n"/>
       <c r="W56" s="11" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="12" t="inlineStr">
+        <is>
+          <t>sc:외화순노출_백만$</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>외화순노출_백만$</t>
+        </is>
+      </c>
+      <c r="D57" s="29" t="n"/>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>외화 순노출 × Δ기말환율 (외화 시트 방식)</t>
+        </is>
+      </c>
+      <c r="H57" s="9" t="n"/>
+      <c r="J57" s="5" t="n"/>
+      <c r="K57" s="10" t="n"/>
+      <c r="L57" s="10" t="n"/>
+      <c r="M57" s="11" t="n"/>
+      <c r="N57" s="10" t="n"/>
+      <c r="O57" s="10" t="n"/>
+      <c r="P57" s="10" t="n"/>
+      <c r="Q57" s="10" t="n"/>
+      <c r="R57" s="11" t="n"/>
+      <c r="S57" s="10" t="n"/>
+      <c r="T57" s="10" t="n"/>
+      <c r="U57" s="10" t="n"/>
+      <c r="V57" s="10" t="n"/>
+      <c r="W57" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10471,7 +10674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W39"/>
+  <dimension ref="A1:W40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -11425,7 +11628,7 @@
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>기타영업외손익</t>
+          <t>이자손익</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -11440,30 +11643,15 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>기타영업외손익</t>
-        </is>
-      </c>
-      <c r="E12" s="18">
-        <f>IFERROR(VLOOKUP($D12,BS별도,MATCH(E$1,BS별도H,0),0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="F12" s="18">
-        <f>IFERROR(VLOOKUP($D12,BS별도,MATCH(F$1,BS별도H,0),0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="G12" s="18">
-        <f>IFERROR(VLOOKUP($D12,BS별도,MATCH(G$1,BS별도H,0),0)/100,"")</f>
-        <v/>
-      </c>
+          <t>이자손익</t>
+        </is>
+      </c>
+      <c r="E12" s="18" t="n"/>
+      <c r="F12" s="18" t="n"/>
+      <c r="G12" s="18" t="n"/>
       <c r="H12" s="34" t="n"/>
-      <c r="I12" s="18">
-        <f>IFERROR(VLOOKUP($D12,BS별도,MATCH(I$1,BS별도H,0),0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="J12" s="19">
-        <f>IFERROR(VLOOKUP($D12,BS별도,MATCH(J$1,BS별도H,0),0)/100,"")</f>
-        <v/>
-      </c>
+      <c r="I12" s="18" t="n"/>
+      <c r="J12" s="19" t="n"/>
       <c r="K12" s="20">
         <f>변수!K26</f>
         <v/>
@@ -11520,7 +11708,7 @@
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>세전이익</t>
+          <t>기타영업외손익</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -11535,7 +11723,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>법인세비용차감전계속사업이익</t>
+          <t>기타영업외손익</t>
         </is>
       </c>
       <c r="E13" s="18">
@@ -11560,11 +11748,11 @@
         <v/>
       </c>
       <c r="K13" s="20">
-        <f>IFERROR(K9+K11+K12,"")</f>
+        <f>변수!K27</f>
         <v/>
       </c>
       <c r="L13" s="20">
-        <f>IFERROR(L9+L11+L12,"")</f>
+        <f>변수!L27</f>
         <v/>
       </c>
       <c r="M13" s="35">
@@ -11572,19 +11760,19 @@
         <v/>
       </c>
       <c r="N13" s="20">
-        <f>IFERROR(N9+N11+N12,"")</f>
+        <f>변수!N27</f>
         <v/>
       </c>
       <c r="O13" s="20">
-        <f>IFERROR(O9+O11+O12,"")</f>
+        <f>변수!O27</f>
         <v/>
       </c>
       <c r="P13" s="20">
-        <f>IFERROR(P9+P11+P12,"")</f>
+        <f>변수!P27</f>
         <v/>
       </c>
       <c r="Q13" s="20">
-        <f>IFERROR(Q9+Q11+Q12,"")</f>
+        <f>변수!Q27</f>
         <v/>
       </c>
       <c r="R13" s="35">
@@ -11592,19 +11780,19 @@
         <v/>
       </c>
       <c r="S13" s="20">
-        <f>IFERROR(S9+S11+S12,"")</f>
+        <f>변수!S27</f>
         <v/>
       </c>
       <c r="T13" s="20">
-        <f>IFERROR(T9+T11+T12,"")</f>
+        <f>변수!T27</f>
         <v/>
       </c>
       <c r="U13" s="20">
-        <f>IFERROR(U9+U11+U12,"")</f>
+        <f>변수!U27</f>
         <v/>
       </c>
       <c r="V13" s="20">
-        <f>IFERROR(V9+V11+V12,"")</f>
+        <f>변수!V27</f>
         <v/>
       </c>
       <c r="W13" s="35">
@@ -11615,7 +11803,7 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>법인세비용</t>
+          <t>세전이익</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -11630,30 +11818,36 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>법인세비용</t>
+          <t>법인세비용차감전계속사업이익</t>
         </is>
       </c>
       <c r="E14" s="18">
         <f>IFERROR(VLOOKUP($D14,BS별도,MATCH(E$1,BS별도H,0),0)/100,"")</f>
         <v/>
       </c>
-      <c r="F14" s="18" t="n"/>
+      <c r="F14" s="18">
+        <f>IFERROR(VLOOKUP($D14,BS별도,MATCH(F$1,BS별도H,0),0)/100,"")</f>
+        <v/>
+      </c>
       <c r="G14" s="18">
         <f>IFERROR(VLOOKUP($D14,BS별도,MATCH(G$1,BS별도H,0),0)/100,"")</f>
         <v/>
       </c>
       <c r="H14" s="34" t="n"/>
-      <c r="I14" s="18" t="n"/>
+      <c r="I14" s="18">
+        <f>IFERROR(VLOOKUP($D14,BS별도,MATCH(I$1,BS별도H,0),0)/100,"")</f>
+        <v/>
+      </c>
       <c r="J14" s="19">
         <f>IFERROR(VLOOKUP($D14,BS별도,MATCH(J$1,BS별도H,0),0)/100,"")</f>
         <v/>
       </c>
       <c r="K14" s="20">
-        <f>IFERROR(K13*변수!K27,"")</f>
+        <f>IFERROR(K9+K11+K13,"")</f>
         <v/>
       </c>
       <c r="L14" s="20">
-        <f>IFERROR(L13*변수!L27,"")</f>
+        <f>IFERROR(L9+L11+L13,"")</f>
         <v/>
       </c>
       <c r="M14" s="35">
@@ -11661,19 +11855,19 @@
         <v/>
       </c>
       <c r="N14" s="20">
-        <f>IFERROR(N13*변수!N27,"")</f>
+        <f>IFERROR(N9+N11+N13,"")</f>
         <v/>
       </c>
       <c r="O14" s="20">
-        <f>IFERROR(O13*변수!O27,"")</f>
+        <f>IFERROR(O9+O11+O13,"")</f>
         <v/>
       </c>
       <c r="P14" s="20">
-        <f>IFERROR(P13*변수!P27,"")</f>
+        <f>IFERROR(P9+P11+P13,"")</f>
         <v/>
       </c>
       <c r="Q14" s="20">
-        <f>IFERROR(Q13*변수!Q27,"")</f>
+        <f>IFERROR(Q9+Q11+Q13,"")</f>
         <v/>
       </c>
       <c r="R14" s="35">
@@ -11681,19 +11875,19 @@
         <v/>
       </c>
       <c r="S14" s="20">
-        <f>IFERROR(S13*변수!S27,"")</f>
+        <f>IFERROR(S9+S11+S13,"")</f>
         <v/>
       </c>
       <c r="T14" s="20">
-        <f>IFERROR(T13*변수!T27,"")</f>
+        <f>IFERROR(T9+T11+T13,"")</f>
         <v/>
       </c>
       <c r="U14" s="20">
-        <f>IFERROR(U13*변수!U27,"")</f>
+        <f>IFERROR(U9+U11+U13,"")</f>
         <v/>
       </c>
       <c r="V14" s="20">
-        <f>IFERROR(V13*변수!V27,"")</f>
+        <f>IFERROR(V9+V11+V13,"")</f>
         <v/>
       </c>
       <c r="W14" s="35">
@@ -11704,7 +11898,7 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>당기순이익</t>
+          <t>법인세비용</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -11719,36 +11913,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>당기순이익</t>
+          <t>법인세비용</t>
         </is>
       </c>
       <c r="E15" s="18">
         <f>IFERROR(VLOOKUP($D15,BS별도,MATCH(E$1,BS별도H,0),0)/100,"")</f>
         <v/>
       </c>
-      <c r="F15" s="18">
-        <f>IFERROR(VLOOKUP($D15,BS별도,MATCH(F$1,BS별도H,0),0)/100,"")</f>
-        <v/>
-      </c>
+      <c r="F15" s="18" t="n"/>
       <c r="G15" s="18">
         <f>IFERROR(VLOOKUP($D15,BS별도,MATCH(G$1,BS별도H,0),0)/100,"")</f>
         <v/>
       </c>
       <c r="H15" s="34" t="n"/>
-      <c r="I15" s="18">
-        <f>IFERROR(VLOOKUP($D15,BS별도,MATCH(I$1,BS별도H,0),0)/100,"")</f>
-        <v/>
-      </c>
+      <c r="I15" s="18" t="n"/>
       <c r="J15" s="19">
         <f>IFERROR(VLOOKUP($D15,BS별도,MATCH(J$1,BS별도H,0),0)/100,"")</f>
         <v/>
       </c>
       <c r="K15" s="20">
-        <f>IFERROR(K13-K14,"")</f>
+        <f>IFERROR(K14*변수!K28,"")</f>
         <v/>
       </c>
       <c r="L15" s="20">
-        <f>IFERROR(L13-L14,"")</f>
+        <f>IFERROR(L14*변수!L28,"")</f>
         <v/>
       </c>
       <c r="M15" s="35">
@@ -11756,19 +11944,19 @@
         <v/>
       </c>
       <c r="N15" s="20">
-        <f>IFERROR(N13-N14,"")</f>
+        <f>IFERROR(N14*변수!N28,"")</f>
         <v/>
       </c>
       <c r="O15" s="20">
-        <f>IFERROR(O13-O14,"")</f>
+        <f>IFERROR(O14*변수!O28,"")</f>
         <v/>
       </c>
       <c r="P15" s="20">
-        <f>IFERROR(P13-P14,"")</f>
+        <f>IFERROR(P14*변수!P28,"")</f>
         <v/>
       </c>
       <c r="Q15" s="20">
-        <f>IFERROR(Q13-Q14,"")</f>
+        <f>IFERROR(Q14*변수!Q28,"")</f>
         <v/>
       </c>
       <c r="R15" s="35">
@@ -11776,19 +11964,19 @@
         <v/>
       </c>
       <c r="S15" s="20">
-        <f>IFERROR(S13-S14,"")</f>
+        <f>IFERROR(S14*변수!S28,"")</f>
         <v/>
       </c>
       <c r="T15" s="20">
-        <f>IFERROR(T13-T14,"")</f>
+        <f>IFERROR(T14*변수!T28,"")</f>
         <v/>
       </c>
       <c r="U15" s="20">
-        <f>IFERROR(U13-U14,"")</f>
+        <f>IFERROR(U14*변수!U28,"")</f>
         <v/>
       </c>
       <c r="V15" s="20">
-        <f>IFERROR(V13-V14,"")</f>
+        <f>IFERROR(V14*변수!V28,"")</f>
         <v/>
       </c>
       <c r="W15" s="35">
@@ -11799,7 +11987,7 @@
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>지배주주순이익</t>
+          <t>당기순이익</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -11814,7 +12002,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>(지배주주지분)당기순이익</t>
+          <t>당기순이익</t>
         </is>
       </c>
       <c r="E16" s="18">
@@ -11839,11 +12027,11 @@
         <v/>
       </c>
       <c r="K16" s="20">
-        <f>IFERROR(K15*변수!K28,"")</f>
+        <f>IFERROR(K14-K15,"")</f>
         <v/>
       </c>
       <c r="L16" s="20">
-        <f>IFERROR(L15*변수!L28,"")</f>
+        <f>IFERROR(L14-L15,"")</f>
         <v/>
       </c>
       <c r="M16" s="35">
@@ -11851,19 +12039,19 @@
         <v/>
       </c>
       <c r="N16" s="20">
-        <f>IFERROR(N15*변수!N28,"")</f>
+        <f>IFERROR(N14-N15,"")</f>
         <v/>
       </c>
       <c r="O16" s="20">
-        <f>IFERROR(O15*변수!O28,"")</f>
+        <f>IFERROR(O14-O15,"")</f>
         <v/>
       </c>
       <c r="P16" s="20">
-        <f>IFERROR(P15*변수!P28,"")</f>
+        <f>IFERROR(P14-P15,"")</f>
         <v/>
       </c>
       <c r="Q16" s="20">
-        <f>IFERROR(Q15*변수!Q28,"")</f>
+        <f>IFERROR(Q14-Q15,"")</f>
         <v/>
       </c>
       <c r="R16" s="35">
@@ -11871,19 +12059,19 @@
         <v/>
       </c>
       <c r="S16" s="20">
-        <f>IFERROR(S15*변수!S28,"")</f>
+        <f>IFERROR(S14-S15,"")</f>
         <v/>
       </c>
       <c r="T16" s="20">
-        <f>IFERROR(T15*변수!T28,"")</f>
+        <f>IFERROR(T14-T15,"")</f>
         <v/>
       </c>
       <c r="U16" s="20">
-        <f>IFERROR(U15*변수!U28,"")</f>
+        <f>IFERROR(U14-U15,"")</f>
         <v/>
       </c>
       <c r="V16" s="20">
-        <f>IFERROR(V15*변수!V28,"")</f>
+        <f>IFERROR(V14-V15,"")</f>
         <v/>
       </c>
       <c r="W16" s="35">
@@ -11894,12 +12082,12 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>자산총계</t>
+          <t>지배주주순이익</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>재무상태</t>
+          <t>손익</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -11909,7 +12097,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>자산총계</t>
+          <t>(지배주주지분)당기순이익</t>
         </is>
       </c>
       <c r="E17" s="18">
@@ -11924,9 +12112,7 @@
         <f>IFERROR(VLOOKUP($D17,BS별도,MATCH(G$1,BS별도H,0),0)/100,"")</f>
         <v/>
       </c>
-      <c r="H17" s="34" t="n">
-        <v>648.01</v>
-      </c>
+      <c r="H17" s="34" t="n"/>
       <c r="I17" s="18">
         <f>IFERROR(VLOOKUP($D17,BS별도,MATCH(I$1,BS별도H,0),0)/100,"")</f>
         <v/>
@@ -11936,62 +12122,62 @@
         <v/>
       </c>
       <c r="K17" s="20">
-        <f>IFERROR(K18+K19,"")</f>
+        <f>IFERROR(K16*변수!K29,"")</f>
         <v/>
       </c>
       <c r="L17" s="20">
-        <f>IFERROR(L18+L19,"")</f>
+        <f>IFERROR(L16*변수!L29,"")</f>
         <v/>
       </c>
       <c r="M17" s="35">
-        <f>L17</f>
+        <f>SUM(I17:L17)</f>
         <v/>
       </c>
       <c r="N17" s="20">
-        <f>IFERROR(N18+N19,"")</f>
+        <f>IFERROR(N16*변수!N29,"")</f>
         <v/>
       </c>
       <c r="O17" s="20">
-        <f>IFERROR(O18+O19,"")</f>
+        <f>IFERROR(O16*변수!O29,"")</f>
         <v/>
       </c>
       <c r="P17" s="20">
-        <f>IFERROR(P18+P19,"")</f>
+        <f>IFERROR(P16*변수!P29,"")</f>
         <v/>
       </c>
       <c r="Q17" s="20">
-        <f>IFERROR(Q18+Q19,"")</f>
+        <f>IFERROR(Q16*변수!Q29,"")</f>
         <v/>
       </c>
       <c r="R17" s="35">
-        <f>Q17</f>
+        <f>SUM(N17:Q17)</f>
         <v/>
       </c>
       <c r="S17" s="20">
-        <f>IFERROR(S18+S19,"")</f>
+        <f>IFERROR(S16*변수!S29,"")</f>
         <v/>
       </c>
       <c r="T17" s="20">
-        <f>IFERROR(T18+T19,"")</f>
+        <f>IFERROR(T16*변수!T29,"")</f>
         <v/>
       </c>
       <c r="U17" s="20">
-        <f>IFERROR(U18+U19,"")</f>
+        <f>IFERROR(U16*변수!U29,"")</f>
         <v/>
       </c>
       <c r="V17" s="20">
-        <f>IFERROR(V18+V19,"")</f>
+        <f>IFERROR(V16*변수!V29,"")</f>
         <v/>
       </c>
       <c r="W17" s="35">
-        <f>V17</f>
+        <f>SUM(S17:V17)</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>부채총계</t>
+          <t>자산총계</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -12006,7 +12192,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>부채총계</t>
+          <t>자산총계</t>
         </is>
       </c>
       <c r="E18" s="18">
@@ -12022,7 +12208,7 @@
         <v/>
       </c>
       <c r="H18" s="34" t="n">
-        <v>165.67</v>
+        <v>648.01</v>
       </c>
       <c r="I18" s="18">
         <f>IFERROR(VLOOKUP($D18,BS별도,MATCH(I$1,BS별도H,0),0)/100,"")</f>
@@ -12033,11 +12219,11 @@
         <v/>
       </c>
       <c r="K18" s="20">
-        <f>IFERROR(J18*(1+변수!K29),"")</f>
+        <f>IFERROR(K19+K20,"")</f>
         <v/>
       </c>
       <c r="L18" s="20">
-        <f>IFERROR(K18*(1+변수!L29),"")</f>
+        <f>IFERROR(L19+L20,"")</f>
         <v/>
       </c>
       <c r="M18" s="35">
@@ -12045,19 +12231,19 @@
         <v/>
       </c>
       <c r="N18" s="20">
-        <f>IFERROR(L18*(1+변수!N29),"")</f>
+        <f>IFERROR(N19+N20,"")</f>
         <v/>
       </c>
       <c r="O18" s="20">
-        <f>IFERROR(N18*(1+변수!O29),"")</f>
+        <f>IFERROR(O19+O20,"")</f>
         <v/>
       </c>
       <c r="P18" s="20">
-        <f>IFERROR(O18*(1+변수!P29),"")</f>
+        <f>IFERROR(P19+P20,"")</f>
         <v/>
       </c>
       <c r="Q18" s="20">
-        <f>IFERROR(P18*(1+변수!Q29),"")</f>
+        <f>IFERROR(Q19+Q20,"")</f>
         <v/>
       </c>
       <c r="R18" s="35">
@@ -12065,19 +12251,19 @@
         <v/>
       </c>
       <c r="S18" s="20">
-        <f>IFERROR(Q18*(1+변수!S29),"")</f>
+        <f>IFERROR(S19+S20,"")</f>
         <v/>
       </c>
       <c r="T18" s="20">
-        <f>IFERROR(S18*(1+변수!T29),"")</f>
+        <f>IFERROR(T19+T20,"")</f>
         <v/>
       </c>
       <c r="U18" s="20">
-        <f>IFERROR(T18*(1+변수!U29),"")</f>
+        <f>IFERROR(U19+U20,"")</f>
         <v/>
       </c>
       <c r="V18" s="20">
-        <f>IFERROR(U18*(1+변수!V29),"")</f>
+        <f>IFERROR(V19+V20,"")</f>
         <v/>
       </c>
       <c r="W18" s="35">
@@ -12088,7 +12274,7 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>자본총계</t>
+          <t>부채총계</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -12103,7 +12289,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>자본총계</t>
+          <t>부채총계</t>
         </is>
       </c>
       <c r="E19" s="18">
@@ -12119,7 +12305,7 @@
         <v/>
       </c>
       <c r="H19" s="34" t="n">
-        <v>482.35</v>
+        <v>165.67</v>
       </c>
       <c r="I19" s="18">
         <f>IFERROR(VLOOKUP($D19,BS별도,MATCH(I$1,BS별도H,0),0)/100,"")</f>
@@ -12130,11 +12316,11 @@
         <v/>
       </c>
       <c r="K19" s="20">
-        <f>IFERROR(J19+K15-변수!K30,"")</f>
+        <f>IFERROR(J19*(1+변수!K30),"")</f>
         <v/>
       </c>
       <c r="L19" s="20">
-        <f>IFERROR(K19+L15-변수!L30,"")</f>
+        <f>IFERROR(K19*(1+변수!L30),"")</f>
         <v/>
       </c>
       <c r="M19" s="35">
@@ -12142,19 +12328,19 @@
         <v/>
       </c>
       <c r="N19" s="20">
-        <f>IFERROR(L19+N15-변수!N30,"")</f>
+        <f>IFERROR(L19*(1+변수!N30),"")</f>
         <v/>
       </c>
       <c r="O19" s="20">
-        <f>IFERROR(N19+O15-변수!O30,"")</f>
+        <f>IFERROR(N19*(1+변수!O30),"")</f>
         <v/>
       </c>
       <c r="P19" s="20">
-        <f>IFERROR(O19+P15-변수!P30,"")</f>
+        <f>IFERROR(O19*(1+변수!P30),"")</f>
         <v/>
       </c>
       <c r="Q19" s="20">
-        <f>IFERROR(P19+Q15-변수!Q30,"")</f>
+        <f>IFERROR(P19*(1+변수!Q30),"")</f>
         <v/>
       </c>
       <c r="R19" s="35">
@@ -12162,19 +12348,19 @@
         <v/>
       </c>
       <c r="S19" s="20">
-        <f>IFERROR(Q19+S15-변수!S30,"")</f>
+        <f>IFERROR(Q19*(1+변수!S30),"")</f>
         <v/>
       </c>
       <c r="T19" s="20">
-        <f>IFERROR(S19+T15-변수!T30,"")</f>
+        <f>IFERROR(S19*(1+변수!T30),"")</f>
         <v/>
       </c>
       <c r="U19" s="20">
-        <f>IFERROR(T19+U15-변수!U30,"")</f>
+        <f>IFERROR(T19*(1+변수!U30),"")</f>
         <v/>
       </c>
       <c r="V19" s="20">
-        <f>IFERROR(U19+V15-변수!V30,"")</f>
+        <f>IFERROR(U19*(1+변수!V30),"")</f>
         <v/>
       </c>
       <c r="W19" s="35">
@@ -12185,7 +12371,7 @@
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>지배주주지분</t>
+          <t>자본총계</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -12200,7 +12386,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>지배주주지분</t>
+          <t>자본총계</t>
         </is>
       </c>
       <c r="E20" s="18">
@@ -12282,7 +12468,7 @@
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>총차입금</t>
+          <t>지배주주지분</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -12297,7 +12483,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>총차입금</t>
+          <t>지배주주지분</t>
         </is>
       </c>
       <c r="E21" s="18">
@@ -12313,7 +12499,7 @@
         <v/>
       </c>
       <c r="H21" s="34" t="n">
-        <v>80</v>
+        <v>482.35</v>
       </c>
       <c r="I21" s="18">
         <f>IFERROR(VLOOKUP($D21,BS별도,MATCH(I$1,BS별도H,0),0)/100,"")</f>
@@ -12324,11 +12510,11 @@
         <v/>
       </c>
       <c r="K21" s="20">
-        <f>IFERROR(J21*(1+변수!K32),"")</f>
+        <f>IFERROR(J21+K17-변수!K32,"")</f>
         <v/>
       </c>
       <c r="L21" s="20">
-        <f>IFERROR(K21*(1+변수!L32),"")</f>
+        <f>IFERROR(K21+L17-변수!L32,"")</f>
         <v/>
       </c>
       <c r="M21" s="35">
@@ -12336,19 +12522,19 @@
         <v/>
       </c>
       <c r="N21" s="20">
-        <f>IFERROR(L21*(1+변수!N32),"")</f>
+        <f>IFERROR(L21+N17-변수!N32,"")</f>
         <v/>
       </c>
       <c r="O21" s="20">
-        <f>IFERROR(N21*(1+변수!O32),"")</f>
+        <f>IFERROR(N21+O17-변수!O32,"")</f>
         <v/>
       </c>
       <c r="P21" s="20">
-        <f>IFERROR(O21*(1+변수!P32),"")</f>
+        <f>IFERROR(O21+P17-변수!P32,"")</f>
         <v/>
       </c>
       <c r="Q21" s="20">
-        <f>IFERROR(P21*(1+변수!Q32),"")</f>
+        <f>IFERROR(P21+Q17-변수!Q32,"")</f>
         <v/>
       </c>
       <c r="R21" s="35">
@@ -12356,19 +12542,19 @@
         <v/>
       </c>
       <c r="S21" s="20">
-        <f>IFERROR(Q21*(1+변수!S32),"")</f>
+        <f>IFERROR(Q21+S17-변수!S32,"")</f>
         <v/>
       </c>
       <c r="T21" s="20">
-        <f>IFERROR(S21*(1+변수!T32),"")</f>
+        <f>IFERROR(S21+T17-변수!T32,"")</f>
         <v/>
       </c>
       <c r="U21" s="20">
-        <f>IFERROR(T21*(1+변수!U32),"")</f>
+        <f>IFERROR(T21+U17-변수!U32,"")</f>
         <v/>
       </c>
       <c r="V21" s="20">
-        <f>IFERROR(U21*(1+변수!V32),"")</f>
+        <f>IFERROR(U21+V17-변수!V32,"")</f>
         <v/>
       </c>
       <c r="W21" s="35">
@@ -12379,7 +12565,7 @@
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>순차입금</t>
+          <t>총차입금</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -12394,7 +12580,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>순차입금</t>
+          <t>총차입금</t>
         </is>
       </c>
       <c r="E22" s="18">
@@ -12410,7 +12596,7 @@
         <v/>
       </c>
       <c r="H22" s="34" t="n">
-        <v>-17.02</v>
+        <v>80</v>
       </c>
       <c r="I22" s="18">
         <f>IFERROR(VLOOKUP($D22,BS별도,MATCH(I$1,BS별도H,0),0)/100,"")</f>
@@ -12476,7 +12662,7 @@
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>이자발생자산</t>
+          <t>순차입금</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -12491,7 +12677,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>이자발생자산</t>
+          <t>순차입금</t>
         </is>
       </c>
       <c r="E23" s="18">
@@ -12507,7 +12693,7 @@
         <v/>
       </c>
       <c r="H23" s="34" t="n">
-        <v>128.74</v>
+        <v>-17.02</v>
       </c>
       <c r="I23" s="18">
         <f>IFERROR(VLOOKUP($D23,BS별도,MATCH(I$1,BS별도H,0),0)/100,"")</f>
@@ -12573,7 +12759,7 @@
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>현금및현금성자산</t>
+          <t>이자발생자산</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -12588,7 +12774,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>현금및현금성자산</t>
+          <t>이자발생자산</t>
         </is>
       </c>
       <c r="E24" s="18">
@@ -12604,7 +12790,7 @@
         <v/>
       </c>
       <c r="H24" s="34" t="n">
-        <v>44.28</v>
+        <v>128.74</v>
       </c>
       <c r="I24" s="18">
         <f>IFERROR(VLOOKUP($D24,BS별도,MATCH(I$1,BS별도H,0),0)/100,"")</f>
@@ -12614,24 +12800,54 @@
         <f>IFERROR(VLOOKUP($D24,BS별도,MATCH(J$1,BS별도H,0),0)/100,"")</f>
         <v/>
       </c>
-      <c r="K24" s="20" t="n"/>
-      <c r="L24" s="20" t="n"/>
+      <c r="K24" s="20">
+        <f>IFERROR(J24*(1+변수!K35),"")</f>
+        <v/>
+      </c>
+      <c r="L24" s="20">
+        <f>IFERROR(K24*(1+변수!L35),"")</f>
+        <v/>
+      </c>
       <c r="M24" s="35">
         <f>L24</f>
         <v/>
       </c>
-      <c r="N24" s="20" t="n"/>
-      <c r="O24" s="20" t="n"/>
-      <c r="P24" s="20" t="n"/>
-      <c r="Q24" s="20" t="n"/>
+      <c r="N24" s="20">
+        <f>IFERROR(L24*(1+변수!N35),"")</f>
+        <v/>
+      </c>
+      <c r="O24" s="20">
+        <f>IFERROR(N24*(1+변수!O35),"")</f>
+        <v/>
+      </c>
+      <c r="P24" s="20">
+        <f>IFERROR(O24*(1+변수!P35),"")</f>
+        <v/>
+      </c>
+      <c r="Q24" s="20">
+        <f>IFERROR(P24*(1+변수!Q35),"")</f>
+        <v/>
+      </c>
       <c r="R24" s="35">
         <f>Q24</f>
         <v/>
       </c>
-      <c r="S24" s="20" t="n"/>
-      <c r="T24" s="20" t="n"/>
-      <c r="U24" s="20" t="n"/>
-      <c r="V24" s="20" t="n"/>
+      <c r="S24" s="20">
+        <f>IFERROR(Q24*(1+변수!S35),"")</f>
+        <v/>
+      </c>
+      <c r="T24" s="20">
+        <f>IFERROR(S24*(1+변수!T35),"")</f>
+        <v/>
+      </c>
+      <c r="U24" s="20">
+        <f>IFERROR(T24*(1+변수!U35),"")</f>
+        <v/>
+      </c>
+      <c r="V24" s="20">
+        <f>IFERROR(U24*(1+변수!V35),"")</f>
+        <v/>
+      </c>
       <c r="W24" s="35">
         <f>V24</f>
         <v/>
@@ -12640,12 +12856,12 @@
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>현금및현금성자산</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>현금흐름</t>
+          <t>재무상태</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -12655,7 +12871,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>현금및현금성자산</t>
         </is>
       </c>
       <c r="E25" s="18">
@@ -12670,7 +12886,9 @@
         <f>IFERROR(VLOOKUP($D25,BS별도,MATCH(G$1,BS별도H,0),0)/100,"")</f>
         <v/>
       </c>
-      <c r="H25" s="34" t="n"/>
+      <c r="H25" s="34" t="n">
+        <v>44.28</v>
+      </c>
       <c r="I25" s="18">
         <f>IFERROR(VLOOKUP($D25,BS별도,MATCH(I$1,BS별도H,0),0)/100,"")</f>
         <v/>
@@ -12682,7 +12900,7 @@
       <c r="K25" s="20" t="n"/>
       <c r="L25" s="20" t="n"/>
       <c r="M25" s="35">
-        <f>SUM(I25:L25)</f>
+        <f>L25</f>
         <v/>
       </c>
       <c r="N25" s="20" t="n"/>
@@ -12690,7 +12908,7 @@
       <c r="P25" s="20" t="n"/>
       <c r="Q25" s="20" t="n"/>
       <c r="R25" s="35">
-        <f>SUM(N25:Q25)</f>
+        <f>Q25</f>
         <v/>
       </c>
       <c r="S25" s="20" t="n"/>
@@ -12698,14 +12916,14 @@
       <c r="U25" s="20" t="n"/>
       <c r="V25" s="20" t="n"/>
       <c r="W25" s="35">
-        <f>SUM(S25:V25)</f>
+        <f>V25</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>영업활동현금흐름</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -12720,24 +12938,29 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>영업활동현금흐름</t>
-        </is>
-      </c>
-      <c r="E26" s="18" t="n">
-        <v>-44.44</v>
-      </c>
-      <c r="F26" s="18" t="n">
-        <v>103.54</v>
-      </c>
-      <c r="G26" s="18" t="n">
-        <v>-85.56</v>
+          <t>CAPEX</t>
+        </is>
+      </c>
+      <c r="E26" s="18">
+        <f>IFERROR(VLOOKUP($D26,BS별도,MATCH(E$1,BS별도H,0),0)/100,"")</f>
+        <v/>
+      </c>
+      <c r="F26" s="18">
+        <f>IFERROR(VLOOKUP($D26,BS별도,MATCH(F$1,BS별도H,0),0)/100,"")</f>
+        <v/>
+      </c>
+      <c r="G26" s="18">
+        <f>IFERROR(VLOOKUP($D26,BS별도,MATCH(G$1,BS별도H,0),0)/100,"")</f>
+        <v/>
       </c>
       <c r="H26" s="34" t="n"/>
-      <c r="I26" s="18" t="n">
-        <v>67.47</v>
-      </c>
-      <c r="J26" s="19" t="n">
-        <v>-23.48</v>
+      <c r="I26" s="18">
+        <f>IFERROR(VLOOKUP($D26,BS별도,MATCH(I$1,BS별도H,0),0)/100,"")</f>
+        <v/>
+      </c>
+      <c r="J26" s="19">
+        <f>IFERROR(VLOOKUP($D26,BS별도,MATCH(J$1,BS별도H,0),0)/100,"")</f>
+        <v/>
       </c>
       <c r="K26" s="20" t="n"/>
       <c r="L26" s="20" t="n"/>
@@ -12765,100 +12988,67 @@
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>주식수</t>
+          <t>영업활동현금흐름</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>주당</t>
+          <t>현금흐름</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>백만주</t>
+          <t>억원</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>유통주식수</t>
-        </is>
-      </c>
-      <c r="E27" s="26" t="n">
-        <v>8.241</v>
-      </c>
-      <c r="F27" s="26" t="n">
-        <v>8.241</v>
-      </c>
-      <c r="G27" s="26" t="n">
-        <v>8.241</v>
-      </c>
-      <c r="H27" s="27">
-        <f>G27</f>
-        <v/>
-      </c>
-      <c r="I27" s="26" t="n">
-        <v>8.241</v>
-      </c>
-      <c r="J27" s="28" t="n">
-        <v>8.241</v>
-      </c>
-      <c r="K27" s="36">
-        <f>IFERROR(J27*(1+변수!K38),"")</f>
-        <v/>
-      </c>
-      <c r="L27" s="36">
-        <f>IFERROR(K27*(1+변수!L38),"")</f>
-        <v/>
-      </c>
-      <c r="M27" s="30">
-        <f>L27</f>
-        <v/>
-      </c>
-      <c r="N27" s="36">
-        <f>IFERROR(L27*(1+변수!N38),"")</f>
-        <v/>
-      </c>
-      <c r="O27" s="36">
-        <f>IFERROR(N27*(1+변수!O38),"")</f>
-        <v/>
-      </c>
-      <c r="P27" s="36">
-        <f>IFERROR(O27*(1+변수!P38),"")</f>
-        <v/>
-      </c>
-      <c r="Q27" s="36">
-        <f>IFERROR(P27*(1+변수!Q38),"")</f>
-        <v/>
-      </c>
-      <c r="R27" s="30">
-        <f>Q27</f>
-        <v/>
-      </c>
-      <c r="S27" s="36">
-        <f>IFERROR(Q27*(1+변수!S38),"")</f>
-        <v/>
-      </c>
-      <c r="T27" s="36">
-        <f>IFERROR(S27*(1+변수!T38),"")</f>
-        <v/>
-      </c>
-      <c r="U27" s="36">
-        <f>IFERROR(T27*(1+변수!U38),"")</f>
-        <v/>
-      </c>
-      <c r="V27" s="36">
-        <f>IFERROR(U27*(1+변수!V38),"")</f>
-        <v/>
-      </c>
-      <c r="W27" s="30">
-        <f>V27</f>
+          <t>영업활동현금흐름</t>
+        </is>
+      </c>
+      <c r="E27" s="18" t="n">
+        <v>-44.44</v>
+      </c>
+      <c r="F27" s="18" t="n">
+        <v>103.54</v>
+      </c>
+      <c r="G27" s="18" t="n">
+        <v>-85.56</v>
+      </c>
+      <c r="H27" s="34" t="n"/>
+      <c r="I27" s="18" t="n">
+        <v>67.47</v>
+      </c>
+      <c r="J27" s="19" t="n">
+        <v>-23.48</v>
+      </c>
+      <c r="K27" s="20" t="n"/>
+      <c r="L27" s="20" t="n"/>
+      <c r="M27" s="35">
+        <f>SUM(I27:L27)</f>
+        <v/>
+      </c>
+      <c r="N27" s="20" t="n"/>
+      <c r="O27" s="20" t="n"/>
+      <c r="P27" s="20" t="n"/>
+      <c r="Q27" s="20" t="n"/>
+      <c r="R27" s="35">
+        <f>SUM(N27:Q27)</f>
+        <v/>
+      </c>
+      <c r="S27" s="20" t="n"/>
+      <c r="T27" s="20" t="n"/>
+      <c r="U27" s="20" t="n"/>
+      <c r="V27" s="20" t="n"/>
+      <c r="W27" s="35">
+        <f>SUM(S27:V27)</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>EPS</t>
+          <t>주식수</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12868,92 +13058,90 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>원</t>
+          <t>백만주</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>EPS</t>
-        </is>
-      </c>
-      <c r="E28" s="18">
-        <f>IFERROR(E16*100/E27,"")</f>
-        <v/>
-      </c>
-      <c r="F28" s="18">
-        <f>IFERROR(F16*100/F27,"")</f>
-        <v/>
-      </c>
-      <c r="G28" s="18">
-        <f>IFERROR(G16*100/G27,"")</f>
-        <v/>
-      </c>
-      <c r="H28" s="34" t="n"/>
-      <c r="I28" s="18">
-        <f>IFERROR(I16*100/I27,"")</f>
-        <v/>
-      </c>
-      <c r="J28" s="19">
-        <f>IFERROR(J16*100/J27,"")</f>
-        <v/>
-      </c>
-      <c r="K28" s="20">
-        <f>IFERROR(K16*100/K27,"")</f>
-        <v/>
-      </c>
-      <c r="L28" s="20">
-        <f>IFERROR(L16*100/L27,"")</f>
-        <v/>
-      </c>
-      <c r="M28" s="35">
-        <f>SUM(I28:L28)</f>
-        <v/>
-      </c>
-      <c r="N28" s="20">
-        <f>IFERROR(N16*100/N27,"")</f>
-        <v/>
-      </c>
-      <c r="O28" s="20">
-        <f>IFERROR(O16*100/O27,"")</f>
-        <v/>
-      </c>
-      <c r="P28" s="20">
-        <f>IFERROR(P16*100/P27,"")</f>
-        <v/>
-      </c>
-      <c r="Q28" s="20">
-        <f>IFERROR(Q16*100/Q27,"")</f>
-        <v/>
-      </c>
-      <c r="R28" s="35">
-        <f>SUM(N28:Q28)</f>
-        <v/>
-      </c>
-      <c r="S28" s="20">
-        <f>IFERROR(S16*100/S27,"")</f>
-        <v/>
-      </c>
-      <c r="T28" s="20">
-        <f>IFERROR(T16*100/T27,"")</f>
-        <v/>
-      </c>
-      <c r="U28" s="20">
-        <f>IFERROR(U16*100/U27,"")</f>
-        <v/>
-      </c>
-      <c r="V28" s="20">
-        <f>IFERROR(V16*100/V27,"")</f>
-        <v/>
-      </c>
-      <c r="W28" s="35">
-        <f>SUM(S28:V28)</f>
+          <t>유통주식수</t>
+        </is>
+      </c>
+      <c r="E28" s="26" t="n">
+        <v>8.241</v>
+      </c>
+      <c r="F28" s="26" t="n">
+        <v>8.241</v>
+      </c>
+      <c r="G28" s="26" t="n">
+        <v>8.241</v>
+      </c>
+      <c r="H28" s="27">
+        <f>G28</f>
+        <v/>
+      </c>
+      <c r="I28" s="26" t="n">
+        <v>8.241</v>
+      </c>
+      <c r="J28" s="28" t="n">
+        <v>8.241</v>
+      </c>
+      <c r="K28" s="36">
+        <f>IFERROR(J28*(1+변수!K39),"")</f>
+        <v/>
+      </c>
+      <c r="L28" s="36">
+        <f>IFERROR(K28*(1+변수!L39),"")</f>
+        <v/>
+      </c>
+      <c r="M28" s="30">
+        <f>L28</f>
+        <v/>
+      </c>
+      <c r="N28" s="36">
+        <f>IFERROR(L28*(1+변수!N39),"")</f>
+        <v/>
+      </c>
+      <c r="O28" s="36">
+        <f>IFERROR(N28*(1+변수!O39),"")</f>
+        <v/>
+      </c>
+      <c r="P28" s="36">
+        <f>IFERROR(O28*(1+변수!P39),"")</f>
+        <v/>
+      </c>
+      <c r="Q28" s="36">
+        <f>IFERROR(P28*(1+변수!Q39),"")</f>
+        <v/>
+      </c>
+      <c r="R28" s="30">
+        <f>Q28</f>
+        <v/>
+      </c>
+      <c r="S28" s="36">
+        <f>IFERROR(Q28*(1+변수!S39),"")</f>
+        <v/>
+      </c>
+      <c r="T28" s="36">
+        <f>IFERROR(S28*(1+변수!T39),"")</f>
+        <v/>
+      </c>
+      <c r="U28" s="36">
+        <f>IFERROR(T28*(1+변수!U39),"")</f>
+        <v/>
+      </c>
+      <c r="V28" s="36">
+        <f>IFERROR(U28*(1+변수!V39),"")</f>
+        <v/>
+      </c>
+      <c r="W28" s="30">
+        <f>V28</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>BPS</t>
+          <t>EPS</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12968,90 +13156,87 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>BPS</t>
+          <t>EPS</t>
         </is>
       </c>
       <c r="E29" s="18">
-        <f>IFERROR(E20*100/E27,"")</f>
+        <f>IFERROR(E17*100/E28,"")</f>
         <v/>
       </c>
       <c r="F29" s="18">
-        <f>IFERROR(F20*100/F27,"")</f>
+        <f>IFERROR(F17*100/F28,"")</f>
         <v/>
       </c>
       <c r="G29" s="18">
-        <f>IFERROR(G20*100/G27,"")</f>
-        <v/>
-      </c>
-      <c r="H29" s="34">
-        <f>G29</f>
-        <v/>
-      </c>
+        <f>IFERROR(G17*100/G28,"")</f>
+        <v/>
+      </c>
+      <c r="H29" s="34" t="n"/>
       <c r="I29" s="18">
-        <f>IFERROR(I20*100/I27,"")</f>
+        <f>IFERROR(I17*100/I28,"")</f>
         <v/>
       </c>
       <c r="J29" s="19">
-        <f>IFERROR(J20*100/J27,"")</f>
+        <f>IFERROR(J17*100/J28,"")</f>
         <v/>
       </c>
       <c r="K29" s="20">
-        <f>IFERROR(K20*100/K27,"")</f>
+        <f>IFERROR(K17*100/K28,"")</f>
         <v/>
       </c>
       <c r="L29" s="20">
-        <f>IFERROR(L20*100/L27,"")</f>
+        <f>IFERROR(L17*100/L28,"")</f>
         <v/>
       </c>
       <c r="M29" s="35">
-        <f>L29</f>
+        <f>SUM(I29:L29)</f>
         <v/>
       </c>
       <c r="N29" s="20">
-        <f>IFERROR(N20*100/N27,"")</f>
+        <f>IFERROR(N17*100/N28,"")</f>
         <v/>
       </c>
       <c r="O29" s="20">
-        <f>IFERROR(O20*100/O27,"")</f>
+        <f>IFERROR(O17*100/O28,"")</f>
         <v/>
       </c>
       <c r="P29" s="20">
-        <f>IFERROR(P20*100/P27,"")</f>
+        <f>IFERROR(P17*100/P28,"")</f>
         <v/>
       </c>
       <c r="Q29" s="20">
-        <f>IFERROR(Q20*100/Q27,"")</f>
+        <f>IFERROR(Q17*100/Q28,"")</f>
         <v/>
       </c>
       <c r="R29" s="35">
-        <f>Q29</f>
+        <f>SUM(N29:Q29)</f>
         <v/>
       </c>
       <c r="S29" s="20">
-        <f>IFERROR(S20*100/S27,"")</f>
+        <f>IFERROR(S17*100/S28,"")</f>
         <v/>
       </c>
       <c r="T29" s="20">
-        <f>IFERROR(T20*100/T27,"")</f>
+        <f>IFERROR(T17*100/T28,"")</f>
         <v/>
       </c>
       <c r="U29" s="20">
-        <f>IFERROR(U20*100/U27,"")</f>
+        <f>IFERROR(U17*100/U28,"")</f>
         <v/>
       </c>
       <c r="V29" s="20">
-        <f>IFERROR(V20*100/V27,"")</f>
+        <f>IFERROR(V17*100/V28,"")</f>
         <v/>
       </c>
       <c r="W29" s="35">
-        <f>V29</f>
+        <f>SUM(S29:V29)</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>DPS</t>
+          <t>BPS</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13066,52 +13251,90 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>DPS(보통주)</t>
-        </is>
-      </c>
-      <c r="E30" s="18" t="n"/>
-      <c r="F30" s="18" t="n"/>
-      <c r="G30" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="18" t="n"/>
-      <c r="J30" s="19" t="n"/>
-      <c r="K30" s="20" t="n"/>
-      <c r="L30" s="20" t="n">
-        <v>0</v>
+          <t>BPS</t>
+        </is>
+      </c>
+      <c r="E30" s="18">
+        <f>IFERROR(E21*100/E28,"")</f>
+        <v/>
+      </c>
+      <c r="F30" s="18">
+        <f>IFERROR(F21*100/F28,"")</f>
+        <v/>
+      </c>
+      <c r="G30" s="18">
+        <f>IFERROR(G21*100/G28,"")</f>
+        <v/>
+      </c>
+      <c r="H30" s="34">
+        <f>G30</f>
+        <v/>
+      </c>
+      <c r="I30" s="18">
+        <f>IFERROR(I21*100/I28,"")</f>
+        <v/>
+      </c>
+      <c r="J30" s="19">
+        <f>IFERROR(J21*100/J28,"")</f>
+        <v/>
+      </c>
+      <c r="K30" s="20">
+        <f>IFERROR(K21*100/K28,"")</f>
+        <v/>
+      </c>
+      <c r="L30" s="20">
+        <f>IFERROR(L21*100/L28,"")</f>
+        <v/>
       </c>
       <c r="M30" s="35">
-        <f>SUM(I30:L30)</f>
-        <v/>
-      </c>
-      <c r="N30" s="20" t="n"/>
-      <c r="O30" s="20" t="n"/>
-      <c r="P30" s="20" t="n"/>
-      <c r="Q30" s="20" t="n">
-        <v>0</v>
+        <f>L30</f>
+        <v/>
+      </c>
+      <c r="N30" s="20">
+        <f>IFERROR(N21*100/N28,"")</f>
+        <v/>
+      </c>
+      <c r="O30" s="20">
+        <f>IFERROR(O21*100/O28,"")</f>
+        <v/>
+      </c>
+      <c r="P30" s="20">
+        <f>IFERROR(P21*100/P28,"")</f>
+        <v/>
+      </c>
+      <c r="Q30" s="20">
+        <f>IFERROR(Q21*100/Q28,"")</f>
+        <v/>
       </c>
       <c r="R30" s="35">
-        <f>SUM(N30:Q30)</f>
-        <v/>
-      </c>
-      <c r="S30" s="20" t="n"/>
-      <c r="T30" s="20" t="n"/>
-      <c r="U30" s="20" t="n"/>
-      <c r="V30" s="20" t="n">
-        <v>0</v>
+        <f>Q30</f>
+        <v/>
+      </c>
+      <c r="S30" s="20">
+        <f>IFERROR(S21*100/S28,"")</f>
+        <v/>
+      </c>
+      <c r="T30" s="20">
+        <f>IFERROR(T21*100/T28,"")</f>
+        <v/>
+      </c>
+      <c r="U30" s="20">
+        <f>IFERROR(U21*100/U28,"")</f>
+        <v/>
+      </c>
+      <c r="V30" s="20">
+        <f>IFERROR(V21*100/V28,"")</f>
+        <v/>
       </c>
       <c r="W30" s="35">
-        <f>SUM(S30:V30)</f>
+        <f>V30</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>PER</t>
+          <t>DPS</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13121,26 +13344,28 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>배</t>
+          <t>원</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>PER</t>
+          <t>DPS(보통주)</t>
         </is>
       </c>
       <c r="E31" s="18" t="n"/>
       <c r="F31" s="18" t="n"/>
-      <c r="G31" s="18" t="n"/>
-      <c r="H31" s="34" t="n"/>
+      <c r="G31" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="34" t="n">
+        <v>0</v>
+      </c>
       <c r="I31" s="18" t="n"/>
-      <c r="J31" s="19" t="n">
-        <v>173.69</v>
-      </c>
-      <c r="K31" s="20" t="n">
-        <v>113.96</v>
-      </c>
-      <c r="L31" s="20" t="n"/>
+      <c r="J31" s="19" t="n"/>
+      <c r="K31" s="20" t="n"/>
+      <c r="L31" s="20" t="n">
+        <v>0</v>
+      </c>
       <c r="M31" s="35">
         <f>SUM(I31:L31)</f>
         <v/>
@@ -13148,7 +13373,9 @@
       <c r="N31" s="20" t="n"/>
       <c r="O31" s="20" t="n"/>
       <c r="P31" s="20" t="n"/>
-      <c r="Q31" s="20" t="n"/>
+      <c r="Q31" s="20" t="n">
+        <v>0</v>
+      </c>
       <c r="R31" s="35">
         <f>SUM(N31:Q31)</f>
         <v/>
@@ -13156,7 +13383,9 @@
       <c r="S31" s="20" t="n"/>
       <c r="T31" s="20" t="n"/>
       <c r="U31" s="20" t="n"/>
-      <c r="V31" s="20" t="n"/>
+      <c r="V31" s="20" t="n">
+        <v>0</v>
+      </c>
       <c r="W31" s="35">
         <f>SUM(S31:V31)</f>
         <v/>
@@ -13165,7 +13394,7 @@
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>PER</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -13180,75 +13409,37 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>PBR</t>
-        </is>
-      </c>
-      <c r="E32" s="18" t="n">
-        <v>5.02</v>
-      </c>
-      <c r="F32" s="18" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="G32" s="18" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="H32" s="34" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="I32" s="18" t="n">
-        <v>3.15</v>
-      </c>
+          <t>PER</t>
+        </is>
+      </c>
+      <c r="E32" s="18" t="n"/>
+      <c r="F32" s="18" t="n"/>
+      <c r="G32" s="18" t="n"/>
+      <c r="H32" s="34" t="n"/>
+      <c r="I32" s="18" t="n"/>
       <c r="J32" s="19" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="K32" s="20">
-        <f>IFERROR(F32*(1+변수!K41),"")</f>
-        <v/>
-      </c>
-      <c r="L32" s="20">
-        <f>IFERROR(G32*(1+변수!L41),"")</f>
-        <v/>
-      </c>
+        <v>173.69</v>
+      </c>
+      <c r="K32" s="20" t="n">
+        <v>113.96</v>
+      </c>
+      <c r="L32" s="20" t="n"/>
       <c r="M32" s="35">
         <f>SUM(I32:L32)</f>
         <v/>
       </c>
-      <c r="N32" s="20">
-        <f>IFERROR(I32*(1+변수!N41),"")</f>
-        <v/>
-      </c>
-      <c r="O32" s="20">
-        <f>IFERROR(J32*(1+변수!O41),"")</f>
-        <v/>
-      </c>
-      <c r="P32" s="20">
-        <f>IFERROR(K32*(1+변수!P41),"")</f>
-        <v/>
-      </c>
-      <c r="Q32" s="20">
-        <f>IFERROR(L32*(1+변수!Q41),"")</f>
-        <v/>
-      </c>
+      <c r="N32" s="20" t="n"/>
+      <c r="O32" s="20" t="n"/>
+      <c r="P32" s="20" t="n"/>
+      <c r="Q32" s="20" t="n"/>
       <c r="R32" s="35">
         <f>SUM(N32:Q32)</f>
         <v/>
       </c>
-      <c r="S32" s="20">
-        <f>IFERROR(N32*(1+변수!S41),"")</f>
-        <v/>
-      </c>
-      <c r="T32" s="20">
-        <f>IFERROR(O32*(1+변수!T41),"")</f>
-        <v/>
-      </c>
-      <c r="U32" s="20">
-        <f>IFERROR(P32*(1+변수!U41),"")</f>
-        <v/>
-      </c>
-      <c r="V32" s="20">
-        <f>IFERROR(Q32*(1+변수!V41),"")</f>
-        <v/>
-      </c>
+      <c r="S32" s="20" t="n"/>
+      <c r="T32" s="20" t="n"/>
+      <c r="U32" s="20" t="n"/>
+      <c r="V32" s="20" t="n"/>
       <c r="W32" s="35">
         <f>SUM(S32:V32)</f>
         <v/>
@@ -13257,46 +13448,48 @@
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>매출전사</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>사업부</t>
+          <t>주당</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>억원</t>
+          <t>배</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>매출 전사(부문 미분리)</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="E33" s="18" t="n">
-        <v>68.89</v>
+        <v>5.02</v>
       </c>
       <c r="F33" s="18" t="n">
-        <v>42.66</v>
+        <v>4.31</v>
       </c>
       <c r="G33" s="18" t="n">
-        <v>116.45</v>
-      </c>
-      <c r="H33" s="34" t="n"/>
+        <v>3.55</v>
+      </c>
+      <c r="H33" s="34" t="n">
+        <v>3.14</v>
+      </c>
       <c r="I33" s="18" t="n">
-        <v>39.88</v>
+        <v>3.15</v>
       </c>
       <c r="J33" s="19" t="n">
-        <v>99.52</v>
+        <v>2.53</v>
       </c>
       <c r="K33" s="20">
-        <f>IFERROR(K5*변수!K42,"")</f>
+        <f>IFERROR(F33*(1+변수!K42),"")</f>
         <v/>
       </c>
       <c r="L33" s="20">
-        <f>IFERROR(L5*변수!L42,"")</f>
+        <f>IFERROR(G33*(1+변수!L42),"")</f>
         <v/>
       </c>
       <c r="M33" s="35">
@@ -13304,19 +13497,19 @@
         <v/>
       </c>
       <c r="N33" s="20">
-        <f>IFERROR(N5*변수!N42,"")</f>
+        <f>IFERROR(I33*(1+변수!N42),"")</f>
         <v/>
       </c>
       <c r="O33" s="20">
-        <f>IFERROR(O5*변수!O42,"")</f>
+        <f>IFERROR(J33*(1+변수!O42),"")</f>
         <v/>
       </c>
       <c r="P33" s="20">
-        <f>IFERROR(P5*변수!P42,"")</f>
+        <f>IFERROR(K33*(1+변수!P42),"")</f>
         <v/>
       </c>
       <c r="Q33" s="20">
-        <f>IFERROR(Q5*변수!Q42,"")</f>
+        <f>IFERROR(L33*(1+변수!Q42),"")</f>
         <v/>
       </c>
       <c r="R33" s="35">
@@ -13324,19 +13517,19 @@
         <v/>
       </c>
       <c r="S33" s="20">
-        <f>IFERROR(S5*변수!S42,"")</f>
+        <f>IFERROR(N33*(1+변수!S42),"")</f>
         <v/>
       </c>
       <c r="T33" s="20">
-        <f>IFERROR(T5*변수!T42,"")</f>
+        <f>IFERROR(O33*(1+변수!T42),"")</f>
         <v/>
       </c>
       <c r="U33" s="20">
-        <f>IFERROR(U5*변수!U42,"")</f>
+        <f>IFERROR(P33*(1+변수!U42),"")</f>
         <v/>
       </c>
       <c r="V33" s="20">
-        <f>IFERROR(V5*변수!V42,"")</f>
+        <f>IFERROR(Q33*(1+변수!V42),"")</f>
         <v/>
       </c>
       <c r="W33" s="35">
@@ -13347,7 +13540,7 @@
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>OP전사</t>
+          <t>매출전사</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -13362,31 +13555,31 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>OP 전사(부문 미분리)</t>
+          <t>매출 전사(부문 미분리)</t>
         </is>
       </c>
       <c r="E34" s="18" t="n">
-        <v>-20.83</v>
+        <v>68.89</v>
       </c>
       <c r="F34" s="18" t="n">
-        <v>-10.14</v>
+        <v>42.66</v>
       </c>
       <c r="G34" s="18" t="n">
-        <v>9.48</v>
+        <v>116.45</v>
       </c>
       <c r="H34" s="34" t="n"/>
       <c r="I34" s="18" t="n">
-        <v>-20.14</v>
+        <v>39.88</v>
       </c>
       <c r="J34" s="19" t="n">
-        <v>5.43</v>
+        <v>99.52</v>
       </c>
       <c r="K34" s="20">
-        <f>IFERROR(K33*변수!K43,"")</f>
+        <f>IFERROR(K5*변수!K43,"")</f>
         <v/>
       </c>
       <c r="L34" s="20">
-        <f>IFERROR(L33*변수!L43,"")</f>
+        <f>IFERROR(L5*변수!L43,"")</f>
         <v/>
       </c>
       <c r="M34" s="35">
@@ -13394,19 +13587,19 @@
         <v/>
       </c>
       <c r="N34" s="20">
-        <f>IFERROR(N33*변수!N43,"")</f>
+        <f>IFERROR(N5*변수!N43,"")</f>
         <v/>
       </c>
       <c r="O34" s="20">
-        <f>IFERROR(O33*변수!O43,"")</f>
+        <f>IFERROR(O5*변수!O43,"")</f>
         <v/>
       </c>
       <c r="P34" s="20">
-        <f>IFERROR(P33*변수!P43,"")</f>
+        <f>IFERROR(P5*변수!P43,"")</f>
         <v/>
       </c>
       <c r="Q34" s="20">
-        <f>IFERROR(Q33*변수!Q43,"")</f>
+        <f>IFERROR(Q5*변수!Q43,"")</f>
         <v/>
       </c>
       <c r="R34" s="35">
@@ -13414,19 +13607,19 @@
         <v/>
       </c>
       <c r="S34" s="20">
-        <f>IFERROR(S33*변수!S43,"")</f>
+        <f>IFERROR(S5*변수!S43,"")</f>
         <v/>
       </c>
       <c r="T34" s="20">
-        <f>IFERROR(T33*변수!T43,"")</f>
+        <f>IFERROR(T5*변수!T43,"")</f>
         <v/>
       </c>
       <c r="U34" s="20">
-        <f>IFERROR(U33*변수!U43,"")</f>
+        <f>IFERROR(U5*변수!U43,"")</f>
         <v/>
       </c>
       <c r="V34" s="20">
-        <f>IFERROR(V33*변수!V43,"")</f>
+        <f>IFERROR(V5*변수!V43,"")</f>
         <v/>
       </c>
       <c r="W34" s="35">
@@ -13435,124 +13628,121 @@
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="2" t="inlineStr">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>OP전사</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>사업부</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>억원</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>OP 전사(부문 미분리)</t>
+        </is>
+      </c>
+      <c r="E35" s="18" t="n">
+        <v>-20.83</v>
+      </c>
+      <c r="F35" s="18" t="n">
+        <v>-10.14</v>
+      </c>
+      <c r="G35" s="18" t="n">
+        <v>9.48</v>
+      </c>
+      <c r="H35" s="34" t="n"/>
+      <c r="I35" s="18" t="n">
+        <v>-20.14</v>
+      </c>
+      <c r="J35" s="19" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="K35" s="20">
+        <f>IFERROR(K34*변수!K44,"")</f>
+        <v/>
+      </c>
+      <c r="L35" s="20">
+        <f>IFERROR(L34*변수!L44,"")</f>
+        <v/>
+      </c>
+      <c r="M35" s="35">
+        <f>SUM(I35:L35)</f>
+        <v/>
+      </c>
+      <c r="N35" s="20">
+        <f>IFERROR(N34*변수!N44,"")</f>
+        <v/>
+      </c>
+      <c r="O35" s="20">
+        <f>IFERROR(O34*변수!O44,"")</f>
+        <v/>
+      </c>
+      <c r="P35" s="20">
+        <f>IFERROR(P34*변수!P44,"")</f>
+        <v/>
+      </c>
+      <c r="Q35" s="20">
+        <f>IFERROR(Q34*변수!Q44,"")</f>
+        <v/>
+      </c>
+      <c r="R35" s="35">
+        <f>SUM(N35:Q35)</f>
+        <v/>
+      </c>
+      <c r="S35" s="20">
+        <f>IFERROR(S34*변수!S44,"")</f>
+        <v/>
+      </c>
+      <c r="T35" s="20">
+        <f>IFERROR(T34*변수!T44,"")</f>
+        <v/>
+      </c>
+      <c r="U35" s="20">
+        <f>IFERROR(U34*변수!U44,"")</f>
+        <v/>
+      </c>
+      <c r="V35" s="20">
+        <f>IFERROR(V34*변수!V44,"")</f>
+        <v/>
+      </c>
+      <c r="W35" s="35">
+        <f>SUM(S35:V35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>비율(참고)</t>
         </is>
       </c>
-      <c r="H35" s="9" t="n"/>
-      <c r="J35" s="5" t="n"/>
-      <c r="K35" s="10" t="n"/>
-      <c r="L35" s="10" t="n"/>
-      <c r="M35" s="11" t="n"/>
-      <c r="N35" s="10" t="n"/>
-      <c r="O35" s="10" t="n"/>
-      <c r="P35" s="10" t="n"/>
-      <c r="Q35" s="10" t="n"/>
-      <c r="R35" s="11" t="n"/>
-      <c r="S35" s="10" t="n"/>
-      <c r="T35" s="10" t="n"/>
-      <c r="U35" s="10" t="n"/>
-      <c r="V35" s="10" t="n"/>
-      <c r="W35" s="11" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="12" t="inlineStr">
-        <is>
-          <t>OPM</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>영업이익 / 매출액</t>
-        </is>
-      </c>
-      <c r="E36" s="21">
-        <f>IFERROR(E9/E5,"")</f>
-        <v/>
-      </c>
-      <c r="F36" s="21">
-        <f>IFERROR(F9/F5,"")</f>
-        <v/>
-      </c>
-      <c r="G36" s="21">
-        <f>IFERROR(G9/G5,"")</f>
-        <v/>
-      </c>
-      <c r="H36" s="22">
-        <f>IFERROR(H9/H5,"")</f>
-        <v/>
-      </c>
-      <c r="I36" s="21">
-        <f>IFERROR(I9/I5,"")</f>
-        <v/>
-      </c>
-      <c r="J36" s="23">
-        <f>IFERROR(J9/J5,"")</f>
-        <v/>
-      </c>
-      <c r="K36" s="31">
-        <f>IFERROR(K9/K5,"")</f>
-        <v/>
-      </c>
-      <c r="L36" s="31">
-        <f>IFERROR(L9/L5,"")</f>
-        <v/>
-      </c>
-      <c r="M36" s="25">
-        <f>IFERROR(M9/M5,"")</f>
-        <v/>
-      </c>
-      <c r="N36" s="31">
-        <f>IFERROR(N9/N5,"")</f>
-        <v/>
-      </c>
-      <c r="O36" s="31">
-        <f>IFERROR(O9/O5,"")</f>
-        <v/>
-      </c>
-      <c r="P36" s="31">
-        <f>IFERROR(P9/P5,"")</f>
-        <v/>
-      </c>
-      <c r="Q36" s="31">
-        <f>IFERROR(Q9/Q5,"")</f>
-        <v/>
-      </c>
-      <c r="R36" s="25">
-        <f>IFERROR(R9/R5,"")</f>
-        <v/>
-      </c>
-      <c r="S36" s="31">
-        <f>IFERROR(S9/S5,"")</f>
-        <v/>
-      </c>
-      <c r="T36" s="31">
-        <f>IFERROR(T9/T5,"")</f>
-        <v/>
-      </c>
-      <c r="U36" s="31">
-        <f>IFERROR(U9/U5,"")</f>
-        <v/>
-      </c>
-      <c r="V36" s="31">
-        <f>IFERROR(V9/V5,"")</f>
-        <v/>
-      </c>
-      <c r="W36" s="25">
-        <f>IFERROR(W9/W5,"")</f>
-        <v/>
-      </c>
+      <c r="H36" s="9" t="n"/>
+      <c r="J36" s="5" t="n"/>
+      <c r="K36" s="10" t="n"/>
+      <c r="L36" s="10" t="n"/>
+      <c r="M36" s="11" t="n"/>
+      <c r="N36" s="10" t="n"/>
+      <c r="O36" s="10" t="n"/>
+      <c r="P36" s="10" t="n"/>
+      <c r="Q36" s="10" t="n"/>
+      <c r="R36" s="11" t="n"/>
+      <c r="S36" s="10" t="n"/>
+      <c r="T36" s="10" t="n"/>
+      <c r="U36" s="10" t="n"/>
+      <c r="V36" s="10" t="n"/>
+      <c r="W36" s="11" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>NPM</t>
+          <t>OPM</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -13562,90 +13752,90 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>지배주주순이익 / 매출액</t>
+          <t>영업이익 / 매출액</t>
         </is>
       </c>
       <c r="E37" s="21">
-        <f>IFERROR(E16/E5,"")</f>
+        <f>IFERROR(E9/E5,"")</f>
         <v/>
       </c>
       <c r="F37" s="21">
-        <f>IFERROR(F16/F5,"")</f>
+        <f>IFERROR(F9/F5,"")</f>
         <v/>
       </c>
       <c r="G37" s="21">
-        <f>IFERROR(G16/G5,"")</f>
+        <f>IFERROR(G9/G5,"")</f>
         <v/>
       </c>
       <c r="H37" s="22">
-        <f>IFERROR(H16/H5,"")</f>
+        <f>IFERROR(H9/H5,"")</f>
         <v/>
       </c>
       <c r="I37" s="21">
-        <f>IFERROR(I16/I5,"")</f>
+        <f>IFERROR(I9/I5,"")</f>
         <v/>
       </c>
       <c r="J37" s="23">
-        <f>IFERROR(J16/J5,"")</f>
+        <f>IFERROR(J9/J5,"")</f>
         <v/>
       </c>
       <c r="K37" s="31">
-        <f>IFERROR(K16/K5,"")</f>
+        <f>IFERROR(K9/K5,"")</f>
         <v/>
       </c>
       <c r="L37" s="31">
-        <f>IFERROR(L16/L5,"")</f>
+        <f>IFERROR(L9/L5,"")</f>
         <v/>
       </c>
       <c r="M37" s="25">
-        <f>IFERROR(M16/M5,"")</f>
+        <f>IFERROR(M9/M5,"")</f>
         <v/>
       </c>
       <c r="N37" s="31">
-        <f>IFERROR(N16/N5,"")</f>
+        <f>IFERROR(N9/N5,"")</f>
         <v/>
       </c>
       <c r="O37" s="31">
-        <f>IFERROR(O16/O5,"")</f>
+        <f>IFERROR(O9/O5,"")</f>
         <v/>
       </c>
       <c r="P37" s="31">
-        <f>IFERROR(P16/P5,"")</f>
+        <f>IFERROR(P9/P5,"")</f>
         <v/>
       </c>
       <c r="Q37" s="31">
-        <f>IFERROR(Q16/Q5,"")</f>
+        <f>IFERROR(Q9/Q5,"")</f>
         <v/>
       </c>
       <c r="R37" s="25">
-        <f>IFERROR(R16/R5,"")</f>
+        <f>IFERROR(R9/R5,"")</f>
         <v/>
       </c>
       <c r="S37" s="31">
-        <f>IFERROR(S16/S5,"")</f>
+        <f>IFERROR(S9/S5,"")</f>
         <v/>
       </c>
       <c r="T37" s="31">
-        <f>IFERROR(T16/T5,"")</f>
+        <f>IFERROR(T9/T5,"")</f>
         <v/>
       </c>
       <c r="U37" s="31">
-        <f>IFERROR(U16/U5,"")</f>
+        <f>IFERROR(U9/U5,"")</f>
         <v/>
       </c>
       <c r="V37" s="31">
-        <f>IFERROR(V16/V5,"")</f>
+        <f>IFERROR(V9/V5,"")</f>
         <v/>
       </c>
       <c r="W37" s="25">
-        <f>IFERROR(W16/W5,"")</f>
+        <f>IFERROR(W9/W5,"")</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>매출원가율</t>
+          <t>NPM</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -13655,175 +13845,268 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>매출원가 / 매출액</t>
+          <t>지배주주순이익 / 매출액</t>
         </is>
       </c>
       <c r="E38" s="21">
-        <f>IFERROR(E6/E5,"")</f>
+        <f>IFERROR(E17/E5,"")</f>
         <v/>
       </c>
       <c r="F38" s="21">
-        <f>IFERROR(F6/F5,"")</f>
+        <f>IFERROR(F17/F5,"")</f>
         <v/>
       </c>
       <c r="G38" s="21">
-        <f>IFERROR(G6/G5,"")</f>
+        <f>IFERROR(G17/G5,"")</f>
         <v/>
       </c>
       <c r="H38" s="22">
-        <f>IFERROR(H6/H5,"")</f>
+        <f>IFERROR(H17/H5,"")</f>
         <v/>
       </c>
       <c r="I38" s="21">
-        <f>IFERROR(I6/I5,"")</f>
+        <f>IFERROR(I17/I5,"")</f>
         <v/>
       </c>
       <c r="J38" s="23">
-        <f>IFERROR(J6/J5,"")</f>
+        <f>IFERROR(J17/J5,"")</f>
         <v/>
       </c>
       <c r="K38" s="31">
-        <f>IFERROR(K6/K5,"")</f>
+        <f>IFERROR(K17/K5,"")</f>
         <v/>
       </c>
       <c r="L38" s="31">
-        <f>IFERROR(L6/L5,"")</f>
+        <f>IFERROR(L17/L5,"")</f>
         <v/>
       </c>
       <c r="M38" s="25">
-        <f>IFERROR(M6/M5,"")</f>
+        <f>IFERROR(M17/M5,"")</f>
         <v/>
       </c>
       <c r="N38" s="31">
-        <f>IFERROR(N6/N5,"")</f>
+        <f>IFERROR(N17/N5,"")</f>
         <v/>
       </c>
       <c r="O38" s="31">
-        <f>IFERROR(O6/O5,"")</f>
+        <f>IFERROR(O17/O5,"")</f>
         <v/>
       </c>
       <c r="P38" s="31">
-        <f>IFERROR(P6/P5,"")</f>
+        <f>IFERROR(P17/P5,"")</f>
         <v/>
       </c>
       <c r="Q38" s="31">
-        <f>IFERROR(Q6/Q5,"")</f>
+        <f>IFERROR(Q17/Q5,"")</f>
         <v/>
       </c>
       <c r="R38" s="25">
-        <f>IFERROR(R6/R5,"")</f>
+        <f>IFERROR(R17/R5,"")</f>
         <v/>
       </c>
       <c r="S38" s="31">
-        <f>IFERROR(S6/S5,"")</f>
+        <f>IFERROR(S17/S5,"")</f>
         <v/>
       </c>
       <c r="T38" s="31">
-        <f>IFERROR(T6/T5,"")</f>
+        <f>IFERROR(T17/T5,"")</f>
         <v/>
       </c>
       <c r="U38" s="31">
-        <f>IFERROR(U6/U5,"")</f>
+        <f>IFERROR(U17/U5,"")</f>
         <v/>
       </c>
       <c r="V38" s="31">
-        <f>IFERROR(V6/V5,"")</f>
+        <f>IFERROR(V17/V5,"")</f>
         <v/>
       </c>
       <c r="W38" s="25">
-        <f>IFERROR(W6/W5,"")</f>
+        <f>IFERROR(W17/W5,"")</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
+          <t>매출원가율</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>매출원가 / 매출액</t>
+        </is>
+      </c>
+      <c r="E39" s="21">
+        <f>IFERROR(E6/E5,"")</f>
+        <v/>
+      </c>
+      <c r="F39" s="21">
+        <f>IFERROR(F6/F5,"")</f>
+        <v/>
+      </c>
+      <c r="G39" s="21">
+        <f>IFERROR(G6/G5,"")</f>
+        <v/>
+      </c>
+      <c r="H39" s="22">
+        <f>IFERROR(H6/H5,"")</f>
+        <v/>
+      </c>
+      <c r="I39" s="21">
+        <f>IFERROR(I6/I5,"")</f>
+        <v/>
+      </c>
+      <c r="J39" s="23">
+        <f>IFERROR(J6/J5,"")</f>
+        <v/>
+      </c>
+      <c r="K39" s="31">
+        <f>IFERROR(K6/K5,"")</f>
+        <v/>
+      </c>
+      <c r="L39" s="31">
+        <f>IFERROR(L6/L5,"")</f>
+        <v/>
+      </c>
+      <c r="M39" s="25">
+        <f>IFERROR(M6/M5,"")</f>
+        <v/>
+      </c>
+      <c r="N39" s="31">
+        <f>IFERROR(N6/N5,"")</f>
+        <v/>
+      </c>
+      <c r="O39" s="31">
+        <f>IFERROR(O6/O5,"")</f>
+        <v/>
+      </c>
+      <c r="P39" s="31">
+        <f>IFERROR(P6/P5,"")</f>
+        <v/>
+      </c>
+      <c r="Q39" s="31">
+        <f>IFERROR(Q6/Q5,"")</f>
+        <v/>
+      </c>
+      <c r="R39" s="25">
+        <f>IFERROR(R6/R5,"")</f>
+        <v/>
+      </c>
+      <c r="S39" s="31">
+        <f>IFERROR(S6/S5,"")</f>
+        <v/>
+      </c>
+      <c r="T39" s="31">
+        <f>IFERROR(T6/T5,"")</f>
+        <v/>
+      </c>
+      <c r="U39" s="31">
+        <f>IFERROR(U6/U5,"")</f>
+        <v/>
+      </c>
+      <c r="V39" s="31">
+        <f>IFERROR(V6/V5,"")</f>
+        <v/>
+      </c>
+      <c r="W39" s="25">
+        <f>IFERROR(W6/W5,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
           <t>판관비율</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>판관비 / 매출액</t>
         </is>
       </c>
-      <c r="E39" s="21">
+      <c r="E40" s="21">
         <f>IFERROR(E8/E5,"")</f>
         <v/>
       </c>
-      <c r="F39" s="21">
+      <c r="F40" s="21">
         <f>IFERROR(F8/F5,"")</f>
         <v/>
       </c>
-      <c r="G39" s="21">
+      <c r="G40" s="21">
         <f>IFERROR(G8/G5,"")</f>
         <v/>
       </c>
-      <c r="H39" s="22">
+      <c r="H40" s="22">
         <f>IFERROR(H8/H5,"")</f>
         <v/>
       </c>
-      <c r="I39" s="21">
+      <c r="I40" s="21">
         <f>IFERROR(I8/I5,"")</f>
         <v/>
       </c>
-      <c r="J39" s="23">
+      <c r="J40" s="23">
         <f>IFERROR(J8/J5,"")</f>
         <v/>
       </c>
-      <c r="K39" s="31">
+      <c r="K40" s="31">
         <f>IFERROR(K8/K5,"")</f>
         <v/>
       </c>
-      <c r="L39" s="31">
+      <c r="L40" s="31">
         <f>IFERROR(L8/L5,"")</f>
         <v/>
       </c>
-      <c r="M39" s="25">
+      <c r="M40" s="25">
         <f>IFERROR(M8/M5,"")</f>
         <v/>
       </c>
-      <c r="N39" s="31">
+      <c r="N40" s="31">
         <f>IFERROR(N8/N5,"")</f>
         <v/>
       </c>
-      <c r="O39" s="31">
+      <c r="O40" s="31">
         <f>IFERROR(O8/O5,"")</f>
         <v/>
       </c>
-      <c r="P39" s="31">
+      <c r="P40" s="31">
         <f>IFERROR(P8/P5,"")</f>
         <v/>
       </c>
-      <c r="Q39" s="31">
+      <c r="Q40" s="31">
         <f>IFERROR(Q8/Q5,"")</f>
         <v/>
       </c>
-      <c r="R39" s="25">
+      <c r="R40" s="25">
         <f>IFERROR(R8/R5,"")</f>
         <v/>
       </c>
-      <c r="S39" s="31">
+      <c r="S40" s="31">
         <f>IFERROR(S8/S5,"")</f>
         <v/>
       </c>
-      <c r="T39" s="31">
+      <c r="T40" s="31">
         <f>IFERROR(T8/T5,"")</f>
         <v/>
       </c>
-      <c r="U39" s="31">
+      <c r="U40" s="31">
         <f>IFERROR(U8/U5,"")</f>
         <v/>
       </c>
-      <c r="V39" s="31">
+      <c r="V40" s="31">
         <f>IFERROR(V8/V5,"")</f>
         <v/>
       </c>
-      <c r="W39" s="25">
+      <c r="W40" s="25">
         <f>IFERROR(W8/W5,"")</f>
         <v/>
       </c>
@@ -13840,7 +14123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S39"/>
+  <dimension ref="A1:S40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -13953,7 +14236,7 @@
         </is>
       </c>
       <c r="D2" s="18">
-        <f>변수!D46</f>
+        <f>변수!D47</f>
         <v/>
       </c>
       <c r="I2" s="38" t="n"/>
@@ -14599,12 +14882,12 @@
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>기타영업외손익</t>
+          <t>이자손익</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>기타영업외손익</t>
+          <t>이자손익(이자수익 − 이자비용)</t>
         </is>
       </c>
       <c r="E12" s="18">
@@ -14671,12 +14954,12 @@
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>세전이익</t>
+          <t>기타영업외손익</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>법인세비용차감전이익</t>
+          <t>기타영업외손익</t>
         </is>
       </c>
       <c r="E13" s="18">
@@ -14743,12 +15026,12 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>법인세비용</t>
+          <t>세전이익</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>법인세비용</t>
+          <t>법인세비용차감전이익</t>
         </is>
       </c>
       <c r="E14" s="18">
@@ -14815,12 +15098,12 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>당기순이익</t>
+          <t>법인세비용</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>당기순이익</t>
+          <t>법인세비용</t>
         </is>
       </c>
       <c r="E15" s="18">
@@ -14887,12 +15170,12 @@
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>지배주주순이익</t>
+          <t>당기순이익</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>지배주주순이익</t>
+          <t>당기순이익</t>
         </is>
       </c>
       <c r="E16" s="18">
@@ -14959,12 +15242,12 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>자산총계</t>
+          <t>지배주주순이익</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>자산총계</t>
+          <t>지배주주순이익</t>
         </is>
       </c>
       <c r="E17" s="18">
@@ -15031,12 +15314,12 @@
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>부채총계</t>
+          <t>자산총계</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>부채총계</t>
+          <t>자산총계</t>
         </is>
       </c>
       <c r="E18" s="18">
@@ -15103,12 +15386,12 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>자본총계</t>
+          <t>부채총계</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>자본총계</t>
+          <t>부채총계</t>
         </is>
       </c>
       <c r="E19" s="18">
@@ -15175,12 +15458,12 @@
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>지배주주지분</t>
+          <t>자본총계</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>지배주주지분</t>
+          <t>자본총계</t>
         </is>
       </c>
       <c r="E20" s="18">
@@ -15247,12 +15530,12 @@
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>총차입금</t>
+          <t>지배주주지분</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>총차입금</t>
+          <t>지배주주지분</t>
         </is>
       </c>
       <c r="E21" s="18">
@@ -15319,12 +15602,12 @@
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>순차입금</t>
+          <t>총차입금</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>순차입금</t>
+          <t>총차입금</t>
         </is>
       </c>
       <c r="E22" s="18">
@@ -15391,12 +15674,12 @@
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>이자발생자산</t>
+          <t>순차입금</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>이자발생자산</t>
+          <t>순차입금</t>
         </is>
       </c>
       <c r="E23" s="18">
@@ -15463,12 +15746,12 @@
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>현금및현금성자산</t>
+          <t>이자발생자산</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>현금및현금성자산</t>
+          <t>이자발생자산</t>
         </is>
       </c>
       <c r="E24" s="18">
@@ -15535,12 +15818,12 @@
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>현금및현금성자산</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>현금및현금성자산</t>
         </is>
       </c>
       <c r="E25" s="18">
@@ -15607,12 +15890,12 @@
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>영업활동현금흐름</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>영업활동현금흐름</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="E26" s="18">
@@ -15679,71 +15962,71 @@
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>주식수</t>
+          <t>영업활동현금흐름</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>유통주식수</t>
-        </is>
-      </c>
-      <c r="E27" s="26">
+          <t>영업활동현금흐름</t>
+        </is>
+      </c>
+      <c r="E27" s="18">
         <f>IFERROR(VLOOKUP($A27,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="F27" s="26">
+      <c r="F27" s="18">
         <f>IFERROR(VLOOKUP($A27,subQ,MATCH(F$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="G27" s="26">
+      <c r="G27" s="18">
         <f>IFERROR(VLOOKUP($A27,subQ,MATCH(G$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="H27" s="26">
+      <c r="H27" s="18">
         <f>IFERROR(VLOOKUP($A27,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I27" s="43">
+      <c r="I27" s="41">
         <f>IFERROR(VLOOKUP($A27,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="J27" s="36">
+      <c r="J27" s="20">
         <f>IFERROR(VLOOKUP($A27,subQ,MATCH(J$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="K27" s="36">
+      <c r="K27" s="20">
         <f>IFERROR(VLOOKUP($A27,subQ,MATCH(K$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="L27" s="36">
+      <c r="L27" s="20">
         <f>IFERROR(VLOOKUP($A27,subQ,MATCH(L$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="M27" s="36">
+      <c r="M27" s="20">
         <f>IFERROR(VLOOKUP($A27,subQ,MATCH(M$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="N27" s="36">
+      <c r="N27" s="20">
         <f>IFERROR(VLOOKUP($A27,subQ,MATCH(N$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="O27" s="36">
+      <c r="O27" s="20">
         <f>IFERROR(VLOOKUP($A27,subQ,MATCH(O$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="P27" s="36">
+      <c r="P27" s="20">
         <f>IFERROR(VLOOKUP($A27,subQ,MATCH(P$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="Q27" s="36">
+      <c r="Q27" s="20">
         <f>IFERROR(VLOOKUP($A27,subQ,MATCH(Q$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="R27" s="36">
+      <c r="R27" s="20">
         <f>IFERROR(VLOOKUP($A27,subQ,MATCH(R$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="S27" s="36">
+      <c r="S27" s="20">
         <f>IFERROR(VLOOKUP($A27,subQ,MATCH(S$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -15751,71 +16034,71 @@
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>EPS</t>
+          <t>주식수</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>EPS</t>
-        </is>
-      </c>
-      <c r="E28" s="18">
+          <t>유통주식수</t>
+        </is>
+      </c>
+      <c r="E28" s="26">
         <f>IFERROR(VLOOKUP($A28,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="F28" s="18">
+      <c r="F28" s="26">
         <f>IFERROR(VLOOKUP($A28,subQ,MATCH(F$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="G28" s="18">
+      <c r="G28" s="26">
         <f>IFERROR(VLOOKUP($A28,subQ,MATCH(G$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="H28" s="18">
+      <c r="H28" s="26">
         <f>IFERROR(VLOOKUP($A28,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I28" s="41">
+      <c r="I28" s="43">
         <f>IFERROR(VLOOKUP($A28,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="J28" s="20">
+      <c r="J28" s="36">
         <f>IFERROR(VLOOKUP($A28,subQ,MATCH(J$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="K28" s="20">
+      <c r="K28" s="36">
         <f>IFERROR(VLOOKUP($A28,subQ,MATCH(K$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="L28" s="20">
+      <c r="L28" s="36">
         <f>IFERROR(VLOOKUP($A28,subQ,MATCH(L$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="M28" s="20">
+      <c r="M28" s="36">
         <f>IFERROR(VLOOKUP($A28,subQ,MATCH(M$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="N28" s="20">
+      <c r="N28" s="36">
         <f>IFERROR(VLOOKUP($A28,subQ,MATCH(N$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="O28" s="20">
+      <c r="O28" s="36">
         <f>IFERROR(VLOOKUP($A28,subQ,MATCH(O$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="P28" s="20">
+      <c r="P28" s="36">
         <f>IFERROR(VLOOKUP($A28,subQ,MATCH(P$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="Q28" s="20">
+      <c r="Q28" s="36">
         <f>IFERROR(VLOOKUP($A28,subQ,MATCH(Q$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="R28" s="20">
+      <c r="R28" s="36">
         <f>IFERROR(VLOOKUP($A28,subQ,MATCH(R$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="S28" s="20">
+      <c r="S28" s="36">
         <f>IFERROR(VLOOKUP($A28,subQ,MATCH(S$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -15823,12 +16106,12 @@
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>BPS</t>
+          <t>EPS</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>BPS</t>
+          <t>EPS</t>
         </is>
       </c>
       <c r="E29" s="18">
@@ -15895,12 +16178,12 @@
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>DPS</t>
+          <t>BPS</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>DPS(보통주)</t>
+          <t>BPS</t>
         </is>
       </c>
       <c r="E30" s="18">
@@ -15967,12 +16250,12 @@
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>PER</t>
+          <t>DPS</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>PER</t>
+          <t>DPS(보통주)</t>
         </is>
       </c>
       <c r="E31" s="18">
@@ -16039,12 +16322,12 @@
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>PER</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>PER</t>
         </is>
       </c>
       <c r="E32" s="18">
@@ -16111,12 +16394,12 @@
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>매출전사</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>매출 전사(부문 미분리)</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="E33" s="18">
@@ -16183,12 +16466,12 @@
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>OP전사</t>
+          <t>매출전사</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>OP 전사(부문 미분리)</t>
+          <t>매출 전사(부문 미분리)</t>
         </is>
       </c>
       <c r="E34" s="18">
@@ -16255,71 +16538,71 @@
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>OPM</t>
+          <t>OP전사</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>영업이익률</t>
-        </is>
-      </c>
-      <c r="E35" s="21">
+          <t>OP 전사(부문 미분리)</t>
+        </is>
+      </c>
+      <c r="E35" s="18">
         <f>IFERROR(VLOOKUP($A35,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="F35" s="21">
+      <c r="F35" s="18">
         <f>IFERROR(VLOOKUP($A35,subQ,MATCH(F$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="G35" s="21">
+      <c r="G35" s="18">
         <f>IFERROR(VLOOKUP($A35,subQ,MATCH(G$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="H35" s="21">
+      <c r="H35" s="18">
         <f>IFERROR(VLOOKUP($A35,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I35" s="42">
+      <c r="I35" s="41">
         <f>IFERROR(VLOOKUP($A35,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="J35" s="31">
+      <c r="J35" s="20">
         <f>IFERROR(VLOOKUP($A35,subQ,MATCH(J$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="K35" s="31">
+      <c r="K35" s="20">
         <f>IFERROR(VLOOKUP($A35,subQ,MATCH(K$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="L35" s="31">
+      <c r="L35" s="20">
         <f>IFERROR(VLOOKUP($A35,subQ,MATCH(L$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="M35" s="31">
+      <c r="M35" s="20">
         <f>IFERROR(VLOOKUP($A35,subQ,MATCH(M$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="N35" s="31">
+      <c r="N35" s="20">
         <f>IFERROR(VLOOKUP($A35,subQ,MATCH(N$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="O35" s="31">
+      <c r="O35" s="20">
         <f>IFERROR(VLOOKUP($A35,subQ,MATCH(O$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="P35" s="31">
+      <c r="P35" s="20">
         <f>IFERROR(VLOOKUP($A35,subQ,MATCH(P$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="Q35" s="31">
+      <c r="Q35" s="20">
         <f>IFERROR(VLOOKUP($A35,subQ,MATCH(Q$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="R35" s="31">
+      <c r="R35" s="20">
         <f>IFERROR(VLOOKUP($A35,subQ,MATCH(R$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="S35" s="31">
+      <c r="S35" s="20">
         <f>IFERROR(VLOOKUP($A35,subQ,MATCH(S$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -16327,12 +16610,12 @@
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>NPM</t>
+          <t>OPM</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NPM</t>
+          <t>영업이익률</t>
         </is>
       </c>
       <c r="E36" s="21">
@@ -16399,168 +16682,240 @@
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>매출액 YoY</t>
+          <t>NPM</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>매출액 YoY</t>
-        </is>
+          <t>NPM</t>
+        </is>
+      </c>
+      <c r="E37" s="21">
+        <f>IFERROR(VLOOKUP($A37,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="F37" s="21">
+        <f>IFERROR(VLOOKUP($A37,subQ,MATCH(F$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="G37" s="21">
+        <f>IFERROR(VLOOKUP($A37,subQ,MATCH(G$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="H37" s="21">
+        <f>IFERROR(VLOOKUP($A37,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
+        <v/>
       </c>
       <c r="I37" s="42">
-        <f>IFERROR(I5/E5-1,"")</f>
+        <f>IFERROR(VLOOKUP($A37,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
       <c r="J37" s="31">
-        <f>IFERROR(J5/F5-1,"")</f>
+        <f>IFERROR(VLOOKUP($A37,subQ,MATCH(J$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
       <c r="K37" s="31">
-        <f>IFERROR(K5/G5-1,"")</f>
+        <f>IFERROR(VLOOKUP($A37,subQ,MATCH(K$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
       <c r="L37" s="31">
-        <f>IFERROR(L5/H5-1,"")</f>
+        <f>IFERROR(VLOOKUP($A37,subQ,MATCH(L$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
       <c r="M37" s="31">
-        <f>IFERROR(M5/I5-1,"")</f>
+        <f>IFERROR(VLOOKUP($A37,subQ,MATCH(M$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
       <c r="N37" s="31">
-        <f>IFERROR(N5/J5-1,"")</f>
+        <f>IFERROR(VLOOKUP($A37,subQ,MATCH(N$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
       <c r="O37" s="31">
-        <f>IFERROR(O5/K5-1,"")</f>
+        <f>IFERROR(VLOOKUP($A37,subQ,MATCH(O$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
       <c r="P37" s="31">
-        <f>IFERROR(P5/L5-1,"")</f>
+        <f>IFERROR(VLOOKUP($A37,subQ,MATCH(P$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
       <c r="Q37" s="31">
-        <f>IFERROR(Q5/M5-1,"")</f>
+        <f>IFERROR(VLOOKUP($A37,subQ,MATCH(Q$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
       <c r="R37" s="31">
-        <f>IFERROR(R5/N5-1,"")</f>
+        <f>IFERROR(VLOOKUP($A37,subQ,MATCH(R$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
       <c r="S37" s="31">
-        <f>IFERROR(S5/O5-1,"")</f>
+        <f>IFERROR(VLOOKUP($A37,subQ,MATCH(S$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>영업이익 YoY</t>
+          <t>매출액 YoY</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>영업이익 YoY</t>
+          <t>매출액 YoY</t>
         </is>
       </c>
       <c r="I38" s="42">
-        <f>IFERROR(I9/E9-1,"")</f>
+        <f>IFERROR(I5/E5-1,"")</f>
         <v/>
       </c>
       <c r="J38" s="31">
-        <f>IFERROR(J9/F9-1,"")</f>
+        <f>IFERROR(J5/F5-1,"")</f>
         <v/>
       </c>
       <c r="K38" s="31">
-        <f>IFERROR(K9/G9-1,"")</f>
+        <f>IFERROR(K5/G5-1,"")</f>
         <v/>
       </c>
       <c r="L38" s="31">
-        <f>IFERROR(L9/H9-1,"")</f>
+        <f>IFERROR(L5/H5-1,"")</f>
         <v/>
       </c>
       <c r="M38" s="31">
-        <f>IFERROR(M9/I9-1,"")</f>
+        <f>IFERROR(M5/I5-1,"")</f>
         <v/>
       </c>
       <c r="N38" s="31">
-        <f>IFERROR(N9/J9-1,"")</f>
+        <f>IFERROR(N5/J5-1,"")</f>
         <v/>
       </c>
       <c r="O38" s="31">
-        <f>IFERROR(O9/K9-1,"")</f>
+        <f>IFERROR(O5/K5-1,"")</f>
         <v/>
       </c>
       <c r="P38" s="31">
-        <f>IFERROR(P9/L9-1,"")</f>
+        <f>IFERROR(P5/L5-1,"")</f>
         <v/>
       </c>
       <c r="Q38" s="31">
-        <f>IFERROR(Q9/M9-1,"")</f>
+        <f>IFERROR(Q5/M5-1,"")</f>
         <v/>
       </c>
       <c r="R38" s="31">
-        <f>IFERROR(R9/N9-1,"")</f>
+        <f>IFERROR(R5/N5-1,"")</f>
         <v/>
       </c>
       <c r="S38" s="31">
-        <f>IFERROR(S9/O9-1,"")</f>
+        <f>IFERROR(S5/O5-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
+          <t>영업이익 YoY</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>영업이익 YoY</t>
+        </is>
+      </c>
+      <c r="I39" s="42">
+        <f>IFERROR(I9/E9-1,"")</f>
+        <v/>
+      </c>
+      <c r="J39" s="31">
+        <f>IFERROR(J9/F9-1,"")</f>
+        <v/>
+      </c>
+      <c r="K39" s="31">
+        <f>IFERROR(K9/G9-1,"")</f>
+        <v/>
+      </c>
+      <c r="L39" s="31">
+        <f>IFERROR(L9/H9-1,"")</f>
+        <v/>
+      </c>
+      <c r="M39" s="31">
+        <f>IFERROR(M9/I9-1,"")</f>
+        <v/>
+      </c>
+      <c r="N39" s="31">
+        <f>IFERROR(N9/J9-1,"")</f>
+        <v/>
+      </c>
+      <c r="O39" s="31">
+        <f>IFERROR(O9/K9-1,"")</f>
+        <v/>
+      </c>
+      <c r="P39" s="31">
+        <f>IFERROR(P9/L9-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q39" s="31">
+        <f>IFERROR(Q9/M9-1,"")</f>
+        <v/>
+      </c>
+      <c r="R39" s="31">
+        <f>IFERROR(R9/N9-1,"")</f>
+        <v/>
+      </c>
+      <c r="S39" s="31">
+        <f>IFERROR(S9/O9-1,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
           <t>지배주주순이익 YoY</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>지배주주순이익 YoY</t>
         </is>
       </c>
-      <c r="I39" s="42">
-        <f>IFERROR(I16/E16-1,"")</f>
-        <v/>
-      </c>
-      <c r="J39" s="31">
-        <f>IFERROR(J16/F16-1,"")</f>
-        <v/>
-      </c>
-      <c r="K39" s="31">
-        <f>IFERROR(K16/G16-1,"")</f>
-        <v/>
-      </c>
-      <c r="L39" s="31">
-        <f>IFERROR(L16/H16-1,"")</f>
-        <v/>
-      </c>
-      <c r="M39" s="31">
-        <f>IFERROR(M16/I16-1,"")</f>
-        <v/>
-      </c>
-      <c r="N39" s="31">
-        <f>IFERROR(N16/J16-1,"")</f>
-        <v/>
-      </c>
-      <c r="O39" s="31">
-        <f>IFERROR(O16/K16-1,"")</f>
-        <v/>
-      </c>
-      <c r="P39" s="31">
-        <f>IFERROR(P16/L16-1,"")</f>
-        <v/>
-      </c>
-      <c r="Q39" s="31">
-        <f>IFERROR(Q16/M16-1,"")</f>
-        <v/>
-      </c>
-      <c r="R39" s="31">
-        <f>IFERROR(R16/N16-1,"")</f>
-        <v/>
-      </c>
-      <c r="S39" s="31">
-        <f>IFERROR(S16/O16-1,"")</f>
+      <c r="I40" s="42">
+        <f>IFERROR(I17/E17-1,"")</f>
+        <v/>
+      </c>
+      <c r="J40" s="31">
+        <f>IFERROR(J17/F17-1,"")</f>
+        <v/>
+      </c>
+      <c r="K40" s="31">
+        <f>IFERROR(K17/G17-1,"")</f>
+        <v/>
+      </c>
+      <c r="L40" s="31">
+        <f>IFERROR(L17/H17-1,"")</f>
+        <v/>
+      </c>
+      <c r="M40" s="31">
+        <f>IFERROR(M17/I17-1,"")</f>
+        <v/>
+      </c>
+      <c r="N40" s="31">
+        <f>IFERROR(N17/J17-1,"")</f>
+        <v/>
+      </c>
+      <c r="O40" s="31">
+        <f>IFERROR(O17/K17-1,"")</f>
+        <v/>
+      </c>
+      <c r="P40" s="31">
+        <f>IFERROR(P17/L17-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q40" s="31">
+        <f>IFERROR(Q17/M17-1,"")</f>
+        <v/>
+      </c>
+      <c r="R40" s="31">
+        <f>IFERROR(R17/N17-1,"")</f>
+        <v/>
+      </c>
+      <c r="S40" s="31">
+        <f>IFERROR(S17/O17-1,"")</f>
         <v/>
       </c>
     </row>
@@ -16575,7 +16930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -16614,7 +16969,7 @@
         </is>
       </c>
       <c r="D2" s="18">
-        <f>변수!D46</f>
+        <f>변수!D47</f>
         <v/>
       </c>
       <c r="E2" s="38" t="n"/>
@@ -16864,12 +17219,12 @@
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>기타영업외손익</t>
+          <t>이자손익</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>기타영업외손익</t>
+          <t>이자손익(이자수익 − 이자비용)</t>
         </is>
       </c>
       <c r="E12" s="41">
@@ -16892,12 +17247,12 @@
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>세전이익</t>
+          <t>기타영업외손익</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>법인세비용차감전이익</t>
+          <t>기타영업외손익</t>
         </is>
       </c>
       <c r="E13" s="41">
@@ -16920,12 +17275,12 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>법인세비용</t>
+          <t>세전이익</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>법인세비용</t>
+          <t>법인세비용차감전이익</t>
         </is>
       </c>
       <c r="E14" s="41">
@@ -16948,12 +17303,12 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>당기순이익</t>
+          <t>법인세비용</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>당기순이익</t>
+          <t>법인세비용</t>
         </is>
       </c>
       <c r="E15" s="41">
@@ -16976,12 +17331,12 @@
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>지배주주순이익</t>
+          <t>당기순이익</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>지배주주순이익</t>
+          <t>당기순이익</t>
         </is>
       </c>
       <c r="E16" s="41">
@@ -17004,12 +17359,12 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>자산총계</t>
+          <t>지배주주순이익</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>자산총계</t>
+          <t>지배주주순이익</t>
         </is>
       </c>
       <c r="E17" s="41">
@@ -17032,12 +17387,12 @@
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>부채총계</t>
+          <t>자산총계</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>부채총계</t>
+          <t>자산총계</t>
         </is>
       </c>
       <c r="E18" s="41">
@@ -17060,12 +17415,12 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>자본총계</t>
+          <t>부채총계</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>자본총계</t>
+          <t>부채총계</t>
         </is>
       </c>
       <c r="E19" s="41">
@@ -17088,12 +17443,12 @@
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>지배주주지분</t>
+          <t>자본총계</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>지배주주지분</t>
+          <t>자본총계</t>
         </is>
       </c>
       <c r="E20" s="41">
@@ -17116,12 +17471,12 @@
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>총차입금</t>
+          <t>지배주주지분</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>총차입금</t>
+          <t>지배주주지분</t>
         </is>
       </c>
       <c r="E21" s="41">
@@ -17144,12 +17499,12 @@
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>순차입금</t>
+          <t>총차입금</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>순차입금</t>
+          <t>총차입금</t>
         </is>
       </c>
       <c r="E22" s="41">
@@ -17172,12 +17527,12 @@
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>이자발생자산</t>
+          <t>순차입금</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>이자발생자산</t>
+          <t>순차입금</t>
         </is>
       </c>
       <c r="E23" s="41">
@@ -17200,12 +17555,12 @@
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>현금및현금성자산</t>
+          <t>이자발생자산</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>현금및현금성자산</t>
+          <t>이자발생자산</t>
         </is>
       </c>
       <c r="E24" s="41">
@@ -17228,12 +17583,12 @@
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>현금및현금성자산</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>현금및현금성자산</t>
         </is>
       </c>
       <c r="E25" s="41">
@@ -17256,12 +17611,12 @@
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>영업활동현금흐름</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>영업활동현금흐름</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="E26" s="41">
@@ -17284,27 +17639,27 @@
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>주식수</t>
+          <t>영업활동현금흐름</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>유통주식수</t>
-        </is>
-      </c>
-      <c r="E27" s="43">
+          <t>영업활동현금흐름</t>
+        </is>
+      </c>
+      <c r="E27" s="41">
         <f>IFERROR(VLOOKUP($A27,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="F27" s="36">
+      <c r="F27" s="20">
         <f>IFERROR(VLOOKUP($A27,subQ,MATCH(F$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="G27" s="36">
+      <c r="G27" s="20">
         <f>IFERROR(VLOOKUP($A27,subQ,MATCH(G$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="H27" s="36">
+      <c r="H27" s="20">
         <f>IFERROR(VLOOKUP($A27,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -17312,27 +17667,27 @@
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>EPS</t>
+          <t>주식수</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>EPS</t>
-        </is>
-      </c>
-      <c r="E28" s="41">
+          <t>유통주식수</t>
+        </is>
+      </c>
+      <c r="E28" s="43">
         <f>IFERROR(VLOOKUP($A28,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="F28" s="20">
+      <c r="F28" s="36">
         <f>IFERROR(VLOOKUP($A28,subQ,MATCH(F$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="G28" s="20">
+      <c r="G28" s="36">
         <f>IFERROR(VLOOKUP($A28,subQ,MATCH(G$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="H28" s="20">
+      <c r="H28" s="36">
         <f>IFERROR(VLOOKUP($A28,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -17340,12 +17695,12 @@
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>BPS</t>
+          <t>EPS</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>BPS</t>
+          <t>EPS</t>
         </is>
       </c>
       <c r="E29" s="41">
@@ -17368,12 +17723,12 @@
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>DPS</t>
+          <t>BPS</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>DPS(보통주)</t>
+          <t>BPS</t>
         </is>
       </c>
       <c r="E30" s="41">
@@ -17396,12 +17751,12 @@
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>PER</t>
+          <t>DPS</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>PER</t>
+          <t>DPS(보통주)</t>
         </is>
       </c>
       <c r="E31" s="41">
@@ -17424,12 +17779,12 @@
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>PER</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>PER</t>
         </is>
       </c>
       <c r="E32" s="41">
@@ -17452,12 +17807,12 @@
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>매출전사</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>매출 전사(부문 미분리)</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="E33" s="41">
@@ -17480,12 +17835,12 @@
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>OP전사</t>
+          <t>매출전사</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>OP 전사(부문 미분리)</t>
+          <t>매출 전사(부문 미분리)</t>
         </is>
       </c>
       <c r="E34" s="41">
@@ -17508,27 +17863,27 @@
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>OPM</t>
+          <t>OP전사</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>영업이익률</t>
-        </is>
-      </c>
-      <c r="E35" s="42">
+          <t>OP 전사(부문 미분리)</t>
+        </is>
+      </c>
+      <c r="E35" s="41">
         <f>IFERROR(VLOOKUP($A35,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="F35" s="31">
+      <c r="F35" s="20">
         <f>IFERROR(VLOOKUP($A35,subQ,MATCH(F$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="G35" s="31">
+      <c r="G35" s="20">
         <f>IFERROR(VLOOKUP($A35,subQ,MATCH(G$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="H35" s="31">
+      <c r="H35" s="20">
         <f>IFERROR(VLOOKUP($A35,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -17536,12 +17891,12 @@
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>NPM</t>
+          <t>OPM</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NPM</t>
+          <t>영업이익률</t>
         </is>
       </c>
       <c r="E36" s="42">
@@ -17564,75 +17919,103 @@
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>매출액 YoY</t>
+          <t>NPM</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>매출액 YoY</t>
-        </is>
-      </c>
-      <c r="E37" s="38" t="n"/>
+          <t>NPM</t>
+        </is>
+      </c>
+      <c r="E37" s="42">
+        <f>IFERROR(VLOOKUP($A37,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
       <c r="F37" s="31">
-        <f>IFERROR(F5/E5-1,"")</f>
+        <f>IFERROR(VLOOKUP($A37,subQ,MATCH(F$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
       <c r="G37" s="31">
-        <f>IFERROR(G5/F5-1,"")</f>
+        <f>IFERROR(VLOOKUP($A37,subQ,MATCH(G$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
       <c r="H37" s="31">
-        <f>IFERROR(H5/G5-1,"")</f>
+        <f>IFERROR(VLOOKUP($A37,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>영업이익 YoY</t>
+          <t>매출액 YoY</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>영업이익 YoY</t>
+          <t>매출액 YoY</t>
         </is>
       </c>
       <c r="E38" s="38" t="n"/>
       <c r="F38" s="31">
-        <f>IFERROR(F9/E9-1,"")</f>
+        <f>IFERROR(F5/E5-1,"")</f>
         <v/>
       </c>
       <c r="G38" s="31">
-        <f>IFERROR(G9/F9-1,"")</f>
+        <f>IFERROR(G5/F5-1,"")</f>
         <v/>
       </c>
       <c r="H38" s="31">
-        <f>IFERROR(H9/G9-1,"")</f>
+        <f>IFERROR(H5/G5-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>지배주주순이익 YoY</t>
+          <t>영업이익 YoY</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>지배주주순이익 YoY</t>
+          <t>영업이익 YoY</t>
         </is>
       </c>
       <c r="E39" s="38" t="n"/>
       <c r="F39" s="31">
-        <f>IFERROR(F16/E16-1,"")</f>
+        <f>IFERROR(F9/E9-1,"")</f>
         <v/>
       </c>
       <c r="G39" s="31">
-        <f>IFERROR(G16/F16-1,"")</f>
+        <f>IFERROR(G9/F9-1,"")</f>
         <v/>
       </c>
       <c r="H39" s="31">
-        <f>IFERROR(H16/G16-1,"")</f>
+        <f>IFERROR(H9/G9-1,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>지배주주순이익 YoY</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>지배주주순이익 YoY</t>
+        </is>
+      </c>
+      <c r="E40" s="38" t="n"/>
+      <c r="F40" s="31">
+        <f>IFERROR(F17/E17-1,"")</f>
+        <v/>
+      </c>
+      <c r="G40" s="31">
+        <f>IFERROR(G17/F17-1,"")</f>
+        <v/>
+      </c>
+      <c r="H40" s="31">
+        <f>IFERROR(H17/G17-1,"")</f>
         <v/>
       </c>
     </row>
@@ -17660,7 +18043,7 @@
         </is>
       </c>
       <c r="C1" s="18">
-        <f>변수!D46</f>
+        <f>변수!D47</f>
         <v/>
       </c>
     </row>
@@ -17671,7 +18054,7 @@
         </is>
       </c>
       <c r="C2">
-        <f>변수!D47</f>
+        <f>변수!D48</f>
         <v/>
       </c>
     </row>
@@ -17848,7 +18231,7 @@
         </is>
       </c>
       <c r="D14" s="18">
-        <f>IFERROR(E7*변수!D52+F7*(1-변수!D52),"")</f>
+        <f>IFERROR(E7*변수!D53+F7*(1-변수!D53),"")</f>
         <v/>
       </c>
     </row>
@@ -17859,7 +18242,7 @@
         </is>
       </c>
       <c r="D15" s="26">
-        <f>변수!D49</f>
+        <f>변수!D50</f>
         <v/>
       </c>
       <c r="E15" s="18">
@@ -17883,7 +18266,7 @@
         </is>
       </c>
       <c r="D16" s="26">
-        <f>변수!D50</f>
+        <f>변수!D51</f>
         <v/>
       </c>
       <c r="E16" s="18">
@@ -17907,7 +18290,7 @@
         </is>
       </c>
       <c r="D17" s="26">
-        <f>변수!D51</f>
+        <f>변수!D52</f>
         <v/>
       </c>
       <c r="E17" s="18">
@@ -17971,7 +18354,7 @@
         </is>
       </c>
       <c r="D23" s="21">
-        <f>변수!D48</f>
+        <f>변수!D49</f>
         <v/>
       </c>
     </row>
@@ -19014,7 +19397,7 @@
         </is>
       </c>
       <c r="D16" s="26">
-        <f>변수!D56</f>
+        <f>변수!D57</f>
         <v/>
       </c>
       <c r="E16" s="2" t="inlineStr">

--- a/argus/kship/models/136150_model.xlsx
+++ b/argus/kship/models/136150_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$W$1</definedName>
@@ -3600,7 +3600,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -4169,35 +4169,35 @@
         <v>1418.75</v>
       </c>
       <c r="L6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="M6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="N6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="O6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="P6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="Q6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="R6" s="11" t="n"/>
       <c r="S6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="U6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="V6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="W6" s="11" t="n"/>
     </row>
@@ -4234,35 +4234,35 @@
         <v>1355.4</v>
       </c>
       <c r="L7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="M7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="N7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="O7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="P7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="Q7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="R7" s="11" t="n"/>
       <c r="S7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="U7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="V7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="W7" s="11" t="n"/>
     </row>
@@ -4299,35 +4299,35 @@
         <v>890.41</v>
       </c>
       <c r="L8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="M8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="N8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="O8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="P8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="Q8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="R8" s="11" t="n"/>
       <c r="S8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="U8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="V8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="W8" s="11" t="n"/>
     </row>
@@ -4364,35 +4364,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="L9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="M9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="N9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="O9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="P9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="Q9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="R9" s="11" t="n"/>
       <c r="S9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="U9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="V9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="W9" s="11" t="n"/>
     </row>
@@ -4429,35 +4429,35 @@
         <v>1631.97</v>
       </c>
       <c r="L10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="M10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="N10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="O10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="P10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="Q10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="R10" s="11" t="n"/>
       <c r="S10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="U10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="V10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="W10" s="11" t="n"/>
     </row>
@@ -4494,35 +4494,35 @@
         <v>1539.06</v>
       </c>
       <c r="L11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="M11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="N11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="O11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="P11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="Q11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="R11" s="11" t="n"/>
       <c r="S11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="U11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="V11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="W11" s="11" t="n"/>
     </row>
@@ -4559,35 +4559,35 @@
         <v>210.43</v>
       </c>
       <c r="L12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="M12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="N12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="O12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="P12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="Q12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="R12" s="11" t="n"/>
       <c r="S12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="U12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="V12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="W12" s="11" t="n"/>
     </row>
@@ -4624,35 +4624,35 @@
         <v>202.16</v>
       </c>
       <c r="L13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="M13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="N13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="O13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="P13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="Q13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="R13" s="11" t="n"/>
       <c r="S13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="U13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="V13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="W13" s="11" t="n"/>
     </row>
@@ -4709,7 +4709,7 @@
         <v>8580</v>
       </c>
       <c r="L15" s="20" t="n">
-        <v>12840</v>
+        <v>14220</v>
       </c>
       <c r="M15" s="11" t="n"/>
       <c r="N15" s="10" t="n"/>
@@ -4754,7 +4754,7 @@
         <v>12000</v>
       </c>
       <c r="L16" s="20" t="n">
-        <v>14100</v>
+        <v>15020</v>
       </c>
       <c r="M16" s="11" t="n"/>
       <c r="N16" s="10" t="n"/>
@@ -4844,7 +4844,7 @@
         <v>7830.5</v>
       </c>
       <c r="L18" s="20" t="n">
-        <v>11845</v>
+        <v>12640</v>
       </c>
       <c r="M18" s="11" t="n"/>
       <c r="N18" s="10" t="n"/>
@@ -6143,7 +6143,7 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>12840</v>
+        <v>14220</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -6530,7 +6530,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>1.945451968850066e-05</v>
+        <v>1.945451968849733e-05</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -7189,7 +7189,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -13761,7 +13761,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -16422,7 +16422,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="43" t="n">
@@ -17848,7 +17848,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.21</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/136150_model.xlsx
+++ b/argus/kship/models/136150_model.xlsx
@@ -3600,7 +3600,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -4169,35 +4169,35 @@
         <v>1418.75</v>
       </c>
       <c r="L6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="M6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="N6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="O6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="P6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="Q6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="R6" s="11" t="n"/>
       <c r="S6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="U6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="V6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="W6" s="11" t="n"/>
     </row>
@@ -4234,35 +4234,35 @@
         <v>1355.4</v>
       </c>
       <c r="L7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="M7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="N7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="O7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="P7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="Q7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="R7" s="11" t="n"/>
       <c r="S7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="U7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="V7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="W7" s="11" t="n"/>
     </row>
@@ -4299,35 +4299,35 @@
         <v>890.41</v>
       </c>
       <c r="L8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="M8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="N8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="O8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="P8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="Q8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="R8" s="11" t="n"/>
       <c r="S8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="U8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="V8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="W8" s="11" t="n"/>
     </row>
@@ -4364,35 +4364,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="L9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="M9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="N9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="O9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="P9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="Q9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="R9" s="11" t="n"/>
       <c r="S9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="U9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="V9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="W9" s="11" t="n"/>
     </row>
@@ -4429,35 +4429,35 @@
         <v>1631.97</v>
       </c>
       <c r="L10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="M10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="N10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="O10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="P10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="Q10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="R10" s="11" t="n"/>
       <c r="S10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="U10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="V10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="W10" s="11" t="n"/>
     </row>
@@ -4494,35 +4494,35 @@
         <v>1539.06</v>
       </c>
       <c r="L11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="M11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="N11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="O11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="P11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="Q11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="R11" s="11" t="n"/>
       <c r="S11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="U11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="V11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="W11" s="11" t="n"/>
     </row>
@@ -4559,35 +4559,35 @@
         <v>210.43</v>
       </c>
       <c r="L12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="M12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="N12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="O12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="P12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="Q12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="R12" s="11" t="n"/>
       <c r="S12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="U12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="V12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="W12" s="11" t="n"/>
     </row>
@@ -4624,35 +4624,35 @@
         <v>202.16</v>
       </c>
       <c r="L13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="M13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="N13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="O13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="P13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="Q13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="R13" s="11" t="n"/>
       <c r="S13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="U13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="V13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="W13" s="11" t="n"/>
     </row>
@@ -4709,7 +4709,7 @@
         <v>8580</v>
       </c>
       <c r="L15" s="20" t="n">
-        <v>14220</v>
+        <v>12900</v>
       </c>
       <c r="M15" s="11" t="n"/>
       <c r="N15" s="10" t="n"/>
@@ -4844,7 +4844,7 @@
         <v>7830.5</v>
       </c>
       <c r="L18" s="20" t="n">
-        <v>12640</v>
+        <v>12590</v>
       </c>
       <c r="M18" s="11" t="n"/>
       <c r="N18" s="10" t="n"/>
@@ -6143,11 +6143,11 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>14220</v>
+        <v>12900</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 10,850원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 12,440원)</t>
         </is>
       </c>
       <c r="H40" s="9" t="n"/>
@@ -6179,7 +6179,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -7189,7 +7189,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -13761,7 +13761,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -16422,7 +16422,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="43" t="n">
@@ -17848,7 +17848,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.44</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/136150_model.xlsx
+++ b/argus/kship/models/136150_model.xlsx
@@ -3600,7 +3600,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -6845,7 +6845,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -7189,7 +7189,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/136150_model.xlsx
+++ b/argus/kship/models/136150_model.xlsx
@@ -4169,35 +4169,35 @@
         <v>1418.75</v>
       </c>
       <c r="L6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="M6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="N6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="O6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="P6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="Q6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="R6" s="11" t="n"/>
       <c r="S6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="U6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="V6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="W6" s="11" t="n"/>
     </row>
@@ -4234,35 +4234,35 @@
         <v>1355.4</v>
       </c>
       <c r="L7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="M7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="N7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="O7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="P7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="Q7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="R7" s="11" t="n"/>
       <c r="S7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="U7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="V7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="W7" s="11" t="n"/>
     </row>
@@ -4299,35 +4299,35 @@
         <v>890.41</v>
       </c>
       <c r="L8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="M8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="N8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="O8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="P8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="Q8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="R8" s="11" t="n"/>
       <c r="S8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="U8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="V8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="W8" s="11" t="n"/>
     </row>
@@ -4364,35 +4364,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="L9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="M9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="N9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="O9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="P9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="Q9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="R9" s="11" t="n"/>
       <c r="S9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="U9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="V9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="W9" s="11" t="n"/>
     </row>
@@ -4429,35 +4429,35 @@
         <v>1631.97</v>
       </c>
       <c r="L10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="M10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="N10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="O10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="P10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="Q10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="R10" s="11" t="n"/>
       <c r="S10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="U10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="V10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="W10" s="11" t="n"/>
     </row>
@@ -4494,35 +4494,35 @@
         <v>1539.06</v>
       </c>
       <c r="L11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="M11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="N11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="O11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="P11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="Q11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="R11" s="11" t="n"/>
       <c r="S11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="U11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="V11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="W11" s="11" t="n"/>
     </row>
@@ -4559,35 +4559,35 @@
         <v>210.43</v>
       </c>
       <c r="L12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="M12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="N12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="O12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="P12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="Q12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="R12" s="11" t="n"/>
       <c r="S12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="U12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="V12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="W12" s="11" t="n"/>
     </row>
@@ -4624,35 +4624,35 @@
         <v>202.16</v>
       </c>
       <c r="L13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="M13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="N13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="O13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="P13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="Q13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="R13" s="11" t="n"/>
       <c r="S13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="U13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="V13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="W13" s="11" t="n"/>
     </row>
@@ -4709,7 +4709,7 @@
         <v>8580</v>
       </c>
       <c r="L15" s="20" t="n">
-        <v>12900</v>
+        <v>12190</v>
       </c>
       <c r="M15" s="11" t="n"/>
       <c r="N15" s="10" t="n"/>
@@ -4844,7 +4844,7 @@
         <v>7830.5</v>
       </c>
       <c r="L18" s="20" t="n">
-        <v>12590</v>
+        <v>12510</v>
       </c>
       <c r="M18" s="11" t="n"/>
       <c r="N18" s="10" t="n"/>
@@ -6143,11 +6143,11 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>12900</v>
+        <v>12190</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 12,440원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 14,100원)</t>
         </is>
       </c>
       <c r="H40" s="9" t="n"/>
@@ -6179,7 +6179,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -13761,7 +13761,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -16422,7 +16422,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="43" t="n">
@@ -17848,7 +17848,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/136150_model.xlsx
+++ b/argus/kship/models/136150_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$W$1</definedName>
@@ -3600,7 +3600,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -3801,7 +3801,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 매출 드라이버 폴백(고객 연동 격자 상관 0.87 가 단일 검정 5% 임계 r 0.88 미달(n=5) (suppliers_mentions·시차 2·수준·창 8)): 전년동기 × (1+g) 추세 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 +3/+1/+6/+4(중위 +3억) → 추정 2026Q3 +0억(차 -3억, -88%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>한계: 모델 quality.warnings — 매출 드라이버 폴백(고객 연동 격자 상관 0.87 가 단일 검정 5% 임계 r 0.88 미달(n=5, n_eff=5) (suppliers_mentions·시차 2·수준·창 8)): 전년동기 × (1+g) 추세 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 +3/+1/+6/+4(중위 +3억) → 추정 2026Q3 +0억(차 -3억, -88%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>1.945451968849733e-05</v>
+        <v>1.945451968850066e-05</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -7189,7 +7189,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/136150_model.xlsx
+++ b/argus/kship/models/136150_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$W$1</definedName>
@@ -4169,35 +4169,35 @@
         <v>1418.75</v>
       </c>
       <c r="L6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="M6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="N6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="O6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="P6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="Q6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="R6" s="11" t="n"/>
       <c r="S6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="U6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="V6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="W6" s="11" t="n"/>
     </row>
@@ -4234,35 +4234,35 @@
         <v>1355.4</v>
       </c>
       <c r="L7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="M7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="N7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="O7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="P7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="Q7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="R7" s="11" t="n"/>
       <c r="S7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="U7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="V7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="W7" s="11" t="n"/>
     </row>
@@ -4299,35 +4299,35 @@
         <v>890.41</v>
       </c>
       <c r="L8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="M8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="N8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="O8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="P8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="Q8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="R8" s="11" t="n"/>
       <c r="S8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="U8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="V8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="W8" s="11" t="n"/>
     </row>
@@ -4364,35 +4364,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="L9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="M9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="N9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="O9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="P9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="Q9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="R9" s="11" t="n"/>
       <c r="S9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="U9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="V9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="W9" s="11" t="n"/>
     </row>
@@ -4429,35 +4429,35 @@
         <v>1631.97</v>
       </c>
       <c r="L10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="M10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="N10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="O10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="P10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="Q10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="R10" s="11" t="n"/>
       <c r="S10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="U10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="V10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="W10" s="11" t="n"/>
     </row>
@@ -4494,35 +4494,35 @@
         <v>1539.06</v>
       </c>
       <c r="L11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="M11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="N11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="O11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="P11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="Q11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="R11" s="11" t="n"/>
       <c r="S11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="U11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="V11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="W11" s="11" t="n"/>
     </row>
@@ -4559,35 +4559,35 @@
         <v>210.43</v>
       </c>
       <c r="L12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="M12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="N12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="O12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="P12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="Q12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="R12" s="11" t="n"/>
       <c r="S12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="U12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="V12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="W12" s="11" t="n"/>
     </row>
@@ -4624,35 +4624,35 @@
         <v>202.16</v>
       </c>
       <c r="L13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="M13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="N13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="O13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="P13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="Q13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="R13" s="11" t="n"/>
       <c r="S13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="U13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="V13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="W13" s="11" t="n"/>
     </row>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 14,100원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 12,900원)</t>
         </is>
       </c>
       <c r="H40" s="9" t="n"/>
@@ -6530,7 +6530,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>1.945451968850066e-05</v>
+        <v>1.945451968849733e-05</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>

--- a/argus/kship/models/136150_model.xlsx
+++ b/argus/kship/models/136150_model.xlsx
@@ -3600,7 +3600,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -4169,35 +4169,35 @@
         <v>1418.75</v>
       </c>
       <c r="L6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="M6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="N6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="O6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="P6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="Q6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="R6" s="11" t="n"/>
       <c r="S6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="U6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="V6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="W6" s="11" t="n"/>
     </row>
@@ -4234,35 +4234,35 @@
         <v>1355.4</v>
       </c>
       <c r="L7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="M7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="N7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="O7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="P7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="Q7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="R7" s="11" t="n"/>
       <c r="S7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="U7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="V7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="W7" s="11" t="n"/>
     </row>
@@ -4299,35 +4299,35 @@
         <v>890.41</v>
       </c>
       <c r="L8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="M8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="N8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="O8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="P8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="Q8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="R8" s="11" t="n"/>
       <c r="S8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="U8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="V8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="W8" s="11" t="n"/>
     </row>
@@ -4364,35 +4364,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="L9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="M9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="N9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="O9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="P9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="Q9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="R9" s="11" t="n"/>
       <c r="S9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="U9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="V9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="W9" s="11" t="n"/>
     </row>
@@ -4429,35 +4429,35 @@
         <v>1631.97</v>
       </c>
       <c r="L10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="M10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="N10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="O10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="P10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="Q10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="R10" s="11" t="n"/>
       <c r="S10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="U10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="V10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="W10" s="11" t="n"/>
     </row>
@@ -4494,35 +4494,35 @@
         <v>1539.06</v>
       </c>
       <c r="L11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="M11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="N11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="O11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="P11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="Q11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="R11" s="11" t="n"/>
       <c r="S11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="U11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="V11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="W11" s="11" t="n"/>
     </row>
@@ -4559,35 +4559,35 @@
         <v>210.43</v>
       </c>
       <c r="L12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="M12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="N12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="O12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="P12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="Q12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="R12" s="11" t="n"/>
       <c r="S12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="U12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="V12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="W12" s="11" t="n"/>
     </row>
@@ -4624,35 +4624,35 @@
         <v>202.16</v>
       </c>
       <c r="L13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="M13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="N13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="O13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="P13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="Q13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="R13" s="11" t="n"/>
       <c r="S13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="U13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="V13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="W13" s="11" t="n"/>
     </row>
@@ -6845,7 +6845,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -7189,7 +7189,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/136150_model.xlsx
+++ b/argus/kship/models/136150_model.xlsx
@@ -3600,7 +3600,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -6845,7 +6845,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -7189,7 +7189,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/136150_model.xlsx
+++ b/argus/kship/models/136150_model.xlsx
@@ -3600,7 +3600,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -4709,7 +4709,7 @@
         <v>8580</v>
       </c>
       <c r="L15" s="20" t="n">
-        <v>12190</v>
+        <v>10650</v>
       </c>
       <c r="M15" s="11" t="n"/>
       <c r="N15" s="10" t="n"/>
@@ -4844,7 +4844,7 @@
         <v>7830.5</v>
       </c>
       <c r="L18" s="20" t="n">
-        <v>12510</v>
+        <v>12200</v>
       </c>
       <c r="M18" s="11" t="n"/>
       <c r="N18" s="10" t="n"/>
@@ -6143,7 +6143,7 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>12190</v>
+        <v>10650</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -7189,7 +7189,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -13761,7 +13761,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -16422,7 +16422,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="43" t="n">
@@ -17848,7 +17848,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/136150_model.xlsx
+++ b/argus/kship/models/136150_model.xlsx
@@ -3600,7 +3600,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -4169,35 +4169,35 @@
         <v>1418.75</v>
       </c>
       <c r="L6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="M6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="N6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="O6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="P6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="Q6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="R6" s="11" t="n"/>
       <c r="S6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="U6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="V6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="W6" s="11" t="n"/>
     </row>
@@ -4234,35 +4234,35 @@
         <v>1355.4</v>
       </c>
       <c r="L7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="M7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="N7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="O7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="P7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="Q7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="R7" s="11" t="n"/>
       <c r="S7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="U7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="V7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="W7" s="11" t="n"/>
     </row>
@@ -4299,35 +4299,35 @@
         <v>890.41</v>
       </c>
       <c r="L8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="M8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="N8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="O8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="P8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="Q8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="R8" s="11" t="n"/>
       <c r="S8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="U8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="V8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="W8" s="11" t="n"/>
     </row>
@@ -4364,35 +4364,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="L9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="M9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="N9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="O9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="P9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="Q9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="R9" s="11" t="n"/>
       <c r="S9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="U9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="V9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="W9" s="11" t="n"/>
     </row>
@@ -4429,35 +4429,35 @@
         <v>1631.97</v>
       </c>
       <c r="L10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="M10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="N10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="O10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="P10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="Q10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="R10" s="11" t="n"/>
       <c r="S10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="U10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="V10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="W10" s="11" t="n"/>
     </row>
@@ -4494,35 +4494,35 @@
         <v>1539.06</v>
       </c>
       <c r="L11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="M11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="N11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="O11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="P11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="Q11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="R11" s="11" t="n"/>
       <c r="S11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="U11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="V11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="W11" s="11" t="n"/>
     </row>
@@ -4559,35 +4559,35 @@
         <v>210.43</v>
       </c>
       <c r="L12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="M12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="N12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="O12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="P12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="Q12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="R12" s="11" t="n"/>
       <c r="S12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="U12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="V12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="W12" s="11" t="n"/>
     </row>
@@ -4624,35 +4624,35 @@
         <v>202.16</v>
       </c>
       <c r="L13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="M13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="N13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="O13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="P13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="Q13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="R13" s="11" t="n"/>
       <c r="S13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="U13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="V13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="W13" s="11" t="n"/>
     </row>
@@ -4709,7 +4709,7 @@
         <v>8580</v>
       </c>
       <c r="L15" s="20" t="n">
-        <v>10650</v>
+        <v>10250</v>
       </c>
       <c r="M15" s="11" t="n"/>
       <c r="N15" s="10" t="n"/>
@@ -4844,7 +4844,7 @@
         <v>7830.5</v>
       </c>
       <c r="L18" s="20" t="n">
-        <v>12200</v>
+        <v>11921.4</v>
       </c>
       <c r="M18" s="11" t="n"/>
       <c r="N18" s="10" t="n"/>
@@ -6143,11 +6143,11 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>10650</v>
+        <v>10250</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 12,900원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 12,190원)</t>
         </is>
       </c>
       <c r="H40" s="9" t="n"/>
@@ -6179,7 +6179,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -7189,7 +7189,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -13761,7 +13761,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -16422,7 +16422,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="43" t="n">
@@ -17848,7 +17848,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/136150_model.xlsx
+++ b/argus/kship/models/136150_model.xlsx
@@ -3600,7 +3600,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4169,35 +4169,35 @@
         <v>1418.75</v>
       </c>
       <c r="L6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="M6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="N6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="O6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="P6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="Q6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="R6" s="11" t="n"/>
       <c r="S6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="U6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="V6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="W6" s="11" t="n"/>
     </row>
@@ -4234,35 +4234,35 @@
         <v>1355.4</v>
       </c>
       <c r="L7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="M7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="N7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="O7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="P7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="Q7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="R7" s="11" t="n"/>
       <c r="S7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="U7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="V7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="W7" s="11" t="n"/>
     </row>
@@ -4299,35 +4299,35 @@
         <v>890.41</v>
       </c>
       <c r="L8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="M8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="N8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="O8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="P8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="Q8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="R8" s="11" t="n"/>
       <c r="S8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="U8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="V8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="W8" s="11" t="n"/>
     </row>
@@ -4364,35 +4364,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="L9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="M9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="N9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="O9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="P9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="Q9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="R9" s="11" t="n"/>
       <c r="S9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="U9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="V9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="W9" s="11" t="n"/>
     </row>
@@ -4429,35 +4429,35 @@
         <v>1631.97</v>
       </c>
       <c r="L10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="M10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="N10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="O10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="P10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="Q10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="R10" s="11" t="n"/>
       <c r="S10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="U10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="V10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="W10" s="11" t="n"/>
     </row>
@@ -4494,35 +4494,35 @@
         <v>1539.06</v>
       </c>
       <c r="L11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="M11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="N11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="O11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="P11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="Q11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="R11" s="11" t="n"/>
       <c r="S11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="U11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="V11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="W11" s="11" t="n"/>
     </row>
@@ -4559,35 +4559,35 @@
         <v>210.43</v>
       </c>
       <c r="L12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="M12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="N12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="O12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="P12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="Q12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="R12" s="11" t="n"/>
       <c r="S12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="U12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="V12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="W12" s="11" t="n"/>
     </row>
@@ -4624,35 +4624,35 @@
         <v>202.16</v>
       </c>
       <c r="L13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="M13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="N13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="O13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="P13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="Q13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="R13" s="11" t="n"/>
       <c r="S13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="U13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="V13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="W13" s="11" t="n"/>
     </row>
@@ -4709,7 +4709,7 @@
         <v>8580</v>
       </c>
       <c r="L15" s="20" t="n">
-        <v>10250</v>
+        <v>9860</v>
       </c>
       <c r="M15" s="11" t="n"/>
       <c r="N15" s="10" t="n"/>
@@ -4844,7 +4844,7 @@
         <v>7830.5</v>
       </c>
       <c r="L18" s="20" t="n">
-        <v>11921.4</v>
+        <v>11665</v>
       </c>
       <c r="M18" s="11" t="n"/>
       <c r="N18" s="10" t="n"/>
@@ -6143,11 +6143,11 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>10250</v>
+        <v>9860</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 12,190원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 10,650원)</t>
         </is>
       </c>
       <c r="H40" s="9" t="n"/>
@@ -6179,7 +6179,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -7189,7 +7189,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -13761,7 +13761,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -16422,7 +16422,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="43" t="n">
@@ -17848,7 +17848,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/136150_model.xlsx
+++ b/argus/kship/models/136150_model.xlsx
@@ -3600,7 +3600,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -4169,35 +4169,35 @@
         <v>1418.75</v>
       </c>
       <c r="L6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="M6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="N6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="O6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="P6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="Q6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="R6" s="11" t="n"/>
       <c r="S6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="U6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="V6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="W6" s="11" t="n"/>
     </row>
@@ -4234,35 +4234,35 @@
         <v>1355.4</v>
       </c>
       <c r="L7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="M7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="N7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="O7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="P7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="Q7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="R7" s="11" t="n"/>
       <c r="S7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="U7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="V7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="W7" s="11" t="n"/>
     </row>
@@ -4299,35 +4299,35 @@
         <v>890.41</v>
       </c>
       <c r="L8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="M8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="N8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="O8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="P8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="Q8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="R8" s="11" t="n"/>
       <c r="S8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="U8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="V8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="W8" s="11" t="n"/>
     </row>
@@ -4364,35 +4364,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="L9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="M9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="N9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="O9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="P9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="Q9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="R9" s="11" t="n"/>
       <c r="S9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="U9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="V9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="W9" s="11" t="n"/>
     </row>
@@ -4429,35 +4429,35 @@
         <v>1631.97</v>
       </c>
       <c r="L10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="M10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="N10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="O10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="P10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="Q10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="R10" s="11" t="n"/>
       <c r="S10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="U10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="V10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="W10" s="11" t="n"/>
     </row>
@@ -4494,35 +4494,35 @@
         <v>1539.06</v>
       </c>
       <c r="L11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="M11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="N11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="O11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="P11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="Q11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="R11" s="11" t="n"/>
       <c r="S11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="U11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="V11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="W11" s="11" t="n"/>
     </row>
@@ -4559,35 +4559,35 @@
         <v>210.43</v>
       </c>
       <c r="L12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="M12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="N12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="O12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="P12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="Q12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="R12" s="11" t="n"/>
       <c r="S12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="U12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="V12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="W12" s="11" t="n"/>
     </row>
@@ -4624,35 +4624,35 @@
         <v>202.16</v>
       </c>
       <c r="L13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="M13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="N13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="O13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="P13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="Q13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="R13" s="11" t="n"/>
       <c r="S13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="U13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="V13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="W13" s="11" t="n"/>
     </row>
@@ -4709,7 +4709,7 @@
         <v>8580</v>
       </c>
       <c r="L15" s="20" t="n">
-        <v>9860</v>
+        <v>9700</v>
       </c>
       <c r="M15" s="11" t="n"/>
       <c r="N15" s="10" t="n"/>
@@ -4844,7 +4844,7 @@
         <v>7830.5</v>
       </c>
       <c r="L18" s="20" t="n">
-        <v>11665</v>
+        <v>11020.9</v>
       </c>
       <c r="M18" s="11" t="n"/>
       <c r="N18" s="10" t="n"/>
@@ -6143,11 +6143,11 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>9860</v>
+        <v>9700</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 10,650원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 9,100원)</t>
         </is>
       </c>
       <c r="H40" s="9" t="n"/>
@@ -6179,7 +6179,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -7189,7 +7189,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -13761,7 +13761,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -16422,7 +16422,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="43" t="n">
@@ -17848,7 +17848,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/136150_model.xlsx
+++ b/argus/kship/models/136150_model.xlsx
@@ -3600,7 +3600,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4169,35 +4169,35 @@
         <v>1418.75</v>
       </c>
       <c r="L6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="M6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="N6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="O6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="P6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="Q6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="R6" s="11" t="n"/>
       <c r="S6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="U6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="V6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="W6" s="11" t="n"/>
     </row>
@@ -4234,35 +4234,35 @@
         <v>1355.4</v>
       </c>
       <c r="L7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="M7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="N7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="O7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="P7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="Q7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="R7" s="11" t="n"/>
       <c r="S7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="U7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="V7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="W7" s="11" t="n"/>
     </row>
@@ -4299,35 +4299,35 @@
         <v>890.41</v>
       </c>
       <c r="L8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="M8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="N8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="O8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="P8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="Q8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="R8" s="11" t="n"/>
       <c r="S8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="U8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="V8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="W8" s="11" t="n"/>
     </row>
@@ -4364,35 +4364,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="L9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="M9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="N9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="O9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="P9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="Q9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="R9" s="11" t="n"/>
       <c r="S9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="U9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="V9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="W9" s="11" t="n"/>
     </row>
@@ -4429,35 +4429,35 @@
         <v>1631.97</v>
       </c>
       <c r="L10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="M10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="N10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="O10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="P10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="Q10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="R10" s="11" t="n"/>
       <c r="S10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="U10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="V10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="W10" s="11" t="n"/>
     </row>
@@ -4494,35 +4494,35 @@
         <v>1539.06</v>
       </c>
       <c r="L11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="M11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="N11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="O11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="P11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="Q11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="R11" s="11" t="n"/>
       <c r="S11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="U11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="V11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="W11" s="11" t="n"/>
     </row>
@@ -4559,35 +4559,35 @@
         <v>210.43</v>
       </c>
       <c r="L12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="M12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="N12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="O12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="P12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="Q12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="R12" s="11" t="n"/>
       <c r="S12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="U12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="V12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="W12" s="11" t="n"/>
     </row>
@@ -4624,35 +4624,35 @@
         <v>202.16</v>
       </c>
       <c r="L13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="M13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="N13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="O13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="P13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="Q13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="R13" s="11" t="n"/>
       <c r="S13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="U13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="V13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="W13" s="11" t="n"/>
     </row>
@@ -4709,7 +4709,7 @@
         <v>8580</v>
       </c>
       <c r="L15" s="20" t="n">
-        <v>9700</v>
+        <v>7880</v>
       </c>
       <c r="M15" s="11" t="n"/>
       <c r="N15" s="10" t="n"/>
@@ -4799,7 +4799,7 @@
         <v>5400</v>
       </c>
       <c r="L17" s="20" t="n">
-        <v>8350</v>
+        <v>7810</v>
       </c>
       <c r="M17" s="11" t="n"/>
       <c r="N17" s="10" t="n"/>
@@ -4844,7 +4844,7 @@
         <v>7830.5</v>
       </c>
       <c r="L18" s="20" t="n">
-        <v>11020.9</v>
+        <v>10203.1</v>
       </c>
       <c r="M18" s="11" t="n"/>
       <c r="N18" s="10" t="n"/>
@@ -6143,11 +6143,11 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>9700</v>
+        <v>7880</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 9,100원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 8,550원)</t>
         </is>
       </c>
       <c r="H40" s="9" t="n"/>
@@ -6179,7 +6179,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -7189,7 +7189,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -13761,7 +13761,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -16422,7 +16422,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="43" t="n">
@@ -17848,7 +17848,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.67</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="33">
